--- a/プロジェクト型演習_成果物_TasBo_編集.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_編集.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER121\Desktop\重要資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\編集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2863CBF9-23EB-4F7F-AB02-6181D0B3AA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40E695F-6571-41B9-9E94-0D7CE13C80C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="表紙" sheetId="1" r:id="rId1"/>
-    <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
+    <sheet name="表紙 " sheetId="9" r:id="rId1"/>
+    <sheet name="ユースケース記述" sheetId="8" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="7" r:id="rId5"/>
@@ -38,21 +38,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
-    <t>○○○○システム</t>
-  </si>
-  <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -424,6 +415,134 @@
     <t>hiddenUpdateDatetime</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>TaskBoy（TasBo）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>栗原</t>
+    <rPh sb="0" eb="2">
+      <t>クリハラ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザが登録済みのタスク情報を変更・更新する。</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・ユーザがシステムにログインしていること
+・編集対象のタスクが存在していること
+・タスク一覧画面またはタスク詳細画面が表示されていること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク一覧画面から編集対象のタスクを選択する。
+2.ユーザは「タスク編集」ボタンを押下する。
+3.システムはタスク編集画面を表示する。
+4.ユーザはタスク情報（タスク名、カテゴリ、期限日、担当者、ステータス等）を修正する。
+5.ユーザは「編集完了」ボタンを押下する。
+6.システムは入力内容の妥当性をチェックする。
+7.システムはタスク情報を更新する。
+8.システムは編集完了メッセージを表示する。
+9.ユーザは「一覧表示」ボタンを押下する。
+10.システムはタスク一覧画面を表示する。</t>
+    <rPh sb="125" eb="129">
+      <t>ヘンシュウカンリョウ</t>
+    </rPh>
+    <rPh sb="190" eb="192">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="213" eb="217">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="222" eb="224">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1. 必須項目が未入力の場合（基本フロー6から分岐）
+a. システムは必須項目の未入力を検出する。
+b. システムはエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A2. タスク名が50文字を超えている場合（基本フロー6から分岐）
+a. システムはタスク名が文字数上限（50文字）を超えていることを検出する。
+b. システムは「タスク名は50文字以内で入力してください。」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A3. メモが100文字を超えている場合（基本フロー6から分岐）
+a. システムはメモが文字数上限（100文字）を超えていることを検出する。
+b. システムは「メモは100文字以内で入力してください。」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A4. 期限日に過去日が入力された場合（基本フロー6から分岐）
+a. システムは期限日が本日より前の日付であることを検出する。
+b. システムは「本日以降の日付を入力してください。」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A5. 更新対象のタスクが既に削除されている場合（基本フロー7から分岐）
+a. システムは更新処理を実行する。
+b. システムは対象タスクが存在しないことを検出する。
+c. システムは「対象のタスクは編集、または削除された可能性があります。」とエラーメッセージを表示する。
+d. システムはタスク一覧画面を表示する。
+e. ユースケースを終了する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1. データベース接続エラーまたはタスク更新処理中にシステムエラーが発生した場合
+a. システムエラーが発生する。
+b. システムはエラーメッセージを表示する。
+c. システムは処理を終了する。。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスク情報が更新されていること
+・タスク一覧画面が表示されていること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク管理システム「TaskBoy」（TasBo）</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名「チームTasBo」</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -522,7 +641,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="73">
     <border>
       <left/>
       <right/>
@@ -1338,21 +1457,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1362,9 +1517,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1485,19 +1637,127 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1515,302 +1775,329 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2860,169 +3147,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41AD61B8-82F6-468C-A20F-20BDF6A378B8}">
   <dimension ref="C1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="16" width="7.7109375" style="33" customWidth="1"/>
+    <col min="17" max="26" width="8.7109375" style="33" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16" ht="30" customHeight="1"/>
-    <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="98" t="s">
+    <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
+    <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
+      <c r="C2" s="189" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="1"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="190"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="190"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="190"/>
+      <c r="N2" s="190"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="191"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="1"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="191"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="1"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="191"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="97"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="3:16" ht="30" customHeight="1">
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="1"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="191"/>
+    </row>
+    <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="191"/>
+    </row>
+    <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
+      <c r="N7" s="192"/>
+      <c r="O7" s="192"/>
+      <c r="P7" s="191"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="100" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="97"/>
-      <c r="K8" s="97"/>
-      <c r="L8" s="97"/>
-      <c r="M8" s="97"/>
+      <c r="E8" s="193" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="95"/>
-      <c r="I13" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="94"/>
-      <c r="K13" s="95"/>
+      <c r="G13" s="194" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="163"/>
+      <c r="I13" s="195">
+        <v>46197</v>
+      </c>
+      <c r="J13" s="162"/>
+      <c r="K13" s="163"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="93"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="95"/>
+      <c r="G14" s="194"/>
+      <c r="H14" s="163"/>
+      <c r="I14" s="194"/>
+      <c r="J14" s="162"/>
+      <c r="K14" s="163"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="93"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="95"/>
+      <c r="G15" s="194"/>
+      <c r="H15" s="163"/>
+      <c r="I15" s="194"/>
+      <c r="J15" s="162"/>
+      <c r="K15" s="163"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="G16" s="196"/>
+      <c r="H16" s="196"/>
+      <c r="I16" s="196"/>
+      <c r="J16" s="196"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="96" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="97"/>
-      <c r="I17" s="97"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="97"/>
+      <c r="G17" s="197" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4009,6 +4297,7 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="G17:K17"/>
     <mergeCell ref="C2:O6"/>
@@ -4017,7 +4306,6 @@
     <mergeCell ref="I13:K13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:K14"/>
-    <mergeCell ref="G15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4026,204 +4314,240 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C7BB4AF-CC7C-49ED-B65A-9285D8F2F8E7}">
+  <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="33" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="139" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="142"/>
+      <c r="F1" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="142"/>
+      <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="132" t="s">
+      <c r="I1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="120"/>
-      <c r="F1" s="132" t="s">
+      <c r="J1" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="120"/>
-      <c r="H1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="144"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="146"/>
+      <c r="F2" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="146"/>
+      <c r="H2" s="147">
+        <v>46196</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="66"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="144"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="150"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="151"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="156"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="B5" s="158"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="159" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="160"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B6" s="162"/>
+      <c r="C6" s="163"/>
+      <c r="D6" s="72" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="164"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="161" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="129"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="130"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="116"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="131"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="B7" s="162"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="164"/>
+    </row>
+    <row r="8" spans="1:10" ht="50.25" customHeight="1">
+      <c r="A8" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="106"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="121" t="s">
+      <c r="B8" s="162"/>
+      <c r="C8" s="163"/>
+      <c r="D8" s="165" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="162"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="162"/>
+      <c r="I8" s="162"/>
+      <c r="J8" s="164"/>
+    </row>
+    <row r="9" spans="1:10" ht="152.25" customHeight="1">
+      <c r="A9" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="108"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="121" t="s">
+      <c r="B9" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="108"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="121" t="s">
+      <c r="C9" s="168"/>
+      <c r="D9" s="165" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="169"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
+      <c r="I9" s="169"/>
+      <c r="J9" s="170"/>
+    </row>
+    <row r="10" spans="1:10" ht="152.25" customHeight="1">
+      <c r="A10" s="171"/>
+      <c r="B10" s="172" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="108"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="122" t="s">
+      <c r="C10" s="173"/>
+      <c r="D10" s="174" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="175"/>
+      <c r="F10" s="175"/>
+      <c r="G10" s="175"/>
+      <c r="H10" s="175"/>
+      <c r="I10" s="175"/>
+      <c r="J10" s="176"/>
+    </row>
+    <row r="11" spans="1:10" ht="321.75" customHeight="1">
+      <c r="A11" s="177"/>
+      <c r="B11" s="178"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="181"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="181"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+    </row>
+    <row r="12" spans="1:10" ht="93.75" customHeight="1">
+      <c r="A12" s="183"/>
+      <c r="B12" s="167" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="125" t="s">
+      <c r="C12" s="163"/>
+      <c r="D12" s="165" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="162"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="162"/>
+      <c r="H12" s="162"/>
+      <c r="I12" s="162"/>
+      <c r="J12" s="164"/>
+    </row>
+    <row r="13" spans="1:10" ht="38.25" customHeight="1">
+      <c r="A13" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="95"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="108"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="123"/>
-      <c r="B10" s="125" t="s">
+      <c r="B13" s="162"/>
+      <c r="C13" s="163"/>
+      <c r="D13" s="165" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="162"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="164"/>
+    </row>
+    <row r="14" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A14" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="108"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="95"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="108"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="121" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="108"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="103"/>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="185"/>
+      <c r="F14" s="185"/>
+      <c r="G14" s="185"/>
+      <c r="H14" s="185"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="188"/>
+    </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
@@ -5210,35 +5534,36 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="D10:J11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5257,424 +5582,424 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="137" t="s">
-        <v>21</v>
+      <c r="A1" s="120" t="s">
+        <v>18</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="113"/>
-      <c r="D1" s="132" t="s">
+      <c r="D1" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="94"/>
+      <c r="F1" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="94"/>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="120"/>
-      <c r="F1" s="132" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" s="120"/>
-      <c r="H1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="114"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="129"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="104"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="114"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="130"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="105"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="116"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="10"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="10"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="10"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="10"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="7"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="10"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="10"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="10"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="7"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="13"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6670,420 +6995,420 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="137" t="s">
-        <v>22</v>
+      <c r="A1" s="120" t="s">
+        <v>19</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="113"/>
-      <c r="D1" s="132" t="s">
+      <c r="D1" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="94"/>
+      <c r="F1" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="94"/>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="120"/>
-      <c r="F1" s="132" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" s="120"/>
-      <c r="H1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="114"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="133" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="134"/>
-      <c r="F2" s="133" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="134"/>
-      <c r="H2" s="138">
+      <c r="B2" s="92"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="96"/>
+      <c r="H2" s="121">
         <v>46196</v>
       </c>
-      <c r="I2" s="126" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="129"/>
+      <c r="I2" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="104"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="114"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="130"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="105"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="116"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="10"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="10"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="10"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="10"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="7"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="10"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="10"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="13"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7096,7 +7421,7 @@
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="J44" s="14"/>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8080,592 +8405,592 @@
   <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="36" customWidth="1"/>
-    <col min="4" max="6" width="16.7109375" style="36" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" style="36" customWidth="1"/>
-    <col min="8" max="10" width="16.7109375" style="36" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="36" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="36"/>
+    <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
+    <col min="4" max="6" width="16.7109375" style="33" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" style="33" customWidth="1"/>
+    <col min="8" max="10" width="16.7109375" style="33" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="59"/>
+      <c r="H1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="63">
+        <v>46196</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="66"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="67"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="67"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="71"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="48"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="53"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="53"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="79" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="74">
+        <v>1</v>
+      </c>
+      <c r="B17" s="45"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="72"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="74">
+        <v>2</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="72"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="74">
+        <v>3</v>
+      </c>
+      <c r="B19" s="45"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="72"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="46"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="74">
+        <v>4</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="72"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="74">
+        <v>5</v>
+      </c>
+      <c r="B21" s="45"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="72"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="74">
         <v>6</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="79" t="s">
+      <c r="B22" s="45"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="72"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="75">
+        <v>8</v>
+      </c>
+      <c r="B23" s="76"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" s="78"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="79"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A24" s="80">
+        <v>9</v>
+      </c>
+      <c r="B24" s="81"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="83"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="84"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="45"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="45"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="74">
         <v>7</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="81" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="84">
-        <v>46196</v>
-      </c>
-      <c r="I2" s="86" t="s">
+      <c r="B28" s="45"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="87"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="88"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="88"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="92"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="51"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="69"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="71"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="72"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="74"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="72"/>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="74"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="74"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="74"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="74"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="51"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="68" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="48"/>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="47">
-        <v>1</v>
-      </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="47">
-        <v>2</v>
-      </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="50"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="51"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="47">
-        <v>3</v>
-      </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="50"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="51"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="47">
-        <v>4</v>
-      </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="39" t="s">
+      <c r="G28" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" s="50"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="51"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="47">
-        <v>5</v>
-      </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="50"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="51"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="47">
-        <v>6</v>
-      </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="50"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="51"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="62">
-        <v>8</v>
-      </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" s="65"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="66"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="57">
-        <v>9</v>
-      </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G24" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="60"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="61"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="51"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" s="48"/>
-      <c r="J27" s="51"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="47">
-        <v>7</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="50"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="51"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="47"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="51"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="46"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="47"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="49"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="51"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="47"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="46"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="47"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="51"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="46"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="47"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="51"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="46"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="62"/>
-      <c r="B33" s="63"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="63"/>
-      <c r="J33" s="66"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="79"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="52"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="56"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="88"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="89"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="57"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="61"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="84"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9635,27 +9960,23 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
@@ -9672,23 +9993,27 @@
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9709,921 +10034,921 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
       <c r="A1" s="111" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
       <c r="D1" s="112"/>
       <c r="E1" s="112"/>
       <c r="F1" s="113"/>
-      <c r="G1" s="132" t="s">
+      <c r="G1" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="93" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="132" t="s">
+      <c r="R1" s="94"/>
+      <c r="S1" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="132" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="132" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="120"/>
-      <c r="S1" s="132" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="106"/>
+      <c r="T1" s="119"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="114"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="133" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="133" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="151">
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="128">
         <v>46182</v>
       </c>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="133" t="s">
-        <v>67</v>
-      </c>
-      <c r="R2" s="134"/>
-      <c r="S2" s="133"/>
-      <c r="T2" s="152"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="96"/>
+      <c r="S2" s="95"/>
+      <c r="T2" s="129"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="114"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="135"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="135"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="135"/>
-      <c r="T3" s="153"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="130"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="116"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="136"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="136"/>
-      <c r="T4" s="154"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="100"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="131"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="132" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="118" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="119"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="133" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="107" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="108"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="104" t="s">
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="107" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="108"/>
+    </row>
+    <row r="8" spans="1:26" ht="7.5" customHeight="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="7"/>
+    </row>
+    <row r="9" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="105"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="105"/>
-      <c r="R5" s="105"/>
-      <c r="S5" s="105"/>
-      <c r="T5" s="106"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="146" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="107" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="94"/>
-      <c r="N6" s="94"/>
-      <c r="O6" s="94"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
-      <c r="S6" s="94"/>
-      <c r="T6" s="108"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="146" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+    </row>
+    <row r="10" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="107" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
-      <c r="S7" s="94"/>
-      <c r="T7" s="108"/>
-    </row>
-    <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="10"/>
-    </row>
-    <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18" t="s">
+      <c r="F10" s="14"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19" t="s">
+      <c r="F11" s="14"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-    </row>
-    <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17" t="s">
+      <c r="F12" s="14"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-    </row>
-    <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17" t="s">
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+    </row>
+    <row r="14" spans="1:26" ht="8.25" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="7"/>
+    </row>
+    <row r="15" spans="1:26" ht="18.75" customHeight="1">
+      <c r="A15" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-    </row>
-    <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
+      <c r="B15" s="91"/>
+      <c r="C15" s="136" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="91"/>
+      <c r="E15" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-    </row>
-    <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25" t="s">
+      <c r="F15" s="91"/>
+      <c r="G15" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="25"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-    </row>
-    <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="10"/>
-    </row>
-    <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="146" t="s">
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="95"/>
-      <c r="C15" s="149" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="95"/>
-      <c r="E15" s="148" t="s">
+      <c r="K15" s="91"/>
+      <c r="L15" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="95"/>
-      <c r="G15" s="148" t="s">
+      <c r="M15" s="90"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="94"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="148" t="s">
+      <c r="P15" s="90"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="95"/>
-      <c r="L15" s="148" t="s">
+      <c r="S15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="94"/>
-      <c r="N15" s="95"/>
-      <c r="O15" s="148" t="s">
+      <c r="T15" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="95"/>
-      <c r="R15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="134">
+        <v>1</v>
+      </c>
+      <c r="B16" s="91"/>
+      <c r="C16" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="D16" s="91"/>
+      <c r="E16" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="27" t="s">
+      <c r="F16" s="91"/>
+      <c r="G16" s="123" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="139">
-        <v>1</v>
-      </c>
-      <c r="B16" s="95"/>
-      <c r="C16" s="140" t="s">
+      <c r="H16" s="90"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="95"/>
-      <c r="E16" s="140" t="s">
+      <c r="K16" s="91"/>
+      <c r="L16" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="95"/>
-      <c r="G16" s="147" t="s">
+      <c r="M16" s="90"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="94"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="147" t="s">
+      <c r="P16" s="90"/>
+      <c r="Q16" s="91"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+    </row>
+    <row r="17" spans="1:26" ht="41.25" customHeight="1">
+      <c r="A17" s="134">
+        <v>2</v>
+      </c>
+      <c r="B17" s="91"/>
+      <c r="C17" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="95"/>
-      <c r="L16" s="143" t="s">
+      <c r="D17" s="91"/>
+      <c r="E17" s="135" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="94"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="143" t="s">
+      <c r="F17" s="91"/>
+      <c r="G17" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="94"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-    </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="139">
-        <v>2</v>
-      </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="140" t="s">
+      <c r="H17" s="90"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="95"/>
-      <c r="E17" s="140" t="s">
+      <c r="K17" s="91"/>
+      <c r="L17" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="147" t="s">
+      <c r="M17" s="90"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="94"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="147" t="s">
-        <v>62</v>
-      </c>
-      <c r="K17" s="95"/>
-      <c r="L17" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17" s="94"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="143" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="94"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="139"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="143"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="143"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="95"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="125"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="125"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="48" customHeight="1">
-      <c r="A19" s="139"/>
-      <c r="B19" s="95"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="147"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="147"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="143"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="95"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="125"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="125"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="91"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="48" customHeight="1">
-      <c r="A20" s="139"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="147"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="147"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="143"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="95"/>
-      <c r="O20" s="143"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
+      <c r="A20" s="134"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="125"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="91"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="48" customHeight="1">
-      <c r="A21" s="139"/>
-      <c r="B21" s="95"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="147"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="147"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="95"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="94"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="125"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="91"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27"/>
+      <c r="W21" s="27"/>
+      <c r="X21" s="27"/>
+      <c r="Y21" s="27"/>
+      <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="48" customHeight="1">
-      <c r="A22" s="139"/>
-      <c r="B22" s="95"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="147"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="147"/>
-      <c r="K22" s="95"/>
-      <c r="L22" s="143"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="95"/>
-      <c r="O22" s="143"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="95"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="125"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="91"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="48" customHeight="1">
-      <c r="A23" s="139"/>
-      <c r="B23" s="95"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="147"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="95"/>
-      <c r="O23" s="143"/>
-      <c r="P23" s="94"/>
-      <c r="Q23" s="95"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="125"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="48" customHeight="1">
-      <c r="A24" s="139"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="147"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="147"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="95"/>
-      <c r="O24" s="143"/>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="95"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
+      <c r="A24" s="134"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="125"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="27"/>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="48" customHeight="1">
-      <c r="A25" s="139"/>
-      <c r="B25" s="95"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="147"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="147"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="143"/>
-      <c r="M25" s="94"/>
-      <c r="N25" s="95"/>
-      <c r="O25" s="143"/>
-      <c r="P25" s="94"/>
-      <c r="Q25" s="95"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="125"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
+      <c r="W25" s="27"/>
+      <c r="X25" s="27"/>
+      <c r="Y25" s="27"/>
+      <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="48" customHeight="1">
-      <c r="A26" s="139"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="147"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="147"/>
-      <c r="K26" s="95"/>
-      <c r="L26" s="143"/>
-      <c r="M26" s="94"/>
-      <c r="N26" s="95"/>
-      <c r="O26" s="143"/>
-      <c r="P26" s="94"/>
-      <c r="Q26" s="95"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="125"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="125"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="48" customHeight="1">
-      <c r="A27" s="139"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="147"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="147"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="143"/>
-      <c r="M27" s="94"/>
-      <c r="N27" s="95"/>
-      <c r="O27" s="143"/>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="95"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="123"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="123"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="125"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="91"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="48" customHeight="1">
-      <c r="A28" s="139"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="147"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="147"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="143"/>
-      <c r="M28" s="94"/>
-      <c r="N28" s="95"/>
-      <c r="O28" s="143"/>
-      <c r="P28" s="94"/>
-      <c r="Q28" s="95"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
+      <c r="A28" s="134"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="123"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="123"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="125"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="91"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="48" customHeight="1">
-      <c r="A29" s="139"/>
-      <c r="B29" s="95"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="95"/>
-      <c r="G29" s="147"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="95"/>
-      <c r="J29" s="147"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="143"/>
-      <c r="M29" s="94"/>
-      <c r="N29" s="95"/>
-      <c r="O29" s="143"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="95"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="123"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="123"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="125"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="91"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="26"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="48" customHeight="1">
-      <c r="A30" s="139"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="147"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="147"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="143"/>
-      <c r="M30" s="94"/>
-      <c r="N30" s="95"/>
-      <c r="O30" s="143"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
+      <c r="A30" s="134"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="123"/>
+      <c r="K30" s="91"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="125"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="48" customHeight="1">
-      <c r="A31" s="141"/>
+      <c r="A31" s="137"/>
       <c r="B31" s="110"/>
-      <c r="C31" s="142"/>
+      <c r="C31" s="138"/>
       <c r="D31" s="110"/>
-      <c r="E31" s="142"/>
+      <c r="E31" s="138"/>
       <c r="F31" s="110"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="102"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="109"/>
       <c r="I31" s="110"/>
-      <c r="J31" s="155"/>
+      <c r="J31" s="124"/>
       <c r="K31" s="110"/>
-      <c r="L31" s="144"/>
-      <c r="M31" s="102"/>
+      <c r="L31" s="126"/>
+      <c r="M31" s="109"/>
       <c r="N31" s="110"/>
-      <c r="O31" s="144"/>
-      <c r="P31" s="102"/>
+      <c r="O31" s="126"/>
+      <c r="P31" s="109"/>
       <c r="Q31" s="110"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
     </row>
     <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
     </row>
     <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
@@ -11594,62 +11919,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11674,62 +11999,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果物_TasBo_編集.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_編集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\編集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40E695F-6571-41B9-9E94-0D7CE13C80C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D52DB7A-ACBC-4A9A-8C3D-8FA9BEF4ABD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="9" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -488,51 +488,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1. 必須項目が未入力の場合（基本フロー6から分岐）
-a. システムは必須項目の未入力を検出する。
-b. システムはエラーメッセージを表示する。
-c. システムは編集画面を再表示する。
-d. ユーザは入力内容を修正する。
-e. 基本フロー5へ戻る。
-A2. タスク名が50文字を超えている場合（基本フロー6から分岐）
-a. システムはタスク名が文字数上限（50文字）を超えていることを検出する。
-b. システムは「タスク名は50文字以内で入力してください。」とエラーメッセージを表示する。
-c. システムは編集画面を再表示する。
-d. ユーザは入力内容を修正する。
-e. 基本フロー5へ戻る。
-A3. メモが100文字を超えている場合（基本フロー6から分岐）
-a. システムはメモが文字数上限（100文字）を超えていることを検出する。
-b. システムは「メモは100文字以内で入力してください。」とエラーメッセージを表示する。
-c. システムは編集画面を再表示する。
-d. ユーザは入力内容を修正する。
-e. 基本フロー5へ戻る。
-A4. 期限日に過去日が入力された場合（基本フロー6から分岐）
-a. システムは期限日が本日より前の日付であることを検出する。
-b. システムは「本日以降の日付を入力してください。」とエラーメッセージを表示する。
-c. システムは編集画面を再表示する。
-d. ユーザは入力内容を修正する。
-e. 基本フロー5へ戻る。
-A5. 更新対象のタスクが既に削除されている場合（基本フロー7から分岐）
-a. システムは更新処理を実行する。
-b. システムは対象タスクが存在しないことを検出する。
-c. システムは「対象のタスクは編集、または削除された可能性があります。」とエラーメッセージを表示する。
-d. システムはタスク一覧画面を表示する。
-e. ユースケースを終了する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>E1. データベース接続エラーまたはタスク更新処理中にシステムエラーが発生した場合
-a. システムエラーが発生する。
-b. システムはエラーメッセージを表示する。
-c. システムは処理を終了する。。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスク情報が更新されていること
-・タスク一覧画面が表示されていること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク管理システム「TaskBoy」（TasBo）</t>
     <rPh sb="3" eb="5">
       <t>カンリ</t>
@@ -541,6 +496,61 @@
   </si>
   <si>
     <t>チーム名「チームTasBo」</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>第二版</t>
+    <rPh sb="0" eb="3">
+      <t>ダイニハン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスク情報が更新されていること
+・編集完了画面が表示されていること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1. 必須項目が未入力の場合（基本フロー6から分岐）
+a. システムは必須項目の未入力を検出する。
+b. システムは「このフィールドを入力してください」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A2. 対象タスクが既に削除されている場合(基本フロー2から分岐）
+a. システムは対象タスクが存在しないことを検出する。
+b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
+c. システムはタスク一覧画面へ戻る。
+A3. タスク名が50文字を超えている場合（基本フロー6から分岐）
+a. システムはタスク名が文字数上限（50文字）を超えていることを検出する。
+b. システムは「タスク名は50文字以内で入力してください。」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A4. メモが100文字を超えている場合（基本フロー6から分岐）
+a. システムはメモが文字数上限（100文字）を超えていることを検出する。
+b. システムは「メモは100文字以内で入力してください。」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。
+A5. 他ユーザ担当のタスクを編集しようとした場合（基本フロー3から分岐）
+a. システムは対象タスクの担当者を確認する。
+b. システムは対象タスクの担当者がログイン中ユーザではないことを検出する。
+c. システムは「タスクの編集は担当者本人のみ行えます。」とエラーメッセージを表示する。
+d. システムはタスク一覧画面へ戻る。
+A6. 期限日に過去日が入力された場合（基本フロー6から分岐）
+a. システムは期限日が本日より前の日付であることを検出する。
+b. システムは「本日以降の日付を入力してください。」とエラーメッセージを表示する。
+c. システムは編集画面を再表示する。
+d. ユーザは入力内容を修正する。
+e. 基本フロー5へ戻る。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1. データベース接続エラーまたはタスク更新処理中にシステムエラーが発生した場合
+a. システムエラーが発生する。
+b. システムはエラーメッセージを表示する。
+c. システムはタスク一覧画面へ遷移する。</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1637,6 +1647,267 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1661,9 +1932,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1679,15 +1947,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1700,12 +1962,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1721,9 +1977,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1775,56 +2028,65 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1832,81 +2094,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1921,183 +2108,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3158,159 +3168,163 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="191"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="45"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="191"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="45"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="191"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="45"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="191"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="45"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="191"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="45"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C7" s="192"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="192"/>
-      <c r="F7" s="192"/>
-      <c r="G7" s="192"/>
-      <c r="H7" s="192"/>
-      <c r="I7" s="192"/>
-      <c r="J7" s="192"/>
-      <c r="K7" s="192"/>
-      <c r="L7" s="192"/>
-      <c r="M7" s="192"/>
-      <c r="N7" s="192"/>
-      <c r="O7" s="192"/>
-      <c r="P7" s="191"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="45"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="193" t="s">
-        <v>111</v>
-      </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="E8" s="107" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="194" t="s">
+      <c r="G13" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="163"/>
-      <c r="I13" s="195">
+      <c r="H13" s="61"/>
+      <c r="I13" s="108">
         <v>46197</v>
       </c>
-      <c r="J13" s="162"/>
-      <c r="K13" s="163"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="61"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="194"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="194"/>
-      <c r="J14" s="162"/>
-      <c r="K14" s="163"/>
+      <c r="G14" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="61"/>
+      <c r="I14" s="108">
+        <v>46198</v>
+      </c>
+      <c r="J14" s="60"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="194"/>
-      <c r="H15" s="163"/>
-      <c r="I15" s="194"/>
-      <c r="J15" s="162"/>
-      <c r="K15" s="163"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G16" s="196"/>
-      <c r="H16" s="196"/>
-      <c r="I16" s="196"/>
-      <c r="J16" s="196"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="197" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="G17" s="104" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4325,228 +4339,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="142"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="142"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="143" t="s">
+      <c r="J1" s="44" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="144"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="146"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="146"/>
-      <c r="H2" s="147">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>46196</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="144"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="150"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="151"/>
-      <c r="B4" s="152"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="156"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="158"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="159" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="158"/>
-      <c r="J5" s="160"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="163"/>
-      <c r="D6" s="72" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="162"/>
-      <c r="H6" s="162"/>
-      <c r="I6" s="162"/>
-      <c r="J6" s="164"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="161" t="s">
+      <c r="A7" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="162"/>
-      <c r="C7" s="163"/>
-      <c r="D7" s="72" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="164"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="50.25" customHeight="1">
-      <c r="A8" s="161" t="s">
+      <c r="A8" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="162"/>
-      <c r="C8" s="163"/>
-      <c r="D8" s="165" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
-      <c r="I8" s="162"/>
-      <c r="J8" s="164"/>
-    </row>
-    <row r="9" spans="1:10" ht="152.25" customHeight="1">
-      <c r="A9" s="166" t="s">
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="63"/>
+    </row>
+    <row r="9" spans="1:10" ht="145.5" customHeight="1">
+      <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="168"/>
-      <c r="D9" s="165" t="s">
+      <c r="C9" s="90"/>
+      <c r="D9" s="79" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="169"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="169"/>
-      <c r="H9" s="169"/>
-      <c r="I9" s="169"/>
-      <c r="J9" s="170"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="152.25" customHeight="1">
-      <c r="A10" s="171"/>
-      <c r="B10" s="172" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="173"/>
-      <c r="D10" s="174" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="176"/>
-    </row>
-    <row r="11" spans="1:10" ht="321.75" customHeight="1">
-      <c r="A11" s="177"/>
-      <c r="B11" s="178"/>
-      <c r="C11" s="179"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="182"/>
-    </row>
-    <row r="12" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A12" s="183"/>
-      <c r="B12" s="167" t="s">
+      <c r="C10" s="94"/>
+      <c r="D10" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="99"/>
+    </row>
+    <row r="11" spans="1:10" ht="385.5" customHeight="1">
+      <c r="A11" s="87"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="102"/>
+    </row>
+    <row r="12" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A12" s="88"/>
+      <c r="B12" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="163"/>
-      <c r="D12" s="165" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="162"/>
-      <c r="F12" s="162"/>
-      <c r="G12" s="162"/>
-      <c r="H12" s="162"/>
-      <c r="I12" s="162"/>
-      <c r="J12" s="164"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A13" s="161" t="s">
+      <c r="A13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="162"/>
-      <c r="C13" s="163"/>
-      <c r="D13" s="165" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="162"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="162"/>
-      <c r="H13" s="162"/>
-      <c r="I13" s="162"/>
-      <c r="J13" s="164"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="79" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="63"/>
     </row>
     <row r="14" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A14" s="184" t="s">
+      <c r="A14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="186"/>
-      <c r="D14" s="187"/>
-      <c r="E14" s="185"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="188"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="84"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5537,7 +5551,6 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="A14:C14"/>
@@ -5552,6 +5565,7 @@
     <mergeCell ref="B10:C11"/>
     <mergeCell ref="D10:J11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:J12"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -5582,19 +5596,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="125"/>
+      <c r="F1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="94"/>
+      <c r="G1" s="125"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -5606,40 +5620,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="104"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="105"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="106"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -6995,19 +7009,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="125"/>
+      <c r="F1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="94"/>
+      <c r="G1" s="125"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -7019,48 +7033,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="95" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="96"/>
-      <c r="F2" s="95" t="s">
+      <c r="E2" s="127"/>
+      <c r="F2" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="96"/>
-      <c r="H2" s="121">
+      <c r="G2" s="127"/>
+      <c r="H2" s="130">
         <v>46196</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="104"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="105"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="106"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -8414,19 +8428,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="144"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="144"/>
       <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
@@ -8438,190 +8452,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="138"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="145"/>
+      <c r="F2" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="63">
+      <c r="G2" s="145"/>
+      <c r="H2" s="147">
         <v>46196</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="149"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="149"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="150" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="70" t="s">
+      <c r="B5" s="151"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="71"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="153"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="133"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="48"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="A7" s="135"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="137"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="139"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="139"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="53"/>
+      <c r="A10" s="138"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="139"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
+      <c r="A11" s="138"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="139"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
+      <c r="A12" s="138"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="139"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
+      <c r="A13" s="138"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="139"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="133"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="72" t="s">
+      <c r="B15" s="132"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="47"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="134"/>
       <c r="I15" s="34" t="s">
         <v>25</v>
       </c>
@@ -8630,11 +8644,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="134"/>
       <c r="D16" s="34" t="s">
         <v>27</v>
       </c>
@@ -8647,18 +8661,18 @@
       <c r="G16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="133"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="74">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="47"/>
+      <c r="B17" s="132"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="36" t="s">
         <v>73</v>
       </c>
@@ -8671,16 +8685,16 @@
       <c r="G17" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="46"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="133"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="155">
         <v>2</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="47"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="134"/>
       <c r="D18" s="36" t="s">
         <v>75</v>
       </c>
@@ -8693,16 +8707,16 @@
       <c r="G18" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="H18" s="72"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="46"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="133"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="74">
+      <c r="A19" s="155">
         <v>3</v>
       </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="47"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="134"/>
       <c r="D19" s="36" t="s">
         <v>74</v>
       </c>
@@ -8715,16 +8729,16 @@
       <c r="G19" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="72"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="46"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="133"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="155">
         <v>4</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="47"/>
+      <c r="B20" s="132"/>
+      <c r="C20" s="134"/>
       <c r="D20" s="36" t="s">
         <v>76</v>
       </c>
@@ -8737,16 +8751,16 @@
       <c r="G20" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="72"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="133"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="74">
+      <c r="A21" s="155">
         <v>5</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="47"/>
+      <c r="B21" s="132"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="36" t="s">
         <v>77</v>
       </c>
@@ -8759,16 +8773,16 @@
       <c r="G21" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="72"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="46"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="133"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="155">
         <v>6</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="47"/>
+      <c r="B22" s="132"/>
+      <c r="C22" s="134"/>
       <c r="D22" s="36" t="s">
         <v>78</v>
       </c>
@@ -8781,16 +8795,16 @@
       <c r="G22" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="H22" s="72"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="133"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="75">
+      <c r="A23" s="156">
         <v>8</v>
       </c>
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
+      <c r="B23" s="157"/>
+      <c r="C23" s="158"/>
       <c r="D23" s="38" t="s">
         <v>91</v>
       </c>
@@ -8803,16 +8817,16 @@
       <c r="G23" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="H23" s="78"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="79"/>
+      <c r="H23" s="159"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="160"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="80">
+      <c r="A24" s="161">
         <v>9</v>
       </c>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82"/>
+      <c r="B24" s="162"/>
+      <c r="C24" s="163"/>
       <c r="D24" s="40" t="s">
         <v>67</v>
       </c>
@@ -8825,37 +8839,37 @@
       <c r="G24" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="H24" s="83"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="84"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="165"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="B25" s="132"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="133"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="72" t="s">
+      <c r="B26" s="132"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="47"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="134"/>
       <c r="I26" s="34" t="s">
         <v>25</v>
       </c>
@@ -8864,11 +8878,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="47"/>
+      <c r="B27" s="132"/>
+      <c r="C27" s="134"/>
       <c r="D27" s="34" t="s">
         <v>27</v>
       </c>
@@ -8881,18 +8895,18 @@
       <c r="G27" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="73" t="s">
+      <c r="H27" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="133"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="74">
+      <c r="A28" s="155">
         <v>7</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="47"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="134"/>
       <c r="D28" s="36" t="s">
         <v>79</v>
       </c>
@@ -8905,92 +8919,92 @@
       <c r="G28" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="72"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="133"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="47"/>
+      <c r="A29" s="155"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="134"/>
       <c r="D29" s="36"/>
       <c r="E29" s="36"/>
       <c r="F29" s="36"/>
       <c r="G29" s="36"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="46"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="133"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="74"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="47"/>
+      <c r="A30" s="155"/>
+      <c r="B30" s="132"/>
+      <c r="C30" s="134"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="46"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="133"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="74"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="47"/>
+      <c r="A31" s="155"/>
+      <c r="B31" s="132"/>
+      <c r="C31" s="134"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="46"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="133"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="74"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="47"/>
+      <c r="A32" s="155"/>
+      <c r="B32" s="132"/>
+      <c r="C32" s="134"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="46"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="132"/>
+      <c r="J32" s="133"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="75"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="77"/>
+      <c r="A33" s="156"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="158"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="79"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="157"/>
+      <c r="J33" s="160"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="85"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="87"/>
+      <c r="A34" s="166"/>
+      <c r="B34" s="167"/>
+      <c r="C34" s="168"/>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="89"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="170"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="80"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="82"/>
+      <c r="A35" s="161"/>
+      <c r="B35" s="162"/>
+      <c r="C35" s="163"/>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="84"/>
+      <c r="H35" s="164"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="165"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10033,190 +10047,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="185" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="93" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="93" t="s">
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="93" t="s">
+      <c r="L1" s="186"/>
+      <c r="M1" s="186"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="93" t="s">
+      <c r="P1" s="125"/>
+      <c r="Q1" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="93" t="s">
+      <c r="R1" s="125"/>
+      <c r="S1" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="119"/>
+      <c r="T1" s="187"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="95" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="95" t="s">
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="128">
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="181">
         <v>46182</v>
       </c>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="95" t="s">
+      <c r="P2" s="127"/>
+      <c r="Q2" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="96"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="129"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="182"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="130"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="183"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="131"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="184"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="188" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="118" t="s">
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="189" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="119"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="186"/>
+      <c r="N5" s="186"/>
+      <c r="O5" s="186"/>
+      <c r="P5" s="186"/>
+      <c r="Q5" s="186"/>
+      <c r="R5" s="186"/>
+      <c r="S5" s="186"/>
+      <c r="T5" s="187"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="190" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="107" t="s">
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="191" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="108"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="172"/>
+      <c r="L6" s="172"/>
+      <c r="M6" s="172"/>
+      <c r="N6" s="172"/>
+      <c r="O6" s="172"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="172"/>
+      <c r="T6" s="192"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="190" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="107" t="s">
+      <c r="B7" s="172"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="108"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="172"/>
+      <c r="K7" s="172"/>
+      <c r="L7" s="172"/>
+      <c r="M7" s="172"/>
+      <c r="N7" s="172"/>
+      <c r="O7" s="172"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="172"/>
+      <c r="T7" s="192"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -10415,37 +10429,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="133" t="s">
+      <c r="A15" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="91"/>
-      <c r="C15" s="136" t="s">
+      <c r="B15" s="173"/>
+      <c r="C15" s="195" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="91"/>
-      <c r="E15" s="122" t="s">
+      <c r="D15" s="173"/>
+      <c r="E15" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="122" t="s">
+      <c r="F15" s="173"/>
+      <c r="G15" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="122" t="s">
+      <c r="H15" s="172"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="122" t="s">
+      <c r="K15" s="173"/>
+      <c r="L15" s="171" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="90"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="122" t="s">
+      <c r="M15" s="172"/>
+      <c r="N15" s="173"/>
+      <c r="O15" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="91"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="173"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -10457,37 +10471,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="193">
         <v>1</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="173"/>
+      <c r="C16" s="194" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="91"/>
-      <c r="E16" s="135" t="s">
+      <c r="D16" s="173"/>
+      <c r="E16" s="194" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="91"/>
-      <c r="G16" s="123" t="s">
+      <c r="F16" s="173"/>
+      <c r="G16" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="90"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="123" t="s">
+      <c r="H16" s="172"/>
+      <c r="I16" s="173"/>
+      <c r="J16" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="91"/>
-      <c r="L16" s="125" t="s">
+      <c r="K16" s="173"/>
+      <c r="L16" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="M16" s="90"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="125" t="s">
+      <c r="M16" s="172"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="178" t="s">
         <v>55</v>
       </c>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="91"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="173"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
       <c r="T16" s="26"/>
@@ -10499,37 +10513,37 @@
       <c r="Z16" s="27"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="193">
         <v>2</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="135" t="s">
+      <c r="B17" s="173"/>
+      <c r="C17" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="91"/>
-      <c r="E17" s="135" t="s">
+      <c r="D17" s="173"/>
+      <c r="E17" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="123" t="s">
+      <c r="F17" s="173"/>
+      <c r="G17" s="174" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="123" t="s">
+      <c r="H17" s="172"/>
+      <c r="I17" s="173"/>
+      <c r="J17" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="K17" s="91"/>
-      <c r="L17" s="125" t="s">
+      <c r="K17" s="173"/>
+      <c r="L17" s="178" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="90"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="125" t="s">
+      <c r="M17" s="172"/>
+      <c r="N17" s="173"/>
+      <c r="O17" s="178" t="s">
         <v>61</v>
       </c>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="91"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="173"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26"/>
@@ -10541,23 +10555,23 @@
       <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="134"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="125"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="125"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="91"/>
+      <c r="A18" s="193"/>
+      <c r="B18" s="173"/>
+      <c r="C18" s="194"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="174"/>
+      <c r="H18" s="172"/>
+      <c r="I18" s="173"/>
+      <c r="J18" s="174"/>
+      <c r="K18" s="173"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="172"/>
+      <c r="N18" s="173"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="172"/>
+      <c r="Q18" s="173"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="26"/>
@@ -10569,23 +10583,23 @@
       <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="48" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="125"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="91"/>
+      <c r="A19" s="193"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="194"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="194"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="172"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="174"/>
+      <c r="K19" s="173"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="172"/>
+      <c r="N19" s="173"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="172"/>
+      <c r="Q19" s="173"/>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
       <c r="T19" s="26"/>
@@ -10597,23 +10611,23 @@
       <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="48" customHeight="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="123"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="125"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="91"/>
+      <c r="A20" s="193"/>
+      <c r="B20" s="173"/>
+      <c r="C20" s="194"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="172"/>
+      <c r="I20" s="173"/>
+      <c r="J20" s="174"/>
+      <c r="K20" s="173"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="172"/>
+      <c r="N20" s="173"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="172"/>
+      <c r="Q20" s="173"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="26"/>
@@ -10625,23 +10639,23 @@
       <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="48" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="123"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="123"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="125"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="125"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="91"/>
+      <c r="A21" s="193"/>
+      <c r="B21" s="173"/>
+      <c r="C21" s="194"/>
+      <c r="D21" s="173"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="172"/>
+      <c r="I21" s="173"/>
+      <c r="J21" s="174"/>
+      <c r="K21" s="173"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="172"/>
+      <c r="N21" s="173"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="172"/>
+      <c r="Q21" s="173"/>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
       <c r="T21" s="26"/>
@@ -10653,23 +10667,23 @@
       <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="48" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="123"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="125"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="91"/>
+      <c r="A22" s="193"/>
+      <c r="B22" s="173"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="172"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="173"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="172"/>
+      <c r="N22" s="173"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="172"/>
+      <c r="Q22" s="173"/>
       <c r="R22" s="25"/>
       <c r="S22" s="25"/>
       <c r="T22" s="26"/>
@@ -10681,23 +10695,23 @@
       <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="48" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="125"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="91"/>
+      <c r="A23" s="193"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="174"/>
+      <c r="H23" s="172"/>
+      <c r="I23" s="173"/>
+      <c r="J23" s="174"/>
+      <c r="K23" s="173"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="172"/>
+      <c r="N23" s="173"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="173"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
       <c r="T23" s="26"/>
@@ -10709,23 +10723,23 @@
       <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="48" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="123"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="123"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="125"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="91"/>
+      <c r="A24" s="193"/>
+      <c r="B24" s="173"/>
+      <c r="C24" s="194"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="173"/>
+      <c r="G24" s="174"/>
+      <c r="H24" s="172"/>
+      <c r="I24" s="173"/>
+      <c r="J24" s="174"/>
+      <c r="K24" s="173"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="172"/>
+      <c r="N24" s="173"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
       <c r="T24" s="26"/>
@@ -10737,23 +10751,23 @@
       <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="48" customHeight="1">
-      <c r="A25" s="134"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="125"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="125"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="91"/>
+      <c r="A25" s="193"/>
+      <c r="B25" s="173"/>
+      <c r="C25" s="194"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="194"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="174"/>
+      <c r="H25" s="172"/>
+      <c r="I25" s="173"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="173"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="172"/>
+      <c r="N25" s="173"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="173"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
@@ -10765,23 +10779,23 @@
       <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="48" customHeight="1">
-      <c r="A26" s="134"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="123"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="125"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="125"/>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="91"/>
+      <c r="A26" s="193"/>
+      <c r="B26" s="173"/>
+      <c r="C26" s="194"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="194"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="174"/>
+      <c r="H26" s="172"/>
+      <c r="I26" s="173"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="173"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="172"/>
+      <c r="N26" s="173"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="172"/>
+      <c r="Q26" s="173"/>
       <c r="R26" s="25"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -10793,23 +10807,23 @@
       <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="48" customHeight="1">
-      <c r="A27" s="134"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="123"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="123"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="125"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="125"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="91"/>
+      <c r="A27" s="193"/>
+      <c r="B27" s="173"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="173"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="173"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="173"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="172"/>
+      <c r="Q27" s="173"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="26"/>
@@ -10821,23 +10835,23 @@
       <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="48" customHeight="1">
-      <c r="A28" s="134"/>
-      <c r="B28" s="91"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="123"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="123"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="125"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="125"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="91"/>
+      <c r="A28" s="193"/>
+      <c r="B28" s="173"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="194"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="172"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="172"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="172"/>
+      <c r="Q28" s="173"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
       <c r="T28" s="26"/>
@@ -10849,23 +10863,23 @@
       <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="48" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="91"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="123"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="123"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="125"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="125"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="91"/>
+      <c r="A29" s="193"/>
+      <c r="B29" s="173"/>
+      <c r="C29" s="194"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="173"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="173"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="172"/>
+      <c r="Q29" s="173"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
       <c r="T29" s="26"/>
@@ -10877,23 +10891,23 @@
       <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="48" customHeight="1">
-      <c r="A30" s="134"/>
-      <c r="B30" s="91"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="123"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="123"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="125"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="91"/>
-      <c r="O30" s="125"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="91"/>
+      <c r="A30" s="193"/>
+      <c r="B30" s="173"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="172"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="172"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
       <c r="R30" s="25"/>
       <c r="S30" s="25"/>
       <c r="T30" s="26"/>
@@ -10905,23 +10919,23 @@
       <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="48" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="124"/>
-      <c r="K31" s="110"/>
-      <c r="L31" s="126"/>
-      <c r="M31" s="109"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="126"/>
-      <c r="P31" s="109"/>
-      <c r="Q31" s="110"/>
+      <c r="A31" s="196"/>
+      <c r="B31" s="177"/>
+      <c r="C31" s="197"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="197"/>
+      <c r="F31" s="177"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="177"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="177"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="177"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="177"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="29"/>

--- a/プロジェクト型演習_成果物_TasBo_編集.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_編集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\編集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D52DB7A-ACBC-4A9A-8C3D-8FA9BEF4ABD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8807534-F481-4466-803A-6805422DE84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -463,31 +463,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザはタスク一覧画面から編集対象のタスクを選択する。
-2.ユーザは「タスク編集」ボタンを押下する。
-3.システムはタスク編集画面を表示する。
-4.ユーザはタスク情報（タスク名、カテゴリ、期限日、担当者、ステータス等）を修正する。
-5.ユーザは「編集完了」ボタンを押下する。
-6.システムは入力内容の妥当性をチェックする。
-7.システムはタスク情報を更新する。
-8.システムは編集完了メッセージを表示する。
-9.ユーザは「一覧表示」ボタンを押下する。
-10.システムはタスク一覧画面を表示する。</t>
-    <rPh sb="125" eb="129">
-      <t>ヘンシュウカンリョウ</t>
-    </rPh>
-    <rPh sb="190" eb="192">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="213" eb="217">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="222" eb="224">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク管理システム「TaskBoy」（TasBo）</t>
     <rPh sb="3" eb="5">
       <t>カンリ</t>
@@ -506,8 +481,32 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>E1. データベース接続エラーまたはタスク更新処理中にシステムエラーが発生した場合
+a. システムエラーが発生する。
+b. システムはエラーメッセージを表示する。
+c. システムはタスク一覧画面へ遷移する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク一覧画面から編集対象のタスクを選択する。
+2.ユーザは「タスク編集」ボタンを押下する。
+3.システムはタスク編集画面を表示する。
+4.ユーザはタスク情報（タスク名、カテゴリ、期限日、担当者、ステータス等）を修正する。
+5.ユーザは「編集完了」ボタンを押下する。
+6. システムは入力内容の妥当性をチェックする。
+7. システムは対象タスクの存在確認および担当者確認を行う。
+8. システムはタスク情報を更新する。
+9. システムは編集完了メッセージを表示する。
+10. ユーザは「一覧表示」ボタンを押下する。
+11. システムはタスク一覧画面を表示する。</t>
+    <rPh sb="125" eb="129">
+      <t>ヘンシュウカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>・タスク情報が更新されていること
-・編集完了画面が表示されていること</t>
+・タスク一覧画面が表示されていること</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -519,24 +518,24 @@
 e. 基本フロー5へ戻る。
 A2. 対象タスクが既に削除されている場合(基本フロー2から分岐）
 a. システムは対象タスクが存在しないことを検出する。
-b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
+b. システムは「対象のタスクが見つかりません。」とエラーメッセージを表示する。
 c. システムはタスク一覧画面へ戻る。
 A3. タスク名が50文字を超えている場合（基本フロー6から分岐）
 a. システムはタスク名が文字数上限（50文字）を超えていることを検出する。
-b. システムは「タスク名は50文字以内で入力してください。」とエラーメッセージを表示する。
+b. システムは「タスク名の入力が正しくありません。」とエラーメッセージを表示する。
 c. システムは編集画面を再表示する。
 d. ユーザは入力内容を修正する。
 e. 基本フロー5へ戻る。
 A4. メモが100文字を超えている場合（基本フロー6から分岐）
 a. システムはメモが文字数上限（100文字）を超えていることを検出する。
-b. システムは「メモは100文字以内で入力してください。」とエラーメッセージを表示する。
+b. システムは「メモの入力が正しくありません。」とエラーメッセージを表示する。
 c. システムは編集画面を再表示する。
 d. ユーザは入力内容を修正する。
 e. 基本フロー5へ戻る。
-A5. 他ユーザ担当のタスクを編集しようとした場合（基本フロー3から分岐）
+A5. 他ユーザ担当のタスクを編集しようとした場合（基本フロー2から分岐）
 a. システムは対象タスクの担当者を確認する。
 b. システムは対象タスクの担当者がログイン中ユーザではないことを検出する。
-c. システムは「タスクの編集は担当者本人のみ行えます。」とエラーメッセージを表示する。
+c. システムは「タスクの編集は本人しか行うことができません。」とエラーメッセージを表示する。
 d. システムはタスク一覧画面へ戻る。
 A6. 期限日に過去日が入力された場合（基本フロー6から分岐）
 a. システムは期限日が本日より前の日付であることを検出する。
@@ -544,13 +543,24 @@
 c. システムは編集画面を再表示する。
 d. ユーザは入力内容を修正する。
 e. 基本フロー5へ戻る。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>E1. データベース接続エラーまたはタスク更新処理中にシステムエラーが発生した場合
-a. システムエラーが発生する。
-b. システムはエラーメッセージを表示する。
-c. システムはタスク一覧画面へ遷移する。</t>
+    <rPh sb="224" eb="225">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="357" eb="359">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="360" eb="361">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="522" eb="524">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="525" eb="526">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="725" eb="726">
+      <t>オコナ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -3267,7 +3277,7 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="68"/>
       <c r="G8" s="68"/>
@@ -3295,7 +3305,7 @@
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H14" s="61"/>
       <c r="I14" s="108">
@@ -3319,7 +3329,7 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H17" s="68"/>
       <c r="I17" s="68"/>
@@ -4470,7 +4480,7 @@
       <c r="I8" s="60"/>
       <c r="J8" s="63"/>
     </row>
-    <row r="9" spans="1:10" ht="145.5" customHeight="1">
+    <row r="9" spans="1:10" ht="176.25" customHeight="1">
       <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
@@ -4479,7 +4489,7 @@
       </c>
       <c r="C9" s="90"/>
       <c r="D9" s="79" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E9" s="91"/>
       <c r="F9" s="91"/>
@@ -4495,7 +4505,7 @@
       </c>
       <c r="C10" s="94"/>
       <c r="D10" s="97" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" s="98"/>
       <c r="F10" s="98"/>
@@ -4523,7 +4533,7 @@
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="79" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -4539,7 +4549,7 @@
       <c r="B13" s="60"/>
       <c r="C13" s="61"/>
       <c r="D13" s="79" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E13" s="60"/>
       <c r="F13" s="60"/>

--- a/プロジェクト型演習_成果物_TasBo_編集.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_編集.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\編集\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8807534-F481-4466-803A-6805422DE84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F132AAF-6A7C-4966-844F-AD855B69FC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1669,6 +1669,93 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1702,21 +1789,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1763,78 +1835,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1918,17 +1918,68 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1987,137 +2038,86 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3196,67 +3196,67 @@
       <c r="P2" s="45"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
       <c r="P3" s="45"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
       <c r="P4" s="45"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
       <c r="P5" s="45"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
       <c r="P6" s="45"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3279,14 +3279,14 @@
       <c r="E8" s="107" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3296,30 +3296,30 @@
       <c r="G13" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="61"/>
+      <c r="H13" s="50"/>
       <c r="I13" s="108">
         <v>46197</v>
       </c>
-      <c r="J13" s="60"/>
-      <c r="K13" s="61"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="61"/>
+      <c r="H14" s="50"/>
       <c r="I14" s="108">
         <v>46198</v>
       </c>
-      <c r="J14" s="60"/>
-      <c r="K14" s="61"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="50"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="103"/>
-      <c r="H15" s="61"/>
+      <c r="H15" s="50"/>
       <c r="I15" s="103"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="61"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="47"/>
@@ -3331,10 +3331,10 @@
       <c r="G17" s="104" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4349,19 +4349,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="85"/>
+      <c r="F1" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
@@ -4373,204 +4373,204 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="99"/>
+      <c r="F2" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="99"/>
+      <c r="H2" s="102">
         <v>46196</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="51"/>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="52"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="81"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="82"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="86" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="58"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="87"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="63"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="62" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="63"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="52"/>
     </row>
     <row r="8" spans="1:10" ht="50.25" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="79" t="s">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="63"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="52"/>
     </row>
     <row r="9" spans="1:10" ht="176.25" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="90"/>
-      <c r="D9" s="79" t="s">
+      <c r="C9" s="64"/>
+      <c r="D9" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="66"/>
     </row>
     <row r="10" spans="1:10" ht="152.25" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="93" t="s">
+      <c r="A10" s="60"/>
+      <c r="B10" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="97" t="s">
+      <c r="C10" s="68"/>
+      <c r="D10" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="99"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="73"/>
     </row>
     <row r="11" spans="1:10" ht="385.5" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="102"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="76"/>
     </row>
     <row r="12" spans="1:10" ht="65.25" customHeight="1">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89" t="s">
+      <c r="A12" s="62"/>
+      <c r="B12" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="79" t="s">
+      <c r="C12" s="50"/>
+      <c r="D12" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="63"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="79" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="63"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="84"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5561,6 +5561,18 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="A14:C14"/>
@@ -5576,18 +5588,6 @@
     <mergeCell ref="D10:J11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:J12"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8438,19 +8438,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="157" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="158"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="144"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="161"/>
+      <c r="F1" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="144"/>
+      <c r="G1" s="161"/>
       <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
@@ -8462,67 +8462,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="155"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="145"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="162"/>
+      <c r="F2" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="145"/>
-      <c r="H2" s="147">
+      <c r="G2" s="162"/>
+      <c r="H2" s="164">
         <v>46196</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="51"/>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="138"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="149"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="166"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="138"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="149"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="166"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="151"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="152" t="s">
+      <c r="B5" s="168"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="169" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="153"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="170"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="150" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="132"/>
@@ -8533,94 +8533,94 @@
       <c r="G6" s="132"/>
       <c r="H6" s="132"/>
       <c r="I6" s="132"/>
-      <c r="J6" s="133"/>
+      <c r="J6" s="134"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="135"/>
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="137"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="154"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="138"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="139"/>
+      <c r="A8" s="155"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="156"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="138"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="139"/>
+      <c r="A9" s="155"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="156"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="138"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="139"/>
+      <c r="A10" s="155"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="156"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="138"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="139"/>
+      <c r="A11" s="155"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="156"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="138"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="139"/>
+      <c r="A12" s="155"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="156"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="138"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="139"/>
+      <c r="A13" s="155"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="156"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="131" t="s">
+      <c r="A14" s="150" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="132"/>
@@ -8631,21 +8631,21 @@
       <c r="G14" s="132"/>
       <c r="H14" s="132"/>
       <c r="I14" s="132"/>
-      <c r="J14" s="133"/>
+      <c r="J14" s="134"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="131" t="s">
+      <c r="A15" s="150" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="132"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="62" t="s">
+      <c r="C15" s="133"/>
+      <c r="D15" s="58" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="132"/>
       <c r="F15" s="132"/>
       <c r="G15" s="132"/>
-      <c r="H15" s="134"/>
+      <c r="H15" s="133"/>
       <c r="I15" s="34" t="s">
         <v>25</v>
       </c>
@@ -8654,11 +8654,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="131" t="s">
+      <c r="A16" s="150" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="132"/>
-      <c r="C16" s="134"/>
+      <c r="C16" s="133"/>
       <c r="D16" s="34" t="s">
         <v>27</v>
       </c>
@@ -8671,18 +8671,18 @@
       <c r="G16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="151" t="s">
         <v>66</v>
       </c>
       <c r="I16" s="132"/>
-      <c r="J16" s="133"/>
+      <c r="J16" s="134"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="131">
         <v>1</v>
       </c>
       <c r="B17" s="132"/>
-      <c r="C17" s="134"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="36" t="s">
         <v>73</v>
       </c>
@@ -8695,16 +8695,16 @@
       <c r="G17" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="62"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="132"/>
-      <c r="J17" s="133"/>
+      <c r="J17" s="134"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155">
+      <c r="A18" s="131">
         <v>2</v>
       </c>
       <c r="B18" s="132"/>
-      <c r="C18" s="134"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="36" t="s">
         <v>75</v>
       </c>
@@ -8717,16 +8717,16 @@
       <c r="G18" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="H18" s="62"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="132"/>
-      <c r="J18" s="133"/>
+      <c r="J18" s="134"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155">
+      <c r="A19" s="131">
         <v>3</v>
       </c>
       <c r="B19" s="132"/>
-      <c r="C19" s="134"/>
+      <c r="C19" s="133"/>
       <c r="D19" s="36" t="s">
         <v>74</v>
       </c>
@@ -8739,16 +8739,16 @@
       <c r="G19" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="62"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="132"/>
-      <c r="J19" s="133"/>
+      <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155">
+      <c r="A20" s="131">
         <v>4</v>
       </c>
       <c r="B20" s="132"/>
-      <c r="C20" s="134"/>
+      <c r="C20" s="133"/>
       <c r="D20" s="36" t="s">
         <v>76</v>
       </c>
@@ -8761,16 +8761,16 @@
       <c r="G20" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="62"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="132"/>
-      <c r="J20" s="133"/>
+      <c r="J20" s="134"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155">
+      <c r="A21" s="131">
         <v>5</v>
       </c>
       <c r="B21" s="132"/>
-      <c r="C21" s="134"/>
+      <c r="C21" s="133"/>
       <c r="D21" s="36" t="s">
         <v>77</v>
       </c>
@@ -8783,16 +8783,16 @@
       <c r="G21" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="62"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="132"/>
-      <c r="J21" s="133"/>
+      <c r="J21" s="134"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155">
+      <c r="A22" s="131">
         <v>6</v>
       </c>
       <c r="B22" s="132"/>
-      <c r="C22" s="134"/>
+      <c r="C22" s="133"/>
       <c r="D22" s="36" t="s">
         <v>78</v>
       </c>
@@ -8805,16 +8805,16 @@
       <c r="G22" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="H22" s="62"/>
+      <c r="H22" s="58"/>
       <c r="I22" s="132"/>
-      <c r="J22" s="133"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="156">
+      <c r="A23" s="145">
         <v>8</v>
       </c>
-      <c r="B23" s="157"/>
-      <c r="C23" s="158"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="147"/>
       <c r="D23" s="38" t="s">
         <v>91</v>
       </c>
@@ -8827,16 +8827,16 @@
       <c r="G23" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="H23" s="159"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="160"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="149"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="161">
+      <c r="A24" s="140">
         <v>9</v>
       </c>
-      <c r="B24" s="162"/>
-      <c r="C24" s="163"/>
+      <c r="B24" s="141"/>
+      <c r="C24" s="142"/>
       <c r="D24" s="40" t="s">
         <v>67</v>
       </c>
@@ -8849,12 +8849,12 @@
       <c r="G24" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="H24" s="164"/>
-      <c r="I24" s="162"/>
-      <c r="J24" s="165"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="141"/>
+      <c r="J24" s="144"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="131" t="s">
+      <c r="A25" s="150" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="132"/>
@@ -8865,21 +8865,21 @@
       <c r="G25" s="132"/>
       <c r="H25" s="132"/>
       <c r="I25" s="132"/>
-      <c r="J25" s="133"/>
+      <c r="J25" s="134"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="131" t="s">
+      <c r="A26" s="150" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="132"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="62" t="s">
+      <c r="C26" s="133"/>
+      <c r="D26" s="58" t="s">
         <v>72</v>
       </c>
       <c r="E26" s="132"/>
       <c r="F26" s="132"/>
       <c r="G26" s="132"/>
-      <c r="H26" s="134"/>
+      <c r="H26" s="133"/>
       <c r="I26" s="34" t="s">
         <v>25</v>
       </c>
@@ -8888,11 +8888,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="131" t="s">
+      <c r="A27" s="150" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="132"/>
-      <c r="C27" s="134"/>
+      <c r="C27" s="133"/>
       <c r="D27" s="34" t="s">
         <v>27</v>
       </c>
@@ -8905,18 +8905,18 @@
       <c r="G27" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="154" t="s">
+      <c r="H27" s="151" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="132"/>
-      <c r="J27" s="133"/>
+      <c r="J27" s="134"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="155">
+      <c r="A28" s="131">
         <v>7</v>
       </c>
       <c r="B28" s="132"/>
-      <c r="C28" s="134"/>
+      <c r="C28" s="133"/>
       <c r="D28" s="36" t="s">
         <v>79</v>
       </c>
@@ -8929,92 +8929,92 @@
       <c r="G28" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="62"/>
+      <c r="H28" s="58"/>
       <c r="I28" s="132"/>
-      <c r="J28" s="133"/>
+      <c r="J28" s="134"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="155"/>
+      <c r="A29" s="131"/>
       <c r="B29" s="132"/>
-      <c r="C29" s="134"/>
+      <c r="C29" s="133"/>
       <c r="D29" s="36"/>
       <c r="E29" s="36"/>
       <c r="F29" s="36"/>
       <c r="G29" s="36"/>
-      <c r="H29" s="62"/>
+      <c r="H29" s="58"/>
       <c r="I29" s="132"/>
-      <c r="J29" s="133"/>
+      <c r="J29" s="134"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="155"/>
+      <c r="A30" s="131"/>
       <c r="B30" s="132"/>
-      <c r="C30" s="134"/>
+      <c r="C30" s="133"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="62"/>
+      <c r="H30" s="58"/>
       <c r="I30" s="132"/>
-      <c r="J30" s="133"/>
+      <c r="J30" s="134"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="155"/>
+      <c r="A31" s="131"/>
       <c r="B31" s="132"/>
-      <c r="C31" s="134"/>
+      <c r="C31" s="133"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="62"/>
+      <c r="H31" s="58"/>
       <c r="I31" s="132"/>
-      <c r="J31" s="133"/>
+      <c r="J31" s="134"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="155"/>
+      <c r="A32" s="131"/>
       <c r="B32" s="132"/>
-      <c r="C32" s="134"/>
+      <c r="C32" s="133"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="62"/>
+      <c r="H32" s="58"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="133"/>
+      <c r="J32" s="134"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="156"/>
-      <c r="B33" s="157"/>
-      <c r="C33" s="158"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="147"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="157"/>
-      <c r="J33" s="160"/>
+      <c r="H33" s="148"/>
+      <c r="I33" s="146"/>
+      <c r="J33" s="149"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="166"/>
-      <c r="B34" s="167"/>
-      <c r="C34" s="168"/>
+      <c r="A34" s="135"/>
+      <c r="B34" s="136"/>
+      <c r="C34" s="137"/>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="167"/>
-      <c r="J34" s="170"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="136"/>
+      <c r="J34" s="139"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="161"/>
-      <c r="B35" s="162"/>
-      <c r="C35" s="163"/>
+      <c r="A35" s="140"/>
+      <c r="B35" s="141"/>
+      <c r="C35" s="142"/>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="164"/>
-      <c r="I35" s="162"/>
-      <c r="J35" s="165"/>
+      <c r="H35" s="143"/>
+      <c r="I35" s="141"/>
+      <c r="J35" s="144"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9984,23 +9984,27 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
@@ -10017,27 +10021,23 @@
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10057,7 +10057,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="196" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="116"/>
@@ -10068,14 +10068,14 @@
       <c r="G1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
       <c r="J1" s="125"/>
       <c r="K1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="186"/>
-      <c r="M1" s="186"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
       <c r="N1" s="125"/>
       <c r="O1" s="124" t="s">
         <v>5</v>
@@ -10088,7 +10088,7 @@
       <c r="S1" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="187"/>
+      <c r="T1" s="184"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="118"/>
@@ -10100,16 +10100,16 @@
       <c r="G2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="180"/>
-      <c r="I2" s="180"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
       <c r="J2" s="127"/>
       <c r="K2" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="180"/>
-      <c r="M2" s="180"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
       <c r="N2" s="127"/>
-      <c r="O2" s="181">
+      <c r="O2" s="192">
         <v>46182</v>
       </c>
       <c r="P2" s="127"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="R2" s="127"/>
       <c r="S2" s="126"/>
-      <c r="T2" s="182"/>
+      <c r="T2" s="193"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="118"/>
@@ -10140,7 +10140,7 @@
       <c r="Q3" s="128"/>
       <c r="R3" s="120"/>
       <c r="S3" s="128"/>
-      <c r="T3" s="183"/>
+      <c r="T3" s="194"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="121"/>
@@ -10162,85 +10162,85 @@
       <c r="Q4" s="129"/>
       <c r="R4" s="123"/>
       <c r="S4" s="129"/>
-      <c r="T4" s="184"/>
+      <c r="T4" s="195"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="188" t="s">
+      <c r="A5" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="182"/>
       <c r="F5" s="125"/>
-      <c r="G5" s="189" t="s">
+      <c r="G5" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="186"/>
-      <c r="I5" s="186"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="186"/>
-      <c r="L5" s="186"/>
-      <c r="M5" s="186"/>
-      <c r="N5" s="186"/>
-      <c r="O5" s="186"/>
-      <c r="P5" s="186"/>
-      <c r="Q5" s="186"/>
-      <c r="R5" s="186"/>
-      <c r="S5" s="186"/>
-      <c r="T5" s="187"/>
+      <c r="H5" s="182"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="182"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="182"/>
+      <c r="M5" s="182"/>
+      <c r="N5" s="182"/>
+      <c r="O5" s="182"/>
+      <c r="P5" s="182"/>
+      <c r="Q5" s="182"/>
+      <c r="R5" s="182"/>
+      <c r="S5" s="182"/>
+      <c r="T5" s="184"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="190" t="s">
+      <c r="A6" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="172"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="191" t="s">
+      <c r="B6" s="178"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="186" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="172"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="172"/>
-      <c r="M6" s="172"/>
-      <c r="N6" s="172"/>
-      <c r="O6" s="172"/>
-      <c r="P6" s="172"/>
-      <c r="Q6" s="172"/>
-      <c r="R6" s="172"/>
-      <c r="S6" s="172"/>
-      <c r="T6" s="192"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="178"/>
+      <c r="L6" s="178"/>
+      <c r="M6" s="178"/>
+      <c r="N6" s="178"/>
+      <c r="O6" s="178"/>
+      <c r="P6" s="178"/>
+      <c r="Q6" s="178"/>
+      <c r="R6" s="178"/>
+      <c r="S6" s="178"/>
+      <c r="T6" s="187"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="190" t="s">
+      <c r="A7" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
-      <c r="D7" s="172"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="191" t="s">
+      <c r="B7" s="178"/>
+      <c r="C7" s="178"/>
+      <c r="D7" s="178"/>
+      <c r="E7" s="178"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
-      <c r="L7" s="172"/>
-      <c r="M7" s="172"/>
-      <c r="N7" s="172"/>
-      <c r="O7" s="172"/>
-      <c r="P7" s="172"/>
-      <c r="Q7" s="172"/>
-      <c r="R7" s="172"/>
-      <c r="S7" s="172"/>
-      <c r="T7" s="192"/>
+      <c r="H7" s="178"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="178"/>
+      <c r="M7" s="178"/>
+      <c r="N7" s="178"/>
+      <c r="O7" s="178"/>
+      <c r="P7" s="178"/>
+      <c r="Q7" s="178"/>
+      <c r="R7" s="178"/>
+      <c r="S7" s="178"/>
+      <c r="T7" s="187"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -10439,37 +10439,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="190" t="s">
+      <c r="A15" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="173"/>
-      <c r="C15" s="195" t="s">
+      <c r="B15" s="172"/>
+      <c r="C15" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="173"/>
-      <c r="E15" s="171" t="s">
+      <c r="D15" s="172"/>
+      <c r="E15" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="173"/>
-      <c r="G15" s="171" t="s">
+      <c r="F15" s="172"/>
+      <c r="G15" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="172"/>
-      <c r="I15" s="173"/>
-      <c r="J15" s="171" t="s">
+      <c r="H15" s="178"/>
+      <c r="I15" s="172"/>
+      <c r="J15" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="173"/>
-      <c r="L15" s="171" t="s">
+      <c r="K15" s="172"/>
+      <c r="L15" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="172"/>
-      <c r="N15" s="173"/>
-      <c r="O15" s="171" t="s">
+      <c r="M15" s="178"/>
+      <c r="N15" s="172"/>
+      <c r="O15" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="172"/>
-      <c r="Q15" s="173"/>
+      <c r="P15" s="178"/>
+      <c r="Q15" s="172"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -10481,37 +10481,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="193">
+      <c r="A16" s="171">
         <v>1</v>
       </c>
-      <c r="B16" s="173"/>
-      <c r="C16" s="194" t="s">
+      <c r="B16" s="172"/>
+      <c r="C16" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="173"/>
-      <c r="E16" s="194" t="s">
+      <c r="D16" s="172"/>
+      <c r="E16" s="173" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="173"/>
-      <c r="G16" s="174" t="s">
+      <c r="F16" s="172"/>
+      <c r="G16" s="188" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="172"/>
-      <c r="I16" s="173"/>
-      <c r="J16" s="174" t="s">
+      <c r="H16" s="178"/>
+      <c r="I16" s="172"/>
+      <c r="J16" s="188" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="173"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="172"/>
+      <c r="L16" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="M16" s="172"/>
-      <c r="N16" s="173"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="178"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="177" t="s">
         <v>55</v>
       </c>
-      <c r="P16" s="172"/>
-      <c r="Q16" s="173"/>
+      <c r="P16" s="178"/>
+      <c r="Q16" s="172"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
       <c r="T16" s="26"/>
@@ -10523,37 +10523,37 @@
       <c r="Z16" s="27"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="193">
+      <c r="A17" s="171">
         <v>2</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="194" t="s">
+      <c r="B17" s="172"/>
+      <c r="C17" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="173"/>
-      <c r="E17" s="194" t="s">
+      <c r="D17" s="172"/>
+      <c r="E17" s="173" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="173"/>
-      <c r="G17" s="174" t="s">
+      <c r="F17" s="172"/>
+      <c r="G17" s="188" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="172"/>
-      <c r="I17" s="173"/>
-      <c r="J17" s="174" t="s">
+      <c r="H17" s="178"/>
+      <c r="I17" s="172"/>
+      <c r="J17" s="188" t="s">
         <v>59</v>
       </c>
-      <c r="K17" s="173"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="172"/>
+      <c r="L17" s="177" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="172"/>
-      <c r="N17" s="173"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="178"/>
+      <c r="N17" s="172"/>
+      <c r="O17" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="P17" s="172"/>
-      <c r="Q17" s="173"/>
+      <c r="P17" s="178"/>
+      <c r="Q17" s="172"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26"/>
@@ -10565,23 +10565,23 @@
       <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="193"/>
-      <c r="B18" s="173"/>
-      <c r="C18" s="194"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="194"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="174"/>
-      <c r="H18" s="172"/>
-      <c r="I18" s="173"/>
-      <c r="J18" s="174"/>
-      <c r="K18" s="173"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="172"/>
-      <c r="N18" s="173"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="172"/>
-      <c r="Q18" s="173"/>
+      <c r="A18" s="171"/>
+      <c r="B18" s="172"/>
+      <c r="C18" s="173"/>
+      <c r="D18" s="172"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="172"/>
+      <c r="G18" s="188"/>
+      <c r="H18" s="178"/>
+      <c r="I18" s="172"/>
+      <c r="J18" s="188"/>
+      <c r="K18" s="172"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="178"/>
+      <c r="N18" s="172"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="178"/>
+      <c r="Q18" s="172"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="26"/>
@@ -10593,23 +10593,23 @@
       <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="48" customHeight="1">
-      <c r="A19" s="193"/>
-      <c r="B19" s="173"/>
-      <c r="C19" s="194"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="172"/>
-      <c r="I19" s="173"/>
-      <c r="J19" s="174"/>
-      <c r="K19" s="173"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="172"/>
-      <c r="N19" s="173"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="172"/>
-      <c r="Q19" s="173"/>
+      <c r="A19" s="171"/>
+      <c r="B19" s="172"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="172"/>
+      <c r="G19" s="188"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="172"/>
+      <c r="J19" s="188"/>
+      <c r="K19" s="172"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="178"/>
+      <c r="N19" s="172"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="178"/>
+      <c r="Q19" s="172"/>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
       <c r="T19" s="26"/>
@@ -10621,23 +10621,23 @@
       <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="48" customHeight="1">
-      <c r="A20" s="193"/>
-      <c r="B20" s="173"/>
-      <c r="C20" s="194"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="194"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="172"/>
-      <c r="I20" s="173"/>
-      <c r="J20" s="174"/>
-      <c r="K20" s="173"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="172"/>
-      <c r="N20" s="173"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="172"/>
-      <c r="Q20" s="173"/>
+      <c r="A20" s="171"/>
+      <c r="B20" s="172"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="172"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="172"/>
+      <c r="G20" s="188"/>
+      <c r="H20" s="178"/>
+      <c r="I20" s="172"/>
+      <c r="J20" s="188"/>
+      <c r="K20" s="172"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="178"/>
+      <c r="N20" s="172"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="178"/>
+      <c r="Q20" s="172"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="26"/>
@@ -10649,23 +10649,23 @@
       <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="48" customHeight="1">
-      <c r="A21" s="193"/>
-      <c r="B21" s="173"/>
-      <c r="C21" s="194"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="194"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="172"/>
-      <c r="I21" s="173"/>
-      <c r="J21" s="174"/>
-      <c r="K21" s="173"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="172"/>
-      <c r="N21" s="173"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="172"/>
-      <c r="Q21" s="173"/>
+      <c r="A21" s="171"/>
+      <c r="B21" s="172"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="178"/>
+      <c r="I21" s="172"/>
+      <c r="J21" s="188"/>
+      <c r="K21" s="172"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="178"/>
+      <c r="N21" s="172"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="178"/>
+      <c r="Q21" s="172"/>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
       <c r="T21" s="26"/>
@@ -10677,23 +10677,23 @@
       <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="48" customHeight="1">
-      <c r="A22" s="193"/>
-      <c r="B22" s="173"/>
-      <c r="C22" s="194"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="194"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="174"/>
-      <c r="H22" s="172"/>
-      <c r="I22" s="173"/>
-      <c r="J22" s="174"/>
-      <c r="K22" s="173"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="172"/>
-      <c r="N22" s="173"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="172"/>
-      <c r="Q22" s="173"/>
+      <c r="A22" s="171"/>
+      <c r="B22" s="172"/>
+      <c r="C22" s="173"/>
+      <c r="D22" s="172"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="172"/>
+      <c r="G22" s="188"/>
+      <c r="H22" s="178"/>
+      <c r="I22" s="172"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="172"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="178"/>
+      <c r="N22" s="172"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="178"/>
+      <c r="Q22" s="172"/>
       <c r="R22" s="25"/>
       <c r="S22" s="25"/>
       <c r="T22" s="26"/>
@@ -10705,23 +10705,23 @@
       <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="48" customHeight="1">
-      <c r="A23" s="193"/>
-      <c r="B23" s="173"/>
-      <c r="C23" s="194"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="173"/>
-      <c r="G23" s="174"/>
-      <c r="H23" s="172"/>
-      <c r="I23" s="173"/>
-      <c r="J23" s="174"/>
-      <c r="K23" s="173"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="172"/>
-      <c r="N23" s="173"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="172"/>
-      <c r="Q23" s="173"/>
+      <c r="A23" s="171"/>
+      <c r="B23" s="172"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="172"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="172"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="178"/>
+      <c r="I23" s="172"/>
+      <c r="J23" s="188"/>
+      <c r="K23" s="172"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="178"/>
+      <c r="N23" s="172"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="178"/>
+      <c r="Q23" s="172"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
       <c r="T23" s="26"/>
@@ -10733,23 +10733,23 @@
       <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="48" customHeight="1">
-      <c r="A24" s="193"/>
-      <c r="B24" s="173"/>
-      <c r="C24" s="194"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="194"/>
-      <c r="F24" s="173"/>
-      <c r="G24" s="174"/>
-      <c r="H24" s="172"/>
-      <c r="I24" s="173"/>
-      <c r="J24" s="174"/>
-      <c r="K24" s="173"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="172"/>
-      <c r="N24" s="173"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="172"/>
-      <c r="Q24" s="173"/>
+      <c r="A24" s="171"/>
+      <c r="B24" s="172"/>
+      <c r="C24" s="173"/>
+      <c r="D24" s="172"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="188"/>
+      <c r="H24" s="178"/>
+      <c r="I24" s="172"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="172"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="178"/>
+      <c r="N24" s="172"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="178"/>
+      <c r="Q24" s="172"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
       <c r="T24" s="26"/>
@@ -10761,23 +10761,23 @@
       <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="48" customHeight="1">
-      <c r="A25" s="193"/>
-      <c r="B25" s="173"/>
-      <c r="C25" s="194"/>
-      <c r="D25" s="173"/>
-      <c r="E25" s="194"/>
-      <c r="F25" s="173"/>
-      <c r="G25" s="174"/>
-      <c r="H25" s="172"/>
-      <c r="I25" s="173"/>
-      <c r="J25" s="174"/>
-      <c r="K25" s="173"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="172"/>
-      <c r="N25" s="173"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="172"/>
-      <c r="Q25" s="173"/>
+      <c r="A25" s="171"/>
+      <c r="B25" s="172"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="172"/>
+      <c r="G25" s="188"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="172"/>
+      <c r="J25" s="188"/>
+      <c r="K25" s="172"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="178"/>
+      <c r="N25" s="172"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="178"/>
+      <c r="Q25" s="172"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
@@ -10789,23 +10789,23 @@
       <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="48" customHeight="1">
-      <c r="A26" s="193"/>
-      <c r="B26" s="173"/>
-      <c r="C26" s="194"/>
-      <c r="D26" s="173"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="173"/>
-      <c r="G26" s="174"/>
-      <c r="H26" s="172"/>
-      <c r="I26" s="173"/>
-      <c r="J26" s="174"/>
-      <c r="K26" s="173"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="172"/>
-      <c r="N26" s="173"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="172"/>
-      <c r="Q26" s="173"/>
+      <c r="A26" s="171"/>
+      <c r="B26" s="172"/>
+      <c r="C26" s="173"/>
+      <c r="D26" s="172"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="188"/>
+      <c r="H26" s="178"/>
+      <c r="I26" s="172"/>
+      <c r="J26" s="188"/>
+      <c r="K26" s="172"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="178"/>
+      <c r="N26" s="172"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="178"/>
+      <c r="Q26" s="172"/>
       <c r="R26" s="25"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -10817,23 +10817,23 @@
       <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="48" customHeight="1">
-      <c r="A27" s="193"/>
-      <c r="B27" s="173"/>
-      <c r="C27" s="194"/>
-      <c r="D27" s="173"/>
-      <c r="E27" s="194"/>
-      <c r="F27" s="173"/>
-      <c r="G27" s="174"/>
-      <c r="H27" s="172"/>
-      <c r="I27" s="173"/>
-      <c r="J27" s="174"/>
-      <c r="K27" s="173"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="172"/>
-      <c r="N27" s="173"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="172"/>
-      <c r="Q27" s="173"/>
+      <c r="A27" s="171"/>
+      <c r="B27" s="172"/>
+      <c r="C27" s="173"/>
+      <c r="D27" s="172"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="172"/>
+      <c r="G27" s="188"/>
+      <c r="H27" s="178"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="178"/>
+      <c r="N27" s="172"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="178"/>
+      <c r="Q27" s="172"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="26"/>
@@ -10845,23 +10845,23 @@
       <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="48" customHeight="1">
-      <c r="A28" s="193"/>
-      <c r="B28" s="173"/>
-      <c r="C28" s="194"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="194"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="174"/>
-      <c r="H28" s="172"/>
-      <c r="I28" s="173"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="173"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="172"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="172"/>
-      <c r="Q28" s="173"/>
+      <c r="A28" s="171"/>
+      <c r="B28" s="172"/>
+      <c r="C28" s="173"/>
+      <c r="D28" s="172"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="172"/>
+      <c r="G28" s="188"/>
+      <c r="H28" s="178"/>
+      <c r="I28" s="172"/>
+      <c r="J28" s="188"/>
+      <c r="K28" s="172"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="178"/>
+      <c r="N28" s="172"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="178"/>
+      <c r="Q28" s="172"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
       <c r="T28" s="26"/>
@@ -10873,23 +10873,23 @@
       <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="48" customHeight="1">
-      <c r="A29" s="193"/>
-      <c r="B29" s="173"/>
-      <c r="C29" s="194"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="194"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="172"/>
-      <c r="I29" s="173"/>
-      <c r="J29" s="174"/>
-      <c r="K29" s="173"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="172"/>
-      <c r="N29" s="173"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="172"/>
-      <c r="Q29" s="173"/>
+      <c r="A29" s="171"/>
+      <c r="B29" s="172"/>
+      <c r="C29" s="173"/>
+      <c r="D29" s="172"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="188"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="172"/>
+      <c r="J29" s="188"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="178"/>
+      <c r="N29" s="172"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="178"/>
+      <c r="Q29" s="172"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
       <c r="T29" s="26"/>
@@ -10901,23 +10901,23 @@
       <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="48" customHeight="1">
-      <c r="A30" s="193"/>
-      <c r="B30" s="173"/>
-      <c r="C30" s="194"/>
-      <c r="D30" s="173"/>
-      <c r="E30" s="194"/>
-      <c r="F30" s="173"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="172"/>
-      <c r="I30" s="173"/>
-      <c r="J30" s="174"/>
-      <c r="K30" s="173"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="172"/>
-      <c r="N30" s="173"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="172"/>
-      <c r="Q30" s="173"/>
+      <c r="A30" s="171"/>
+      <c r="B30" s="172"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="188"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="172"/>
+      <c r="J30" s="188"/>
+      <c r="K30" s="172"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="178"/>
+      <c r="N30" s="172"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="178"/>
+      <c r="Q30" s="172"/>
       <c r="R30" s="25"/>
       <c r="S30" s="25"/>
       <c r="T30" s="26"/>
@@ -10929,23 +10929,23 @@
       <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="48" customHeight="1">
-      <c r="A31" s="196"/>
-      <c r="B31" s="177"/>
-      <c r="C31" s="197"/>
-      <c r="D31" s="177"/>
-      <c r="E31" s="197"/>
-      <c r="F31" s="177"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="177"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="177"/>
+      <c r="A31" s="174"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="197"/>
+      <c r="H31" s="180"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="197"/>
+      <c r="K31" s="175"/>
       <c r="L31" s="179"/>
-      <c r="M31" s="176"/>
-      <c r="N31" s="177"/>
+      <c r="M31" s="180"/>
+      <c r="N31" s="175"/>
       <c r="O31" s="179"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="177"/>
+      <c r="P31" s="180"/>
+      <c r="Q31" s="175"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="29"/>
@@ -11943,6 +11943,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11967,118 +12079,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果物_TasBo_編集.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_編集.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER121\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F132AAF-6A7C-4966-844F-AD855B69FC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C101BBF7-54B4-41BB-BB9C-48070C0915A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="9" r:id="rId1"/>
@@ -19,7 +19,16 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="7" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="10" r:id="rId7"/>
+    <sheet name="カバレッジレポート　一覧表示" sheetId="11" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="範囲１" localSheetId="6">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="146">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -563,6 +572,238 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>TaskBoy(TasBo)</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>畠山</t>
+    <rPh sb="0" eb="2">
+      <t>ハタケヤマ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク一覧表示機能</t>
+    <rPh sb="3" eb="9">
+      <t>イチランヒョウジキノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>TaskDAO.java</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カバレッジレポート</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>（１）概要</t>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>対象クラス</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>TaskDAO.java</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>カバレッジ率</t>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>（２）報告事項</t>
+    <rPh sb="3" eb="5">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>調査結果</t>
+    <rPh sb="0" eb="2">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>分析・考察</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウサツ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>備　考</t>
+    <rPh sb="0" eb="1">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>alter(TaskBean task)</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>正しくタスクが編集できることを確認する。</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
 </sst>
 </file>
 
@@ -571,7 +812,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -646,8 +887,95 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -660,8 +988,20 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="73">
+  <borders count="92">
     <border>
       <left/>
       <right/>
@@ -1519,12 +1859,244 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1669,6 +2241,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1679,11 +2284,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1699,9 +2352,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1756,84 +2406,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1918,16 +2490,109 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1945,184 +2610,305 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="75" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="74" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="75" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="74" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="76" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="76" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="73" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="77" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="74" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="75" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="78" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="78" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="78" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="79" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="56" fontId="15" fillId="0" borderId="78" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="79" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="83" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="82" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="83" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="83" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="86" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="86" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="64" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="75" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="74" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="75" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="74" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="87" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="88" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="89" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="76" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="90" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="86" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="91" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{336D8449-DF56-4652-8247-ECBED917399C}"/>
+    <cellStyle name="標準 4" xfId="4" xr:uid="{D9353DA9-51A1-482B-A368-11103D361241}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="2" xr:uid="{3776BDF2-FD86-4C37-AEEE-DC65C95DDA36}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="3" xr:uid="{33F447B7-57F7-4CF2-BFA4-616B62B5FFF8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2970,6 +3756,129 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>128331</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10001763" cy="2152649"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ED4B830-FA72-4A02-909D-70A62562D99B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="328356" y="11458575"/>
+          <a:ext cx="10001763" cy="2152649"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>218145</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10582275" cy="3602311"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB70203-790F-4055-92E3-0B78EFB3E8EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525" y="3389970"/>
+          <a:ext cx="10582275" cy="3602311"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="表紙 "/>
+      <sheetName val="ユースケース記述 "/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="詳細クラス図"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="カバレッジレポート　一覧表示"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3196,67 +4105,67 @@
       <c r="P2" s="45"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="92"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="45"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="92"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="92"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="45"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="45"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="45"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3279,14 +4188,14 @@
       <c r="E8" s="107" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3296,30 +4205,30 @@
       <c r="G13" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
+      <c r="H13" s="61"/>
       <c r="I13" s="108">
         <v>46197</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="61"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="50"/>
+      <c r="H14" s="61"/>
       <c r="I14" s="108">
         <v>46198</v>
       </c>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="103"/>
-      <c r="H15" s="50"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="103"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="47"/>
@@ -3331,10 +4240,10 @@
       <c r="G17" s="104" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4349,19 +5258,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="85"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="85"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
@@ -4373,204 +5282,204 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="91"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="98" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="99"/>
-      <c r="F2" s="98" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="99"/>
-      <c r="H2" s="102">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>46196</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="80"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="81"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="82"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="86" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="87"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="52"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="50.25" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="52"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="176.25" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="51" t="s">
+      <c r="C9" s="90"/>
+      <c r="D9" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="66"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="152.25" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="67" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="71" t="s">
+      <c r="C10" s="94"/>
+      <c r="D10" s="97" t="s">
         <v>113</v>
       </c>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="73"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="99"/>
     </row>
     <row r="11" spans="1:10" ht="385.5" customHeight="1">
-      <c r="A11" s="61"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="76"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="102"/>
     </row>
     <row r="12" spans="1:10" ht="65.25" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="51" t="s">
+      <c r="C12" s="61"/>
+      <c r="D12" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="52"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="52"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="63"/>
     </row>
     <row r="14" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="57"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="84"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5561,18 +6470,6 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="A14:C14"/>
@@ -5588,6 +6485,18 @@
     <mergeCell ref="D10:J11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:J12"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8438,19 +9347,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="161"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="144"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="161"/>
+      <c r="G1" s="144"/>
       <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
@@ -8462,67 +9371,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="155"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="98" t="s">
+      <c r="A2" s="138"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="162"/>
-      <c r="F2" s="98" t="s">
+      <c r="E2" s="145"/>
+      <c r="F2" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="162"/>
-      <c r="H2" s="164">
+      <c r="G2" s="145"/>
+      <c r="H2" s="147">
         <v>46196</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="80"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="155"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="165"/>
-      <c r="I3" s="165"/>
-      <c r="J3" s="166"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="149"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="155"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="166"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="149"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="150" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="161"/>
-      <c r="D5" s="169" t="s">
+      <c r="B5" s="151"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="170"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="153"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="150" t="s">
+      <c r="A6" s="131" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="132"/>
@@ -8533,94 +9442,94 @@
       <c r="G6" s="132"/>
       <c r="H6" s="132"/>
       <c r="I6" s="132"/>
-      <c r="J6" s="134"/>
+      <c r="J6" s="133"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="152"/>
-      <c r="B7" s="153"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="154"/>
+      <c r="A7" s="135"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="137"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="155"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="156"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="139"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="155"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="156"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="139"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="155"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="156"/>
+      <c r="A10" s="138"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="139"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="155"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="156"/>
+      <c r="A11" s="138"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="139"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="155"/>
-      <c r="B12" s="92"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="156"/>
+      <c r="A12" s="138"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="139"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="155"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="92"/>
-      <c r="H13" s="92"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="156"/>
+      <c r="A13" s="138"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="139"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="131" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="132"/>
@@ -8631,21 +9540,21 @@
       <c r="G14" s="132"/>
       <c r="H14" s="132"/>
       <c r="I14" s="132"/>
-      <c r="J14" s="134"/>
+      <c r="J14" s="133"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="150" t="s">
+      <c r="A15" s="131" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="132"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="58" t="s">
+      <c r="C15" s="134"/>
+      <c r="D15" s="62" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="132"/>
       <c r="F15" s="132"/>
       <c r="G15" s="132"/>
-      <c r="H15" s="133"/>
+      <c r="H15" s="134"/>
       <c r="I15" s="34" t="s">
         <v>25</v>
       </c>
@@ -8654,11 +9563,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="150" t="s">
+      <c r="A16" s="131" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="132"/>
-      <c r="C16" s="133"/>
+      <c r="C16" s="134"/>
       <c r="D16" s="34" t="s">
         <v>27</v>
       </c>
@@ -8671,18 +9580,18 @@
       <c r="G16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="151" t="s">
+      <c r="H16" s="154" t="s">
         <v>66</v>
       </c>
       <c r="I16" s="132"/>
-      <c r="J16" s="134"/>
+      <c r="J16" s="133"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="131">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
       <c r="B17" s="132"/>
-      <c r="C17" s="133"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="36" t="s">
         <v>73</v>
       </c>
@@ -8695,16 +9604,16 @@
       <c r="G17" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="58"/>
+      <c r="H17" s="62"/>
       <c r="I17" s="132"/>
-      <c r="J17" s="134"/>
+      <c r="J17" s="133"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="131">
+      <c r="A18" s="155">
         <v>2</v>
       </c>
       <c r="B18" s="132"/>
-      <c r="C18" s="133"/>
+      <c r="C18" s="134"/>
       <c r="D18" s="36" t="s">
         <v>75</v>
       </c>
@@ -8717,16 +9626,16 @@
       <c r="G18" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="H18" s="58"/>
+      <c r="H18" s="62"/>
       <c r="I18" s="132"/>
-      <c r="J18" s="134"/>
+      <c r="J18" s="133"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="131">
+      <c r="A19" s="155">
         <v>3</v>
       </c>
       <c r="B19" s="132"/>
-      <c r="C19" s="133"/>
+      <c r="C19" s="134"/>
       <c r="D19" s="36" t="s">
         <v>74</v>
       </c>
@@ -8739,16 +9648,16 @@
       <c r="G19" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="58"/>
+      <c r="H19" s="62"/>
       <c r="I19" s="132"/>
-      <c r="J19" s="134"/>
+      <c r="J19" s="133"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="131">
+      <c r="A20" s="155">
         <v>4</v>
       </c>
       <c r="B20" s="132"/>
-      <c r="C20" s="133"/>
+      <c r="C20" s="134"/>
       <c r="D20" s="36" t="s">
         <v>76</v>
       </c>
@@ -8761,16 +9670,16 @@
       <c r="G20" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="62"/>
       <c r="I20" s="132"/>
-      <c r="J20" s="134"/>
+      <c r="J20" s="133"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="131">
+      <c r="A21" s="155">
         <v>5</v>
       </c>
       <c r="B21" s="132"/>
-      <c r="C21" s="133"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="36" t="s">
         <v>77</v>
       </c>
@@ -8783,16 +9692,16 @@
       <c r="G21" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="58"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="132"/>
-      <c r="J21" s="134"/>
+      <c r="J21" s="133"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="131">
+      <c r="A22" s="155">
         <v>6</v>
       </c>
       <c r="B22" s="132"/>
-      <c r="C22" s="133"/>
+      <c r="C22" s="134"/>
       <c r="D22" s="36" t="s">
         <v>78</v>
       </c>
@@ -8805,16 +9714,16 @@
       <c r="G22" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="H22" s="58"/>
+      <c r="H22" s="62"/>
       <c r="I22" s="132"/>
-      <c r="J22" s="134"/>
+      <c r="J22" s="133"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="145">
+      <c r="A23" s="156">
         <v>8</v>
       </c>
-      <c r="B23" s="146"/>
-      <c r="C23" s="147"/>
+      <c r="B23" s="157"/>
+      <c r="C23" s="158"/>
       <c r="D23" s="38" t="s">
         <v>91</v>
       </c>
@@ -8827,16 +9736,16 @@
       <c r="G23" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="H23" s="148"/>
-      <c r="I23" s="146"/>
-      <c r="J23" s="149"/>
+      <c r="H23" s="159"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="160"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="140">
+      <c r="A24" s="161">
         <v>9</v>
       </c>
-      <c r="B24" s="141"/>
-      <c r="C24" s="142"/>
+      <c r="B24" s="162"/>
+      <c r="C24" s="163"/>
       <c r="D24" s="40" t="s">
         <v>67</v>
       </c>
@@ -8849,12 +9758,12 @@
       <c r="G24" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="H24" s="143"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="144"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="165"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="150" t="s">
+      <c r="A25" s="131" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="132"/>
@@ -8865,21 +9774,21 @@
       <c r="G25" s="132"/>
       <c r="H25" s="132"/>
       <c r="I25" s="132"/>
-      <c r="J25" s="134"/>
+      <c r="J25" s="133"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="150" t="s">
+      <c r="A26" s="131" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="132"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="58" t="s">
+      <c r="C26" s="134"/>
+      <c r="D26" s="62" t="s">
         <v>72</v>
       </c>
       <c r="E26" s="132"/>
       <c r="F26" s="132"/>
       <c r="G26" s="132"/>
-      <c r="H26" s="133"/>
+      <c r="H26" s="134"/>
       <c r="I26" s="34" t="s">
         <v>25</v>
       </c>
@@ -8888,11 +9797,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="150" t="s">
+      <c r="A27" s="131" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="132"/>
-      <c r="C27" s="133"/>
+      <c r="C27" s="134"/>
       <c r="D27" s="34" t="s">
         <v>27</v>
       </c>
@@ -8905,18 +9814,18 @@
       <c r="G27" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="151" t="s">
+      <c r="H27" s="154" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="132"/>
-      <c r="J27" s="134"/>
+      <c r="J27" s="133"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="131">
+      <c r="A28" s="155">
         <v>7</v>
       </c>
       <c r="B28" s="132"/>
-      <c r="C28" s="133"/>
+      <c r="C28" s="134"/>
       <c r="D28" s="36" t="s">
         <v>79</v>
       </c>
@@ -8929,92 +9838,92 @@
       <c r="G28" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="58"/>
+      <c r="H28" s="62"/>
       <c r="I28" s="132"/>
-      <c r="J28" s="134"/>
+      <c r="J28" s="133"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="131"/>
+      <c r="A29" s="155"/>
       <c r="B29" s="132"/>
-      <c r="C29" s="133"/>
+      <c r="C29" s="134"/>
       <c r="D29" s="36"/>
       <c r="E29" s="36"/>
       <c r="F29" s="36"/>
       <c r="G29" s="36"/>
-      <c r="H29" s="58"/>
+      <c r="H29" s="62"/>
       <c r="I29" s="132"/>
-      <c r="J29" s="134"/>
+      <c r="J29" s="133"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="131"/>
+      <c r="A30" s="155"/>
       <c r="B30" s="132"/>
-      <c r="C30" s="133"/>
+      <c r="C30" s="134"/>
       <c r="E30" s="36"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="58"/>
+      <c r="H30" s="62"/>
       <c r="I30" s="132"/>
-      <c r="J30" s="134"/>
+      <c r="J30" s="133"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="131"/>
+      <c r="A31" s="155"/>
       <c r="B31" s="132"/>
-      <c r="C31" s="133"/>
+      <c r="C31" s="134"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="58"/>
+      <c r="H31" s="62"/>
       <c r="I31" s="132"/>
-      <c r="J31" s="134"/>
+      <c r="J31" s="133"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="131"/>
+      <c r="A32" s="155"/>
       <c r="B32" s="132"/>
-      <c r="C32" s="133"/>
+      <c r="C32" s="134"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="58"/>
+      <c r="H32" s="62"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="134"/>
+      <c r="J32" s="133"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="145"/>
-      <c r="B33" s="146"/>
-      <c r="C33" s="147"/>
+      <c r="A33" s="156"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="158"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39"/>
-      <c r="H33" s="148"/>
-      <c r="I33" s="146"/>
-      <c r="J33" s="149"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="157"/>
+      <c r="J33" s="160"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="135"/>
-      <c r="B34" s="136"/>
-      <c r="C34" s="137"/>
+      <c r="A34" s="166"/>
+      <c r="B34" s="167"/>
+      <c r="C34" s="168"/>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="139"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="170"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A35" s="140"/>
-      <c r="B35" s="141"/>
-      <c r="C35" s="142"/>
+      <c r="A35" s="161"/>
+      <c r="B35" s="162"/>
+      <c r="C35" s="163"/>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="143"/>
-      <c r="I35" s="141"/>
-      <c r="J35" s="144"/>
+      <c r="H35" s="164"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="165"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9984,27 +10893,23 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
@@ -10021,23 +10926,27 @@
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10057,7 +10966,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="185" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="116"/>
@@ -10068,14 +10977,14 @@
       <c r="G1" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
       <c r="J1" s="125"/>
       <c r="K1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
+      <c r="L1" s="186"/>
+      <c r="M1" s="186"/>
       <c r="N1" s="125"/>
       <c r="O1" s="124" t="s">
         <v>5</v>
@@ -10088,7 +10997,7 @@
       <c r="S1" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="184"/>
+      <c r="T1" s="187"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="118"/>
@@ -10100,16 +11009,16 @@
       <c r="G2" s="126" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
       <c r="J2" s="127"/>
       <c r="K2" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="191"/>
-      <c r="M2" s="191"/>
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
       <c r="N2" s="127"/>
-      <c r="O2" s="192">
+      <c r="O2" s="181">
         <v>46182</v>
       </c>
       <c r="P2" s="127"/>
@@ -10118,7 +11027,7 @@
       </c>
       <c r="R2" s="127"/>
       <c r="S2" s="126"/>
-      <c r="T2" s="193"/>
+      <c r="T2" s="182"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="118"/>
@@ -10140,7 +11049,7 @@
       <c r="Q3" s="128"/>
       <c r="R3" s="120"/>
       <c r="S3" s="128"/>
-      <c r="T3" s="194"/>
+      <c r="T3" s="183"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="121"/>
@@ -10162,85 +11071,85 @@
       <c r="Q4" s="129"/>
       <c r="R4" s="123"/>
       <c r="S4" s="129"/>
-      <c r="T4" s="195"/>
+      <c r="T4" s="184"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="181" t="s">
+      <c r="A5" s="188" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
       <c r="F5" s="125"/>
-      <c r="G5" s="183" t="s">
+      <c r="G5" s="189" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="182"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="182"/>
-      <c r="Q5" s="182"/>
-      <c r="R5" s="182"/>
-      <c r="S5" s="182"/>
-      <c r="T5" s="184"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="186"/>
+      <c r="N5" s="186"/>
+      <c r="O5" s="186"/>
+      <c r="P5" s="186"/>
+      <c r="Q5" s="186"/>
+      <c r="R5" s="186"/>
+      <c r="S5" s="186"/>
+      <c r="T5" s="187"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="185" t="s">
+      <c r="A6" s="190" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="178"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="186" t="s">
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="191" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="178"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="178"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="178"/>
-      <c r="N6" s="178"/>
-      <c r="O6" s="178"/>
-      <c r="P6" s="178"/>
-      <c r="Q6" s="178"/>
-      <c r="R6" s="178"/>
-      <c r="S6" s="178"/>
-      <c r="T6" s="187"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="172"/>
+      <c r="L6" s="172"/>
+      <c r="M6" s="172"/>
+      <c r="N6" s="172"/>
+      <c r="O6" s="172"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="172"/>
+      <c r="T6" s="192"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="185" t="s">
+      <c r="A7" s="190" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="178"/>
-      <c r="C7" s="178"/>
-      <c r="D7" s="178"/>
-      <c r="E7" s="178"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="186" t="s">
+      <c r="B7" s="172"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="178"/>
-      <c r="I7" s="178"/>
-      <c r="J7" s="178"/>
-      <c r="K7" s="178"/>
-      <c r="L7" s="178"/>
-      <c r="M7" s="178"/>
-      <c r="N7" s="178"/>
-      <c r="O7" s="178"/>
-      <c r="P7" s="178"/>
-      <c r="Q7" s="178"/>
-      <c r="R7" s="178"/>
-      <c r="S7" s="178"/>
-      <c r="T7" s="187"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="172"/>
+      <c r="K7" s="172"/>
+      <c r="L7" s="172"/>
+      <c r="M7" s="172"/>
+      <c r="N7" s="172"/>
+      <c r="O7" s="172"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="172"/>
+      <c r="T7" s="192"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -10439,37 +11348,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="185" t="s">
+      <c r="A15" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="172"/>
-      <c r="C15" s="190" t="s">
+      <c r="B15" s="173"/>
+      <c r="C15" s="195" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="172"/>
-      <c r="E15" s="189" t="s">
+      <c r="D15" s="173"/>
+      <c r="E15" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="172"/>
-      <c r="G15" s="189" t="s">
+      <c r="F15" s="173"/>
+      <c r="G15" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="178"/>
-      <c r="I15" s="172"/>
-      <c r="J15" s="189" t="s">
+      <c r="H15" s="172"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="172"/>
-      <c r="L15" s="189" t="s">
+      <c r="K15" s="173"/>
+      <c r="L15" s="171" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="178"/>
-      <c r="N15" s="172"/>
-      <c r="O15" s="189" t="s">
+      <c r="M15" s="172"/>
+      <c r="N15" s="173"/>
+      <c r="O15" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="178"/>
-      <c r="Q15" s="172"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="173"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -10481,37 +11390,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="171">
+      <c r="A16" s="193">
         <v>1</v>
       </c>
-      <c r="B16" s="172"/>
-      <c r="C16" s="173" t="s">
+      <c r="B16" s="173"/>
+      <c r="C16" s="194" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="172"/>
-      <c r="E16" s="173" t="s">
+      <c r="D16" s="173"/>
+      <c r="E16" s="194" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="172"/>
-      <c r="G16" s="188" t="s">
+      <c r="F16" s="173"/>
+      <c r="G16" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="178"/>
-      <c r="I16" s="172"/>
-      <c r="J16" s="188" t="s">
+      <c r="H16" s="172"/>
+      <c r="I16" s="173"/>
+      <c r="J16" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="172"/>
-      <c r="L16" s="177" t="s">
+      <c r="K16" s="173"/>
+      <c r="L16" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="M16" s="178"/>
-      <c r="N16" s="172"/>
-      <c r="O16" s="177" t="s">
+      <c r="M16" s="172"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="178" t="s">
         <v>55</v>
       </c>
-      <c r="P16" s="178"/>
-      <c r="Q16" s="172"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="173"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
       <c r="T16" s="26"/>
@@ -10523,37 +11432,37 @@
       <c r="Z16" s="27"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="171">
+      <c r="A17" s="193">
         <v>2</v>
       </c>
-      <c r="B17" s="172"/>
-      <c r="C17" s="173" t="s">
+      <c r="B17" s="173"/>
+      <c r="C17" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="172"/>
-      <c r="E17" s="173" t="s">
+      <c r="D17" s="173"/>
+      <c r="E17" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="172"/>
-      <c r="G17" s="188" t="s">
+      <c r="F17" s="173"/>
+      <c r="G17" s="174" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="178"/>
-      <c r="I17" s="172"/>
-      <c r="J17" s="188" t="s">
+      <c r="H17" s="172"/>
+      <c r="I17" s="173"/>
+      <c r="J17" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="K17" s="172"/>
-      <c r="L17" s="177" t="s">
+      <c r="K17" s="173"/>
+      <c r="L17" s="178" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="178"/>
-      <c r="N17" s="172"/>
-      <c r="O17" s="177" t="s">
+      <c r="M17" s="172"/>
+      <c r="N17" s="173"/>
+      <c r="O17" s="178" t="s">
         <v>61</v>
       </c>
-      <c r="P17" s="178"/>
-      <c r="Q17" s="172"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="173"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26"/>
@@ -10565,23 +11474,23 @@
       <c r="Z17" s="27"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="171"/>
-      <c r="B18" s="172"/>
-      <c r="C18" s="173"/>
-      <c r="D18" s="172"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="172"/>
-      <c r="G18" s="188"/>
-      <c r="H18" s="178"/>
-      <c r="I18" s="172"/>
-      <c r="J18" s="188"/>
-      <c r="K18" s="172"/>
-      <c r="L18" s="177"/>
-      <c r="M18" s="178"/>
-      <c r="N18" s="172"/>
-      <c r="O18" s="177"/>
-      <c r="P18" s="178"/>
-      <c r="Q18" s="172"/>
+      <c r="A18" s="193"/>
+      <c r="B18" s="173"/>
+      <c r="C18" s="194"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="174"/>
+      <c r="H18" s="172"/>
+      <c r="I18" s="173"/>
+      <c r="J18" s="174"/>
+      <c r="K18" s="173"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="172"/>
+      <c r="N18" s="173"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="172"/>
+      <c r="Q18" s="173"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
       <c r="T18" s="26"/>
@@ -10593,23 +11502,23 @@
       <c r="Z18" s="27"/>
     </row>
     <row r="19" spans="1:26" ht="48" customHeight="1">
-      <c r="A19" s="171"/>
-      <c r="B19" s="172"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="172"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="172"/>
-      <c r="G19" s="188"/>
-      <c r="H19" s="178"/>
-      <c r="I19" s="172"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="172"/>
-      <c r="L19" s="177"/>
-      <c r="M19" s="178"/>
-      <c r="N19" s="172"/>
-      <c r="O19" s="177"/>
-      <c r="P19" s="178"/>
-      <c r="Q19" s="172"/>
+      <c r="A19" s="193"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="194"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="194"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="172"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="174"/>
+      <c r="K19" s="173"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="172"/>
+      <c r="N19" s="173"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="172"/>
+      <c r="Q19" s="173"/>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
       <c r="T19" s="26"/>
@@ -10621,23 +11530,23 @@
       <c r="Z19" s="27"/>
     </row>
     <row r="20" spans="1:26" ht="48" customHeight="1">
-      <c r="A20" s="171"/>
-      <c r="B20" s="172"/>
-      <c r="C20" s="173"/>
-      <c r="D20" s="172"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="172"/>
-      <c r="G20" s="188"/>
-      <c r="H20" s="178"/>
-      <c r="I20" s="172"/>
-      <c r="J20" s="188"/>
-      <c r="K20" s="172"/>
-      <c r="L20" s="177"/>
-      <c r="M20" s="178"/>
-      <c r="N20" s="172"/>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
-      <c r="Q20" s="172"/>
+      <c r="A20" s="193"/>
+      <c r="B20" s="173"/>
+      <c r="C20" s="194"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="172"/>
+      <c r="I20" s="173"/>
+      <c r="J20" s="174"/>
+      <c r="K20" s="173"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="172"/>
+      <c r="N20" s="173"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="172"/>
+      <c r="Q20" s="173"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="26"/>
@@ -10649,23 +11558,23 @@
       <c r="Z20" s="27"/>
     </row>
     <row r="21" spans="1:26" ht="48" customHeight="1">
-      <c r="A21" s="171"/>
-      <c r="B21" s="172"/>
-      <c r="C21" s="173"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="172"/>
-      <c r="G21" s="188"/>
-      <c r="H21" s="178"/>
-      <c r="I21" s="172"/>
-      <c r="J21" s="188"/>
-      <c r="K21" s="172"/>
-      <c r="L21" s="177"/>
-      <c r="M21" s="178"/>
-      <c r="N21" s="172"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="178"/>
-      <c r="Q21" s="172"/>
+      <c r="A21" s="193"/>
+      <c r="B21" s="173"/>
+      <c r="C21" s="194"/>
+      <c r="D21" s="173"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="172"/>
+      <c r="I21" s="173"/>
+      <c r="J21" s="174"/>
+      <c r="K21" s="173"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="172"/>
+      <c r="N21" s="173"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="172"/>
+      <c r="Q21" s="173"/>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
       <c r="T21" s="26"/>
@@ -10677,23 +11586,23 @@
       <c r="Z21" s="27"/>
     </row>
     <row r="22" spans="1:26" ht="48" customHeight="1">
-      <c r="A22" s="171"/>
-      <c r="B22" s="172"/>
-      <c r="C22" s="173"/>
-      <c r="D22" s="172"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="172"/>
-      <c r="G22" s="188"/>
-      <c r="H22" s="178"/>
-      <c r="I22" s="172"/>
-      <c r="J22" s="188"/>
-      <c r="K22" s="172"/>
-      <c r="L22" s="177"/>
-      <c r="M22" s="178"/>
-      <c r="N22" s="172"/>
-      <c r="O22" s="177"/>
-      <c r="P22" s="178"/>
-      <c r="Q22" s="172"/>
+      <c r="A22" s="193"/>
+      <c r="B22" s="173"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="172"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="173"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="172"/>
+      <c r="N22" s="173"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="172"/>
+      <c r="Q22" s="173"/>
       <c r="R22" s="25"/>
       <c r="S22" s="25"/>
       <c r="T22" s="26"/>
@@ -10705,23 +11614,23 @@
       <c r="Z22" s="27"/>
     </row>
     <row r="23" spans="1:26" ht="48" customHeight="1">
-      <c r="A23" s="171"/>
-      <c r="B23" s="172"/>
-      <c r="C23" s="173"/>
-      <c r="D23" s="172"/>
-      <c r="E23" s="173"/>
-      <c r="F23" s="172"/>
-      <c r="G23" s="188"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="172"/>
-      <c r="J23" s="188"/>
-      <c r="K23" s="172"/>
-      <c r="L23" s="177"/>
-      <c r="M23" s="178"/>
-      <c r="N23" s="172"/>
-      <c r="O23" s="177"/>
-      <c r="P23" s="178"/>
-      <c r="Q23" s="172"/>
+      <c r="A23" s="193"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="174"/>
+      <c r="H23" s="172"/>
+      <c r="I23" s="173"/>
+      <c r="J23" s="174"/>
+      <c r="K23" s="173"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="172"/>
+      <c r="N23" s="173"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="173"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
       <c r="T23" s="26"/>
@@ -10733,23 +11642,23 @@
       <c r="Z23" s="27"/>
     </row>
     <row r="24" spans="1:26" ht="48" customHeight="1">
-      <c r="A24" s="171"/>
-      <c r="B24" s="172"/>
-      <c r="C24" s="173"/>
-      <c r="D24" s="172"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="188"/>
-      <c r="H24" s="178"/>
-      <c r="I24" s="172"/>
-      <c r="J24" s="188"/>
-      <c r="K24" s="172"/>
-      <c r="L24" s="177"/>
-      <c r="M24" s="178"/>
-      <c r="N24" s="172"/>
-      <c r="O24" s="177"/>
-      <c r="P24" s="178"/>
-      <c r="Q24" s="172"/>
+      <c r="A24" s="193"/>
+      <c r="B24" s="173"/>
+      <c r="C24" s="194"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="173"/>
+      <c r="G24" s="174"/>
+      <c r="H24" s="172"/>
+      <c r="I24" s="173"/>
+      <c r="J24" s="174"/>
+      <c r="K24" s="173"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="172"/>
+      <c r="N24" s="173"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
       <c r="T24" s="26"/>
@@ -10761,23 +11670,23 @@
       <c r="Z24" s="27"/>
     </row>
     <row r="25" spans="1:26" ht="48" customHeight="1">
-      <c r="A25" s="171"/>
-      <c r="B25" s="172"/>
-      <c r="C25" s="173"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="173"/>
-      <c r="F25" s="172"/>
-      <c r="G25" s="188"/>
-      <c r="H25" s="178"/>
-      <c r="I25" s="172"/>
-      <c r="J25" s="188"/>
-      <c r="K25" s="172"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="172"/>
-      <c r="O25" s="177"/>
-      <c r="P25" s="178"/>
-      <c r="Q25" s="172"/>
+      <c r="A25" s="193"/>
+      <c r="B25" s="173"/>
+      <c r="C25" s="194"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="194"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="174"/>
+      <c r="H25" s="172"/>
+      <c r="I25" s="173"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="173"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="172"/>
+      <c r="N25" s="173"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="173"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
@@ -10789,23 +11698,23 @@
       <c r="Z25" s="27"/>
     </row>
     <row r="26" spans="1:26" ht="48" customHeight="1">
-      <c r="A26" s="171"/>
-      <c r="B26" s="172"/>
-      <c r="C26" s="173"/>
-      <c r="D26" s="172"/>
-      <c r="E26" s="173"/>
-      <c r="F26" s="172"/>
-      <c r="G26" s="188"/>
-      <c r="H26" s="178"/>
-      <c r="I26" s="172"/>
-      <c r="J26" s="188"/>
-      <c r="K26" s="172"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="178"/>
-      <c r="N26" s="172"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="178"/>
-      <c r="Q26" s="172"/>
+      <c r="A26" s="193"/>
+      <c r="B26" s="173"/>
+      <c r="C26" s="194"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="194"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="174"/>
+      <c r="H26" s="172"/>
+      <c r="I26" s="173"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="173"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="172"/>
+      <c r="N26" s="173"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="172"/>
+      <c r="Q26" s="173"/>
       <c r="R26" s="25"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -10817,23 +11726,23 @@
       <c r="Z26" s="27"/>
     </row>
     <row r="27" spans="1:26" ht="48" customHeight="1">
-      <c r="A27" s="171"/>
-      <c r="B27" s="172"/>
-      <c r="C27" s="173"/>
-      <c r="D27" s="172"/>
-      <c r="E27" s="173"/>
-      <c r="F27" s="172"/>
-      <c r="G27" s="188"/>
-      <c r="H27" s="178"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="188"/>
-      <c r="K27" s="172"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="178"/>
-      <c r="N27" s="172"/>
-      <c r="O27" s="177"/>
-      <c r="P27" s="178"/>
-      <c r="Q27" s="172"/>
+      <c r="A27" s="193"/>
+      <c r="B27" s="173"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="173"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="173"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="173"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="172"/>
+      <c r="Q27" s="173"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="26"/>
@@ -10845,23 +11754,23 @@
       <c r="Z27" s="27"/>
     </row>
     <row r="28" spans="1:26" ht="48" customHeight="1">
-      <c r="A28" s="171"/>
-      <c r="B28" s="172"/>
-      <c r="C28" s="173"/>
-      <c r="D28" s="172"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="172"/>
-      <c r="G28" s="188"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="172"/>
-      <c r="J28" s="188"/>
-      <c r="K28" s="172"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="178"/>
-      <c r="N28" s="172"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="178"/>
-      <c r="Q28" s="172"/>
+      <c r="A28" s="193"/>
+      <c r="B28" s="173"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="194"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="172"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="172"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="172"/>
+      <c r="Q28" s="173"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
       <c r="T28" s="26"/>
@@ -10873,23 +11782,23 @@
       <c r="Z28" s="27"/>
     </row>
     <row r="29" spans="1:26" ht="48" customHeight="1">
-      <c r="A29" s="171"/>
-      <c r="B29" s="172"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="172"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="172"/>
-      <c r="G29" s="188"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="172"/>
-      <c r="J29" s="188"/>
-      <c r="K29" s="172"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="178"/>
-      <c r="N29" s="172"/>
-      <c r="O29" s="177"/>
-      <c r="P29" s="178"/>
-      <c r="Q29" s="172"/>
+      <c r="A29" s="193"/>
+      <c r="B29" s="173"/>
+      <c r="C29" s="194"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="173"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="173"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="172"/>
+      <c r="Q29" s="173"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
       <c r="T29" s="26"/>
@@ -10901,23 +11810,23 @@
       <c r="Z29" s="27"/>
     </row>
     <row r="30" spans="1:26" ht="48" customHeight="1">
-      <c r="A30" s="171"/>
-      <c r="B30" s="172"/>
-      <c r="C30" s="173"/>
-      <c r="D30" s="172"/>
-      <c r="E30" s="173"/>
-      <c r="F30" s="172"/>
-      <c r="G30" s="188"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="172"/>
-      <c r="J30" s="188"/>
-      <c r="K30" s="172"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="178"/>
-      <c r="N30" s="172"/>
-      <c r="O30" s="177"/>
-      <c r="P30" s="178"/>
-      <c r="Q30" s="172"/>
+      <c r="A30" s="193"/>
+      <c r="B30" s="173"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="172"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="172"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
       <c r="R30" s="25"/>
       <c r="S30" s="25"/>
       <c r="T30" s="26"/>
@@ -10929,23 +11838,23 @@
       <c r="Z30" s="27"/>
     </row>
     <row r="31" spans="1:26" ht="48" customHeight="1">
-      <c r="A31" s="174"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="197"/>
-      <c r="H31" s="180"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="197"/>
-      <c r="K31" s="175"/>
+      <c r="A31" s="196"/>
+      <c r="B31" s="177"/>
+      <c r="C31" s="197"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="197"/>
+      <c r="F31" s="177"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="177"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="177"/>
       <c r="L31" s="179"/>
-      <c r="M31" s="180"/>
-      <c r="N31" s="175"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="177"/>
       <c r="O31" s="179"/>
-      <c r="P31" s="180"/>
-      <c r="Q31" s="175"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="177"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="29"/>
@@ -11943,62 +12852,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12023,65 +12932,3581 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102B4EF4-ABA0-40CB-8D0A-015A0983E6C1}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="206" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="241" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="206" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="241" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="206" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="206" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="206"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="198" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="198"/>
+      <c r="C1" s="199" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="200"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="202" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="205" t="s">
+        <v>117</v>
+      </c>
+      <c r="O1" s="202" t="s">
+        <v>118</v>
+      </c>
+      <c r="P1" s="204"/>
+      <c r="Q1" s="205" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" s="202" t="s">
+        <v>120</v>
+      </c>
+      <c r="S1" s="204"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="198"/>
+      <c r="B2" s="198"/>
+      <c r="C2" s="199" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="200"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="202" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="203"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="203"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="205" t="s">
+        <v>123</v>
+      </c>
+      <c r="O2" s="207">
+        <v>46199</v>
+      </c>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="209" t="s">
+        <v>124</v>
+      </c>
+      <c r="R2" s="210" t="s">
+        <v>118</v>
+      </c>
+      <c r="S2" s="211"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="212"/>
+      <c r="B3" s="213"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="212"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="214" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="215" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="216" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="216" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4" s="217"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="217"/>
+      <c r="L4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="216" t="s">
+        <v>129</v>
+      </c>
+      <c r="O4" s="217"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="214" t="s">
+        <v>130</v>
+      </c>
+      <c r="R4" s="216" t="s">
+        <v>131</v>
+      </c>
+      <c r="S4" s="218"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="219">
+        <v>1</v>
+      </c>
+      <c r="B5" s="220" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="221" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="221"/>
+      <c r="E5" s="221"/>
+      <c r="F5" s="221"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="221" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="221"/>
+      <c r="J5" s="221"/>
+      <c r="K5" s="221"/>
+      <c r="L5" s="221"/>
+      <c r="M5" s="221"/>
+      <c r="N5" s="222" t="s">
+        <v>145</v>
+      </c>
+      <c r="O5" s="223"/>
+      <c r="P5" s="224"/>
+      <c r="Q5" s="225">
+        <v>46199</v>
+      </c>
+      <c r="R5" s="226"/>
+      <c r="S5" s="227"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="228"/>
+      <c r="B6" s="228"/>
+      <c r="C6" s="229"/>
+      <c r="D6" s="229"/>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="229"/>
+      <c r="I6" s="229"/>
+      <c r="J6" s="229"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="229"/>
+      <c r="M6" s="229"/>
+      <c r="N6" s="230"/>
+      <c r="O6" s="231"/>
+      <c r="P6" s="232"/>
+      <c r="Q6" s="233"/>
+      <c r="R6" s="234"/>
+      <c r="S6" s="234"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="228"/>
+      <c r="B7" s="228"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="229"/>
+      <c r="I7" s="229"/>
+      <c r="J7" s="229"/>
+      <c r="K7" s="229"/>
+      <c r="L7" s="229"/>
+      <c r="M7" s="229"/>
+      <c r="N7" s="235"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="237"/>
+      <c r="Q7" s="233"/>
+      <c r="R7" s="234"/>
+      <c r="S7" s="234"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="228"/>
+      <c r="B8" s="228"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="235"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="237"/>
+      <c r="Q8" s="233"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="234"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="228"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="235"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="237"/>
+      <c r="Q9" s="228"/>
+      <c r="R9" s="234"/>
+      <c r="S9" s="234"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="228"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="229"/>
+      <c r="F10" s="229"/>
+      <c r="G10" s="229"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="240"/>
+      <c r="N10" s="235"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="237"/>
+      <c r="Q10" s="233"/>
+      <c r="R10" s="234"/>
+      <c r="S10" s="234"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="228"/>
+      <c r="B11" s="228"/>
+      <c r="C11" s="229"/>
+      <c r="D11" s="229"/>
+      <c r="E11" s="229"/>
+      <c r="F11" s="229"/>
+      <c r="G11" s="229"/>
+      <c r="H11" s="238"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="240"/>
+      <c r="N11" s="235"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="237"/>
+      <c r="Q11" s="228"/>
+      <c r="R11" s="234"/>
+      <c r="S11" s="234"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="228"/>
+      <c r="B12" s="228"/>
+      <c r="C12" s="229"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="229"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="229"/>
+      <c r="H12" s="238"/>
+      <c r="I12" s="239"/>
+      <c r="J12" s="239"/>
+      <c r="K12" s="239"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="240"/>
+      <c r="N12" s="235"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="237"/>
+      <c r="Q12" s="228"/>
+      <c r="R12" s="234"/>
+      <c r="S12" s="234"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="228"/>
+      <c r="B13" s="228"/>
+      <c r="C13" s="229"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="229"/>
+      <c r="F13" s="229"/>
+      <c r="G13" s="229"/>
+      <c r="H13" s="238"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
+      <c r="M13" s="240"/>
+      <c r="N13" s="235"/>
+      <c r="O13" s="236"/>
+      <c r="P13" s="237"/>
+      <c r="Q13" s="228"/>
+      <c r="R13" s="234"/>
+      <c r="S13" s="234"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="228"/>
+      <c r="B14" s="228"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="239"/>
+      <c r="J14" s="239"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
+      <c r="M14" s="240"/>
+      <c r="N14" s="235"/>
+      <c r="O14" s="236"/>
+      <c r="P14" s="237"/>
+      <c r="Q14" s="228"/>
+      <c r="R14" s="234"/>
+      <c r="S14" s="234"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="228"/>
+      <c r="B15" s="228"/>
+      <c r="C15" s="229"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
+      <c r="F15" s="229"/>
+      <c r="G15" s="229"/>
+      <c r="H15" s="238"/>
+      <c r="I15" s="239"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="239"/>
+      <c r="L15" s="239"/>
+      <c r="M15" s="240"/>
+      <c r="N15" s="235"/>
+      <c r="O15" s="236"/>
+      <c r="P15" s="237"/>
+      <c r="Q15" s="228"/>
+      <c r="R15" s="234"/>
+      <c r="S15" s="234"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="228"/>
+      <c r="B16" s="228"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="229"/>
+      <c r="E16" s="229"/>
+      <c r="F16" s="229"/>
+      <c r="G16" s="229"/>
+      <c r="H16" s="238"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="240"/>
+      <c r="N16" s="235"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="237"/>
+      <c r="Q16" s="228"/>
+      <c r="R16" s="234"/>
+      <c r="S16" s="234"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="228"/>
+      <c r="B17" s="228"/>
+      <c r="C17" s="229"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="229"/>
+      <c r="G17" s="229"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="239"/>
+      <c r="M17" s="240"/>
+      <c r="N17" s="235"/>
+      <c r="O17" s="236"/>
+      <c r="P17" s="237"/>
+      <c r="Q17" s="228"/>
+      <c r="R17" s="234"/>
+      <c r="S17" s="234"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="228"/>
+      <c r="B18" s="228"/>
+      <c r="C18" s="229"/>
+      <c r="D18" s="229"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="229"/>
+      <c r="G18" s="229"/>
+      <c r="H18" s="238"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
+      <c r="M18" s="240"/>
+      <c r="N18" s="235"/>
+      <c r="O18" s="236"/>
+      <c r="P18" s="237"/>
+      <c r="Q18" s="228"/>
+      <c r="R18" s="234"/>
+      <c r="S18" s="234"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="228"/>
+      <c r="B19" s="228"/>
+      <c r="C19" s="229"/>
+      <c r="D19" s="229"/>
+      <c r="E19" s="229"/>
+      <c r="F19" s="229"/>
+      <c r="G19" s="229"/>
+      <c r="H19" s="238"/>
+      <c r="I19" s="239"/>
+      <c r="J19" s="239"/>
+      <c r="K19" s="239"/>
+      <c r="L19" s="239"/>
+      <c r="M19" s="240"/>
+      <c r="N19" s="235"/>
+      <c r="O19" s="236"/>
+      <c r="P19" s="237"/>
+      <c r="Q19" s="228"/>
+      <c r="R19" s="234"/>
+      <c r="S19" s="234"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="228"/>
+      <c r="B20" s="228"/>
+      <c r="C20" s="229"/>
+      <c r="D20" s="229"/>
+      <c r="E20" s="229"/>
+      <c r="F20" s="229"/>
+      <c r="G20" s="229"/>
+      <c r="H20" s="238"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="239"/>
+      <c r="K20" s="239"/>
+      <c r="L20" s="239"/>
+      <c r="M20" s="240"/>
+      <c r="N20" s="235"/>
+      <c r="O20" s="236"/>
+      <c r="P20" s="237"/>
+      <c r="Q20" s="228"/>
+      <c r="R20" s="234"/>
+      <c r="S20" s="234"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="228"/>
+      <c r="B21" s="228"/>
+      <c r="C21" s="229"/>
+      <c r="D21" s="229"/>
+      <c r="E21" s="229"/>
+      <c r="F21" s="229"/>
+      <c r="G21" s="229"/>
+      <c r="H21" s="238"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
+      <c r="M21" s="240"/>
+      <c r="N21" s="235"/>
+      <c r="O21" s="236"/>
+      <c r="P21" s="237"/>
+      <c r="Q21" s="228"/>
+      <c r="R21" s="234"/>
+      <c r="S21" s="234"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="228"/>
+      <c r="B22" s="228"/>
+      <c r="C22" s="229"/>
+      <c r="D22" s="229"/>
+      <c r="E22" s="229"/>
+      <c r="F22" s="229"/>
+      <c r="G22" s="229"/>
+      <c r="H22" s="238"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="239"/>
+      <c r="M22" s="240"/>
+      <c r="N22" s="235"/>
+      <c r="O22" s="236"/>
+      <c r="P22" s="237"/>
+      <c r="Q22" s="228"/>
+      <c r="R22" s="234"/>
+      <c r="S22" s="234"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="228"/>
+      <c r="B23" s="228"/>
+      <c r="C23" s="229"/>
+      <c r="D23" s="229"/>
+      <c r="E23" s="229"/>
+      <c r="F23" s="229"/>
+      <c r="G23" s="229"/>
+      <c r="H23" s="238"/>
+      <c r="I23" s="239"/>
+      <c r="J23" s="239"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="239"/>
+      <c r="M23" s="240"/>
+      <c r="N23" s="235"/>
+      <c r="O23" s="236"/>
+      <c r="P23" s="237"/>
+      <c r="Q23" s="228"/>
+      <c r="R23" s="234"/>
+      <c r="S23" s="234"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="228"/>
+      <c r="B24" s="228"/>
+      <c r="C24" s="229"/>
+      <c r="D24" s="229"/>
+      <c r="E24" s="229"/>
+      <c r="F24" s="229"/>
+      <c r="G24" s="229"/>
+      <c r="H24" s="238"/>
+      <c r="I24" s="239"/>
+      <c r="J24" s="239"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="239"/>
+      <c r="M24" s="240"/>
+      <c r="N24" s="235"/>
+      <c r="O24" s="236"/>
+      <c r="P24" s="237"/>
+      <c r="Q24" s="228"/>
+      <c r="R24" s="234"/>
+      <c r="S24" s="234"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="228"/>
+      <c r="B25" s="228"/>
+      <c r="C25" s="229"/>
+      <c r="D25" s="229"/>
+      <c r="E25" s="229"/>
+      <c r="F25" s="229"/>
+      <c r="G25" s="229"/>
+      <c r="H25" s="238"/>
+      <c r="I25" s="239"/>
+      <c r="J25" s="239"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
+      <c r="M25" s="240"/>
+      <c r="N25" s="235"/>
+      <c r="O25" s="236"/>
+      <c r="P25" s="237"/>
+      <c r="Q25" s="228"/>
+      <c r="R25" s="234"/>
+      <c r="S25" s="234"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="228"/>
+      <c r="B26" s="228"/>
+      <c r="C26" s="229"/>
+      <c r="D26" s="229"/>
+      <c r="E26" s="229"/>
+      <c r="F26" s="229"/>
+      <c r="G26" s="229"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="239"/>
+      <c r="J26" s="239"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
+      <c r="M26" s="240"/>
+      <c r="N26" s="235"/>
+      <c r="O26" s="236"/>
+      <c r="P26" s="237"/>
+      <c r="Q26" s="228"/>
+      <c r="R26" s="234"/>
+      <c r="S26" s="234"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="228"/>
+      <c r="B27" s="228"/>
+      <c r="C27" s="229"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="238"/>
+      <c r="I27" s="239"/>
+      <c r="J27" s="239"/>
+      <c r="K27" s="239"/>
+      <c r="L27" s="239"/>
+      <c r="M27" s="240"/>
+      <c r="N27" s="235"/>
+      <c r="O27" s="236"/>
+      <c r="P27" s="237"/>
+      <c r="Q27" s="228"/>
+      <c r="R27" s="234"/>
+      <c r="S27" s="234"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="228"/>
+      <c r="B28" s="228"/>
+      <c r="C28" s="229"/>
+      <c r="D28" s="229"/>
+      <c r="E28" s="229"/>
+      <c r="F28" s="229"/>
+      <c r="G28" s="229"/>
+      <c r="H28" s="238"/>
+      <c r="I28" s="239"/>
+      <c r="J28" s="239"/>
+      <c r="K28" s="239"/>
+      <c r="L28" s="239"/>
+      <c r="M28" s="240"/>
+      <c r="N28" s="235"/>
+      <c r="O28" s="236"/>
+      <c r="P28" s="237"/>
+      <c r="Q28" s="228"/>
+      <c r="R28" s="234"/>
+      <c r="S28" s="234"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="228"/>
+      <c r="B29" s="228"/>
+      <c r="C29" s="229"/>
+      <c r="D29" s="229"/>
+      <c r="E29" s="229"/>
+      <c r="F29" s="229"/>
+      <c r="G29" s="229"/>
+      <c r="H29" s="238"/>
+      <c r="I29" s="239"/>
+      <c r="J29" s="239"/>
+      <c r="K29" s="239"/>
+      <c r="L29" s="239"/>
+      <c r="M29" s="240"/>
+      <c r="N29" s="235"/>
+      <c r="O29" s="236"/>
+      <c r="P29" s="237"/>
+      <c r="Q29" s="228"/>
+      <c r="R29" s="234"/>
+      <c r="S29" s="234"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="228"/>
+      <c r="B30" s="228"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="229"/>
+      <c r="G30" s="229"/>
+      <c r="H30" s="238"/>
+      <c r="I30" s="239"/>
+      <c r="J30" s="239"/>
+      <c r="K30" s="239"/>
+      <c r="L30" s="239"/>
+      <c r="M30" s="240"/>
+      <c r="N30" s="235"/>
+      <c r="O30" s="236"/>
+      <c r="P30" s="237"/>
+      <c r="Q30" s="228"/>
+      <c r="R30" s="234"/>
+      <c r="S30" s="234"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="228"/>
+      <c r="B31" s="228"/>
+      <c r="C31" s="229"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="229"/>
+      <c r="G31" s="229"/>
+      <c r="H31" s="238"/>
+      <c r="I31" s="239"/>
+      <c r="J31" s="239"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
+      <c r="M31" s="240"/>
+      <c r="N31" s="235"/>
+      <c r="O31" s="236"/>
+      <c r="P31" s="237"/>
+      <c r="Q31" s="228"/>
+      <c r="R31" s="234"/>
+      <c r="S31" s="234"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="228"/>
+      <c r="B32" s="228"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="229"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
+      <c r="G32" s="229"/>
+      <c r="H32" s="238"/>
+      <c r="I32" s="239"/>
+      <c r="J32" s="239"/>
+      <c r="K32" s="239"/>
+      <c r="L32" s="239"/>
+      <c r="M32" s="240"/>
+      <c r="N32" s="235"/>
+      <c r="O32" s="236"/>
+      <c r="P32" s="237"/>
+      <c r="Q32" s="228"/>
+      <c r="R32" s="234"/>
+      <c r="S32" s="234"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="228"/>
+      <c r="B33" s="228"/>
+      <c r="C33" s="229"/>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
+      <c r="G33" s="229"/>
+      <c r="H33" s="238"/>
+      <c r="I33" s="239"/>
+      <c r="J33" s="239"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
+      <c r="M33" s="240"/>
+      <c r="N33" s="235"/>
+      <c r="O33" s="236"/>
+      <c r="P33" s="237"/>
+      <c r="Q33" s="228"/>
+      <c r="R33" s="234"/>
+      <c r="S33" s="234"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="228"/>
+      <c r="B34" s="228"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="238"/>
+      <c r="I34" s="239"/>
+      <c r="J34" s="239"/>
+      <c r="K34" s="239"/>
+      <c r="L34" s="239"/>
+      <c r="M34" s="240"/>
+      <c r="N34" s="235"/>
+      <c r="O34" s="236"/>
+      <c r="P34" s="237"/>
+      <c r="Q34" s="228"/>
+      <c r="R34" s="234"/>
+      <c r="S34" s="234"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="228"/>
+      <c r="B35" s="228"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="238"/>
+      <c r="I35" s="239"/>
+      <c r="J35" s="239"/>
+      <c r="K35" s="239"/>
+      <c r="L35" s="239"/>
+      <c r="M35" s="240"/>
+      <c r="N35" s="235"/>
+      <c r="O35" s="236"/>
+      <c r="P35" s="237"/>
+      <c r="Q35" s="228"/>
+      <c r="R35" s="234"/>
+      <c r="S35" s="234"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="228"/>
+      <c r="B36" s="228"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="238"/>
+      <c r="I36" s="239"/>
+      <c r="J36" s="239"/>
+      <c r="K36" s="239"/>
+      <c r="L36" s="239"/>
+      <c r="M36" s="240"/>
+      <c r="N36" s="235"/>
+      <c r="O36" s="236"/>
+      <c r="P36" s="237"/>
+      <c r="Q36" s="228"/>
+      <c r="R36" s="234"/>
+      <c r="S36" s="234"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="228"/>
+      <c r="B37" s="228"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="238"/>
+      <c r="I37" s="239"/>
+      <c r="J37" s="239"/>
+      <c r="K37" s="239"/>
+      <c r="L37" s="239"/>
+      <c r="M37" s="240"/>
+      <c r="N37" s="235"/>
+      <c r="O37" s="236"/>
+      <c r="P37" s="237"/>
+      <c r="Q37" s="228"/>
+      <c r="R37" s="234"/>
+      <c r="S37" s="234"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="228"/>
+      <c r="B38" s="228"/>
+      <c r="C38" s="229"/>
+      <c r="D38" s="229"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
+      <c r="G38" s="229"/>
+      <c r="H38" s="238"/>
+      <c r="I38" s="239"/>
+      <c r="J38" s="239"/>
+      <c r="K38" s="239"/>
+      <c r="L38" s="239"/>
+      <c r="M38" s="240"/>
+      <c r="N38" s="235"/>
+      <c r="O38" s="236"/>
+      <c r="P38" s="237"/>
+      <c r="Q38" s="228"/>
+      <c r="R38" s="234"/>
+      <c r="S38" s="234"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="228"/>
+      <c r="B39" s="228"/>
+      <c r="C39" s="229"/>
+      <c r="D39" s="229"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
+      <c r="G39" s="229"/>
+      <c r="H39" s="238"/>
+      <c r="I39" s="239"/>
+      <c r="J39" s="239"/>
+      <c r="K39" s="239"/>
+      <c r="L39" s="239"/>
+      <c r="M39" s="240"/>
+      <c r="N39" s="235"/>
+      <c r="O39" s="236"/>
+      <c r="P39" s="237"/>
+      <c r="Q39" s="228"/>
+      <c r="R39" s="234"/>
+      <c r="S39" s="234"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="228"/>
+      <c r="B40" s="228"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="229"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="238"/>
+      <c r="I40" s="239"/>
+      <c r="J40" s="239"/>
+      <c r="K40" s="239"/>
+      <c r="L40" s="239"/>
+      <c r="M40" s="240"/>
+      <c r="N40" s="235"/>
+      <c r="O40" s="236"/>
+      <c r="P40" s="237"/>
+      <c r="Q40" s="228"/>
+      <c r="R40" s="234"/>
+      <c r="S40" s="234"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="228"/>
+      <c r="B41" s="228"/>
+      <c r="C41" s="229"/>
+      <c r="D41" s="229"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
+      <c r="G41" s="229"/>
+      <c r="H41" s="238"/>
+      <c r="I41" s="239"/>
+      <c r="J41" s="239"/>
+      <c r="K41" s="239"/>
+      <c r="L41" s="239"/>
+      <c r="M41" s="240"/>
+      <c r="N41" s="235"/>
+      <c r="O41" s="236"/>
+      <c r="P41" s="237"/>
+      <c r="Q41" s="228"/>
+      <c r="R41" s="234"/>
+      <c r="S41" s="234"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="228"/>
+      <c r="B42" s="228"/>
+      <c r="C42" s="229"/>
+      <c r="D42" s="229"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
+      <c r="G42" s="229"/>
+      <c r="H42" s="238"/>
+      <c r="I42" s="239"/>
+      <c r="J42" s="239"/>
+      <c r="K42" s="239"/>
+      <c r="L42" s="239"/>
+      <c r="M42" s="240"/>
+      <c r="N42" s="235"/>
+      <c r="O42" s="236"/>
+      <c r="P42" s="237"/>
+      <c r="Q42" s="228"/>
+      <c r="R42" s="234"/>
+      <c r="S42" s="234"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="228"/>
+      <c r="B43" s="228"/>
+      <c r="C43" s="229"/>
+      <c r="D43" s="229"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="238"/>
+      <c r="I43" s="239"/>
+      <c r="J43" s="239"/>
+      <c r="K43" s="239"/>
+      <c r="L43" s="239"/>
+      <c r="M43" s="240"/>
+      <c r="N43" s="235"/>
+      <c r="O43" s="236"/>
+      <c r="P43" s="237"/>
+      <c r="Q43" s="228"/>
+      <c r="R43" s="234"/>
+      <c r="S43" s="234"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="228"/>
+      <c r="B44" s="228"/>
+      <c r="C44" s="229"/>
+      <c r="D44" s="229"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
+      <c r="G44" s="229"/>
+      <c r="H44" s="238"/>
+      <c r="I44" s="239"/>
+      <c r="J44" s="239"/>
+      <c r="K44" s="239"/>
+      <c r="L44" s="239"/>
+      <c r="M44" s="240"/>
+      <c r="N44" s="235"/>
+      <c r="O44" s="236"/>
+      <c r="P44" s="237"/>
+      <c r="Q44" s="228"/>
+      <c r="R44" s="234"/>
+      <c r="S44" s="234"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="228"/>
+      <c r="B45" s="228"/>
+      <c r="C45" s="229"/>
+      <c r="D45" s="229"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
+      <c r="G45" s="229"/>
+      <c r="H45" s="238"/>
+      <c r="I45" s="239"/>
+      <c r="J45" s="239"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="239"/>
+      <c r="M45" s="240"/>
+      <c r="N45" s="235"/>
+      <c r="O45" s="236"/>
+      <c r="P45" s="237"/>
+      <c r="Q45" s="228"/>
+      <c r="R45" s="234"/>
+      <c r="S45" s="234"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="228"/>
+      <c r="B46" s="228"/>
+      <c r="C46" s="229"/>
+      <c r="D46" s="229"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
+      <c r="G46" s="229"/>
+      <c r="H46" s="238"/>
+      <c r="I46" s="239"/>
+      <c r="J46" s="239"/>
+      <c r="K46" s="239"/>
+      <c r="L46" s="239"/>
+      <c r="M46" s="240"/>
+      <c r="N46" s="235"/>
+      <c r="O46" s="236"/>
+      <c r="P46" s="237"/>
+      <c r="Q46" s="228"/>
+      <c r="R46" s="234"/>
+      <c r="S46" s="234"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="228"/>
+      <c r="B47" s="228"/>
+      <c r="C47" s="229"/>
+      <c r="D47" s="229"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
+      <c r="G47" s="229"/>
+      <c r="H47" s="238"/>
+      <c r="I47" s="239"/>
+      <c r="J47" s="239"/>
+      <c r="K47" s="239"/>
+      <c r="L47" s="239"/>
+      <c r="M47" s="240"/>
+      <c r="N47" s="235"/>
+      <c r="O47" s="236"/>
+      <c r="P47" s="237"/>
+      <c r="Q47" s="228"/>
+      <c r="R47" s="234"/>
+      <c r="S47" s="234"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="228"/>
+      <c r="B48" s="228"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="238"/>
+      <c r="I48" s="239"/>
+      <c r="J48" s="239"/>
+      <c r="K48" s="239"/>
+      <c r="L48" s="239"/>
+      <c r="M48" s="240"/>
+      <c r="N48" s="235"/>
+      <c r="O48" s="236"/>
+      <c r="P48" s="237"/>
+      <c r="Q48" s="228"/>
+      <c r="R48" s="234"/>
+      <c r="S48" s="234"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="228"/>
+      <c r="B49" s="228"/>
+      <c r="C49" s="229"/>
+      <c r="D49" s="229"/>
+      <c r="E49" s="229"/>
+      <c r="F49" s="229"/>
+      <c r="G49" s="229"/>
+      <c r="H49" s="238"/>
+      <c r="I49" s="239"/>
+      <c r="J49" s="239"/>
+      <c r="K49" s="239"/>
+      <c r="L49" s="239"/>
+      <c r="M49" s="240"/>
+      <c r="N49" s="235"/>
+      <c r="O49" s="236"/>
+      <c r="P49" s="237"/>
+      <c r="Q49" s="228"/>
+      <c r="R49" s="234"/>
+      <c r="S49" s="234"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="228"/>
+      <c r="B50" s="228"/>
+      <c r="C50" s="229"/>
+      <c r="D50" s="229"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
+      <c r="G50" s="229"/>
+      <c r="H50" s="238"/>
+      <c r="I50" s="239"/>
+      <c r="J50" s="239"/>
+      <c r="K50" s="239"/>
+      <c r="L50" s="239"/>
+      <c r="M50" s="240"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="236"/>
+      <c r="P50" s="237"/>
+      <c r="Q50" s="228"/>
+      <c r="R50" s="234"/>
+      <c r="S50" s="234"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="228"/>
+      <c r="B51" s="228"/>
+      <c r="C51" s="229"/>
+      <c r="D51" s="229"/>
+      <c r="E51" s="229"/>
+      <c r="F51" s="229"/>
+      <c r="G51" s="229"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="239"/>
+      <c r="J51" s="239"/>
+      <c r="K51" s="239"/>
+      <c r="L51" s="239"/>
+      <c r="M51" s="240"/>
+      <c r="N51" s="235"/>
+      <c r="O51" s="236"/>
+      <c r="P51" s="237"/>
+      <c r="Q51" s="228"/>
+      <c r="R51" s="234"/>
+      <c r="S51" s="234"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="228"/>
+      <c r="B52" s="228"/>
+      <c r="C52" s="229"/>
+      <c r="D52" s="229"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="229"/>
+      <c r="G52" s="229"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="239"/>
+      <c r="J52" s="239"/>
+      <c r="K52" s="239"/>
+      <c r="L52" s="239"/>
+      <c r="M52" s="240"/>
+      <c r="N52" s="235"/>
+      <c r="O52" s="236"/>
+      <c r="P52" s="237"/>
+      <c r="Q52" s="228"/>
+      <c r="R52" s="234"/>
+      <c r="S52" s="234"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF256AC-DB89-4235-BE48-8D325A18A7D5}">
+  <dimension ref="A1:BA55"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="24.95" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="3" style="250" customWidth="1"/>
+    <col min="3" max="3" width="3" style="251" customWidth="1"/>
+    <col min="4" max="5" width="3" style="250" customWidth="1"/>
+    <col min="6" max="6" width="3" style="251" customWidth="1"/>
+    <col min="7" max="16384" width="3" style="250"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:53" ht="30" customHeight="1">
+      <c r="A1" s="242"/>
+      <c r="B1" s="243" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="244"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="244"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+      <c r="M1" s="246"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="245"/>
+      <c r="P1" s="246"/>
+      <c r="Q1" s="242"/>
+      <c r="R1" s="242"/>
+      <c r="S1" s="242"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="242"/>
+      <c r="V1" s="245"/>
+      <c r="W1" s="246"/>
+      <c r="X1" s="242"/>
+      <c r="Y1" s="242"/>
+      <c r="Z1" s="242"/>
+      <c r="AA1" s="242"/>
+      <c r="AB1" s="242"/>
+      <c r="AC1" s="245"/>
+      <c r="AD1" s="246"/>
+      <c r="AE1" s="245"/>
+      <c r="AF1" s="246"/>
+      <c r="AG1" s="242"/>
+      <c r="AH1" s="242"/>
+      <c r="AI1" s="242"/>
+      <c r="AJ1" s="242"/>
+      <c r="AK1" s="242"/>
+      <c r="AL1" s="242"/>
+      <c r="AM1" s="242"/>
+      <c r="AN1" s="242"/>
+      <c r="AO1" s="247" t="s">
+        <v>135</v>
+      </c>
+      <c r="AP1" s="247"/>
+      <c r="AQ1" s="247"/>
+      <c r="AR1" s="247"/>
+      <c r="AS1" s="247"/>
+      <c r="AT1" s="248">
+        <v>46199</v>
+      </c>
+      <c r="AU1" s="249"/>
+      <c r="AV1" s="249"/>
+      <c r="AW1" s="249"/>
+      <c r="AX1" s="249"/>
+      <c r="AY1" s="249"/>
+      <c r="AZ1" s="249"/>
+      <c r="BA1" s="249"/>
+    </row>
+    <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="4" spans="1:53" ht="18" customHeight="1">
+      <c r="A4" s="252" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="252"/>
+      <c r="C4" s="253"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="M4" s="252"/>
+      <c r="N4" s="252"/>
+      <c r="O4" s="252"/>
+      <c r="P4" s="252"/>
+      <c r="Q4" s="252"/>
+      <c r="R4" s="252"/>
+      <c r="S4" s="252"/>
+      <c r="T4" s="252"/>
+      <c r="U4" s="252"/>
+      <c r="V4" s="252"/>
+      <c r="W4" s="252"/>
+      <c r="X4" s="252"/>
+      <c r="Y4" s="252"/>
+      <c r="Z4" s="252"/>
+      <c r="AA4" s="252"/>
+      <c r="AB4" s="252"/>
+      <c r="AC4" s="252"/>
+      <c r="AD4" s="252"/>
+      <c r="AE4" s="252"/>
+      <c r="AF4" s="252"/>
+      <c r="AG4" s="252"/>
+      <c r="AH4" s="252"/>
+      <c r="AI4" s="252"/>
+      <c r="AJ4" s="252"/>
+      <c r="AK4" s="252"/>
+    </row>
+    <row r="5" spans="1:53" ht="24.95" customHeight="1">
+      <c r="A5" s="254" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="255"/>
+      <c r="C5" s="255"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="257" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="M5" s="258"/>
+      <c r="N5" s="258"/>
+      <c r="O5" s="258"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="259"/>
+    </row>
+    <row r="6" spans="1:53" ht="24.95" customHeight="1">
+      <c r="A6" s="254" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="255"/>
+      <c r="C6" s="255"/>
+      <c r="D6" s="255"/>
+      <c r="E6" s="255"/>
+      <c r="F6" s="256"/>
+      <c r="G6" s="260">
+        <v>1</v>
+      </c>
+      <c r="H6" s="258"/>
+      <c r="I6" s="258"/>
+      <c r="J6" s="258"/>
+      <c r="K6" s="258"/>
+      <c r="L6" s="258"/>
+      <c r="M6" s="258"/>
+      <c r="N6" s="258"/>
+      <c r="O6" s="258"/>
+      <c r="P6" s="258"/>
+      <c r="Q6" s="258"/>
+      <c r="R6" s="258"/>
+      <c r="S6" s="259"/>
+    </row>
+    <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="8" spans="1:53" ht="18" customHeight="1">
+      <c r="A8" s="252" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" ht="18" customHeight="1">
+      <c r="A9" s="254" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="255"/>
+      <c r="C9" s="255"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
+      <c r="M9" s="255"/>
+      <c r="N9" s="255"/>
+      <c r="O9" s="255"/>
+      <c r="P9" s="255"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="255"/>
+      <c r="U9" s="255"/>
+      <c r="V9" s="255"/>
+      <c r="W9" s="255"/>
+      <c r="X9" s="255"/>
+      <c r="Y9" s="255"/>
+      <c r="Z9" s="255"/>
+      <c r="AA9" s="255"/>
+      <c r="AB9" s="255"/>
+      <c r="AC9" s="255"/>
+      <c r="AD9" s="255"/>
+      <c r="AE9" s="255"/>
+      <c r="AF9" s="255"/>
+      <c r="AG9" s="255"/>
+      <c r="AH9" s="255"/>
+      <c r="AI9" s="255"/>
+      <c r="AJ9" s="255"/>
+      <c r="AK9" s="255"/>
+      <c r="AL9" s="255"/>
+      <c r="AM9" s="255"/>
+      <c r="AN9" s="255"/>
+      <c r="AO9" s="255"/>
+      <c r="AP9" s="255"/>
+      <c r="AQ9" s="255"/>
+      <c r="AR9" s="255"/>
+      <c r="AS9" s="255"/>
+      <c r="AT9" s="255"/>
+      <c r="AU9" s="255"/>
+      <c r="AV9" s="255"/>
+      <c r="AW9" s="255"/>
+      <c r="AX9" s="255"/>
+      <c r="AY9" s="255"/>
+      <c r="AZ9" s="255"/>
+      <c r="BA9" s="256"/>
+    </row>
+    <row r="10" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A10" s="261"/>
+      <c r="B10" s="262"/>
+      <c r="C10" s="262"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
+      <c r="K10" s="262"/>
+      <c r="L10" s="262"/>
+      <c r="M10" s="262"/>
+      <c r="N10" s="262"/>
+      <c r="O10" s="262"/>
+      <c r="P10" s="262"/>
+      <c r="Q10" s="262"/>
+      <c r="R10" s="262"/>
+      <c r="S10" s="262"/>
+      <c r="T10" s="262"/>
+      <c r="U10" s="262"/>
+      <c r="V10" s="262"/>
+      <c r="W10" s="262"/>
+      <c r="X10" s="262"/>
+      <c r="Y10" s="262"/>
+      <c r="Z10" s="262"/>
+      <c r="AA10" s="262"/>
+      <c r="AB10" s="262"/>
+      <c r="AC10" s="262"/>
+      <c r="AD10" s="262"/>
+      <c r="AE10" s="262"/>
+      <c r="AF10" s="262"/>
+      <c r="AG10" s="262"/>
+      <c r="AH10" s="262"/>
+      <c r="AI10" s="262"/>
+      <c r="AJ10" s="262"/>
+      <c r="AK10" s="262"/>
+      <c r="BA10" s="263"/>
+    </row>
+    <row r="11" spans="1:53" ht="21.75" customHeight="1">
+      <c r="A11" s="261"/>
+      <c r="B11" s="262"/>
+      <c r="C11" s="262"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
+      <c r="M11" s="262"/>
+      <c r="N11" s="262"/>
+      <c r="O11" s="262"/>
+      <c r="P11" s="262"/>
+      <c r="Q11" s="262"/>
+      <c r="R11" s="262"/>
+      <c r="S11" s="262"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
+      <c r="AA11" s="262"/>
+      <c r="AB11" s="262"/>
+      <c r="AC11" s="262"/>
+      <c r="AD11" s="262"/>
+      <c r="AE11" s="262"/>
+      <c r="AF11" s="262"/>
+      <c r="AG11" s="262"/>
+      <c r="AH11" s="262"/>
+      <c r="AI11" s="262"/>
+      <c r="AJ11" s="262"/>
+      <c r="AK11" s="262"/>
+      <c r="BA11" s="263"/>
+    </row>
+    <row r="12" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A12" s="261"/>
+      <c r="B12" s="262"/>
+      <c r="C12" s="262"/>
+      <c r="D12" s="262"/>
+      <c r="E12" s="262"/>
+      <c r="F12" s="262"/>
+      <c r="G12" s="262"/>
+      <c r="H12" s="262"/>
+      <c r="I12" s="262"/>
+      <c r="J12" s="262"/>
+      <c r="K12" s="262"/>
+      <c r="L12" s="262"/>
+      <c r="M12" s="262"/>
+      <c r="N12" s="262"/>
+      <c r="O12" s="262"/>
+      <c r="P12" s="262"/>
+      <c r="Q12" s="262"/>
+      <c r="R12" s="262"/>
+      <c r="S12" s="262"/>
+      <c r="T12" s="262"/>
+      <c r="U12" s="262"/>
+      <c r="V12" s="262"/>
+      <c r="W12" s="262"/>
+      <c r="X12" s="262"/>
+      <c r="Y12" s="262"/>
+      <c r="Z12" s="262"/>
+      <c r="AA12" s="262"/>
+      <c r="AB12" s="262"/>
+      <c r="AC12" s="262"/>
+      <c r="AD12" s="262"/>
+      <c r="AE12" s="262"/>
+      <c r="AF12" s="262"/>
+      <c r="AG12" s="262"/>
+      <c r="AH12" s="262"/>
+      <c r="AI12" s="262"/>
+      <c r="AJ12" s="262"/>
+      <c r="AK12" s="262"/>
+      <c r="BA12" s="263"/>
+    </row>
+    <row r="13" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A13" s="261"/>
+      <c r="B13" s="262"/>
+      <c r="C13" s="262"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
+      <c r="M13" s="262"/>
+      <c r="N13" s="262"/>
+      <c r="O13" s="262"/>
+      <c r="P13" s="262"/>
+      <c r="Q13" s="262"/>
+      <c r="R13" s="262"/>
+      <c r="S13" s="262"/>
+      <c r="T13" s="262"/>
+      <c r="U13" s="262"/>
+      <c r="V13" s="262"/>
+      <c r="W13" s="262"/>
+      <c r="X13" s="262"/>
+      <c r="Y13" s="262"/>
+      <c r="Z13" s="262"/>
+      <c r="AA13" s="262"/>
+      <c r="AB13" s="262"/>
+      <c r="AC13" s="262"/>
+      <c r="AD13" s="262"/>
+      <c r="AE13" s="262"/>
+      <c r="AF13" s="262"/>
+      <c r="AG13" s="262"/>
+      <c r="AH13" s="262"/>
+      <c r="AI13" s="262"/>
+      <c r="AJ13" s="262"/>
+      <c r="AK13" s="262"/>
+      <c r="BA13" s="263"/>
+    </row>
+    <row r="14" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A14" s="261"/>
+      <c r="B14" s="262"/>
+      <c r="C14" s="262"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="262"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="262"/>
+      <c r="J14" s="262"/>
+      <c r="K14" s="262"/>
+      <c r="L14" s="262"/>
+      <c r="M14" s="262"/>
+      <c r="N14" s="262"/>
+      <c r="O14" s="262"/>
+      <c r="P14" s="262"/>
+      <c r="Q14" s="262"/>
+      <c r="R14" s="262"/>
+      <c r="S14" s="262"/>
+      <c r="T14" s="262"/>
+      <c r="U14" s="262"/>
+      <c r="V14" s="262"/>
+      <c r="W14" s="262"/>
+      <c r="X14" s="262"/>
+      <c r="Y14" s="262"/>
+      <c r="Z14" s="262"/>
+      <c r="AA14" s="262"/>
+      <c r="AB14" s="262"/>
+      <c r="AC14" s="262"/>
+      <c r="AD14" s="262"/>
+      <c r="AE14" s="262"/>
+      <c r="AF14" s="262"/>
+      <c r="AG14" s="262"/>
+      <c r="AH14" s="262"/>
+      <c r="AI14" s="262"/>
+      <c r="AJ14" s="262"/>
+      <c r="AK14" s="262"/>
+      <c r="BA14" s="263"/>
+    </row>
+    <row r="15" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A15" s="261"/>
+      <c r="B15" s="262"/>
+      <c r="C15" s="262"/>
+      <c r="D15" s="262"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="262"/>
+      <c r="G15" s="262"/>
+      <c r="H15" s="262"/>
+      <c r="I15" s="262"/>
+      <c r="J15" s="262"/>
+      <c r="K15" s="262"/>
+      <c r="L15" s="262"/>
+      <c r="M15" s="262"/>
+      <c r="N15" s="262"/>
+      <c r="O15" s="262"/>
+      <c r="P15" s="262"/>
+      <c r="Q15" s="262"/>
+      <c r="R15" s="262"/>
+      <c r="S15" s="262"/>
+      <c r="T15" s="262"/>
+      <c r="U15" s="262"/>
+      <c r="V15" s="262"/>
+      <c r="W15" s="262"/>
+      <c r="X15" s="262"/>
+      <c r="Y15" s="262"/>
+      <c r="Z15" s="262"/>
+      <c r="AA15" s="262"/>
+      <c r="AB15" s="262"/>
+      <c r="AC15" s="262"/>
+      <c r="AD15" s="262"/>
+      <c r="AE15" s="262"/>
+      <c r="AF15" s="262"/>
+      <c r="AG15" s="262"/>
+      <c r="AH15" s="262"/>
+      <c r="AI15" s="262"/>
+      <c r="AJ15" s="262"/>
+      <c r="AK15" s="262"/>
+      <c r="BA15" s="263"/>
+    </row>
+    <row r="16" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A16" s="261"/>
+      <c r="B16" s="262"/>
+      <c r="C16" s="262"/>
+      <c r="D16" s="262"/>
+      <c r="E16" s="262"/>
+      <c r="F16" s="262"/>
+      <c r="G16" s="262"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="262"/>
+      <c r="J16" s="262"/>
+      <c r="K16" s="262"/>
+      <c r="L16" s="262"/>
+      <c r="M16" s="262"/>
+      <c r="N16" s="262"/>
+      <c r="O16" s="262"/>
+      <c r="P16" s="262"/>
+      <c r="Q16" s="262"/>
+      <c r="R16" s="262"/>
+      <c r="S16" s="262"/>
+      <c r="T16" s="262"/>
+      <c r="U16" s="262"/>
+      <c r="V16" s="262"/>
+      <c r="W16" s="262"/>
+      <c r="X16" s="262"/>
+      <c r="Y16" s="262"/>
+      <c r="Z16" s="262"/>
+      <c r="AA16" s="262"/>
+      <c r="AB16" s="262"/>
+      <c r="AC16" s="262"/>
+      <c r="AD16" s="262"/>
+      <c r="AE16" s="262"/>
+      <c r="AF16" s="262"/>
+      <c r="AG16" s="262"/>
+      <c r="AH16" s="262"/>
+      <c r="AI16" s="262"/>
+      <c r="AJ16" s="262"/>
+      <c r="AK16" s="262"/>
+      <c r="BA16" s="263"/>
+    </row>
+    <row r="17" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A17" s="261"/>
+      <c r="B17" s="262"/>
+      <c r="C17" s="262"/>
+      <c r="D17" s="262"/>
+      <c r="E17" s="262"/>
+      <c r="F17" s="262"/>
+      <c r="G17" s="262"/>
+      <c r="H17" s="262"/>
+      <c r="I17" s="262"/>
+      <c r="J17" s="262"/>
+      <c r="K17" s="262"/>
+      <c r="L17" s="262"/>
+      <c r="M17" s="262"/>
+      <c r="N17" s="262"/>
+      <c r="O17" s="262"/>
+      <c r="P17" s="262"/>
+      <c r="Q17" s="262"/>
+      <c r="R17" s="262"/>
+      <c r="S17" s="262"/>
+      <c r="T17" s="262"/>
+      <c r="U17" s="262"/>
+      <c r="V17" s="262"/>
+      <c r="W17" s="262"/>
+      <c r="X17" s="262"/>
+      <c r="Y17" s="262"/>
+      <c r="Z17" s="262"/>
+      <c r="AA17" s="262"/>
+      <c r="AB17" s="262"/>
+      <c r="AC17" s="262"/>
+      <c r="AD17" s="262"/>
+      <c r="AE17" s="262"/>
+      <c r="AF17" s="262"/>
+      <c r="AG17" s="262"/>
+      <c r="AH17" s="262"/>
+      <c r="AI17" s="262"/>
+      <c r="AJ17" s="262"/>
+      <c r="AK17" s="262"/>
+      <c r="BA17" s="263"/>
+    </row>
+    <row r="18" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A18" s="261"/>
+      <c r="B18" s="262"/>
+      <c r="C18" s="262"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
+      <c r="M18" s="262"/>
+      <c r="N18" s="262"/>
+      <c r="O18" s="262"/>
+      <c r="P18" s="262"/>
+      <c r="Q18" s="262"/>
+      <c r="R18" s="262"/>
+      <c r="S18" s="262"/>
+      <c r="T18" s="262"/>
+      <c r="U18" s="262"/>
+      <c r="V18" s="262"/>
+      <c r="W18" s="262"/>
+      <c r="X18" s="262"/>
+      <c r="Y18" s="262"/>
+      <c r="Z18" s="262"/>
+      <c r="AA18" s="262"/>
+      <c r="AB18" s="262"/>
+      <c r="AC18" s="262"/>
+      <c r="AD18" s="262"/>
+      <c r="AE18" s="262"/>
+      <c r="AF18" s="262"/>
+      <c r="AG18" s="262"/>
+      <c r="AH18" s="262"/>
+      <c r="AI18" s="262"/>
+      <c r="AJ18" s="262"/>
+      <c r="AK18" s="262"/>
+      <c r="BA18" s="263"/>
+    </row>
+    <row r="19" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A19" s="261"/>
+      <c r="B19" s="262"/>
+      <c r="C19" s="262"/>
+      <c r="D19" s="262"/>
+      <c r="E19" s="262"/>
+      <c r="F19" s="262"/>
+      <c r="G19" s="262"/>
+      <c r="H19" s="262"/>
+      <c r="I19" s="262"/>
+      <c r="J19" s="262"/>
+      <c r="K19" s="262"/>
+      <c r="L19" s="262"/>
+      <c r="M19" s="262"/>
+      <c r="N19" s="262"/>
+      <c r="O19" s="262"/>
+      <c r="P19" s="262"/>
+      <c r="Q19" s="262"/>
+      <c r="R19" s="262"/>
+      <c r="S19" s="262"/>
+      <c r="T19" s="262"/>
+      <c r="U19" s="262"/>
+      <c r="V19" s="262"/>
+      <c r="W19" s="262"/>
+      <c r="X19" s="262"/>
+      <c r="Y19" s="262"/>
+      <c r="Z19" s="262"/>
+      <c r="AA19" s="262"/>
+      <c r="AB19" s="262"/>
+      <c r="AC19" s="262"/>
+      <c r="AD19" s="262"/>
+      <c r="AE19" s="262"/>
+      <c r="AF19" s="262"/>
+      <c r="AG19" s="262"/>
+      <c r="AH19" s="262"/>
+      <c r="AI19" s="262"/>
+      <c r="AJ19" s="262"/>
+      <c r="AK19" s="262"/>
+      <c r="BA19" s="263"/>
+    </row>
+    <row r="20" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A20" s="261"/>
+      <c r="B20" s="262"/>
+      <c r="C20" s="262"/>
+      <c r="D20" s="262"/>
+      <c r="E20" s="262"/>
+      <c r="F20" s="262"/>
+      <c r="G20" s="262"/>
+      <c r="H20" s="262"/>
+      <c r="I20" s="262"/>
+      <c r="J20" s="262"/>
+      <c r="K20" s="262"/>
+      <c r="L20" s="262"/>
+      <c r="M20" s="262"/>
+      <c r="N20" s="262"/>
+      <c r="O20" s="262"/>
+      <c r="P20" s="262"/>
+      <c r="Q20" s="262"/>
+      <c r="R20" s="262"/>
+      <c r="S20" s="262"/>
+      <c r="T20" s="262"/>
+      <c r="U20" s="262"/>
+      <c r="V20" s="262"/>
+      <c r="W20" s="262"/>
+      <c r="X20" s="262"/>
+      <c r="Y20" s="262"/>
+      <c r="Z20" s="262"/>
+      <c r="AA20" s="262"/>
+      <c r="AB20" s="262"/>
+      <c r="AC20" s="262"/>
+      <c r="AD20" s="262"/>
+      <c r="AE20" s="262"/>
+      <c r="AF20" s="262"/>
+      <c r="AG20" s="262"/>
+      <c r="AH20" s="262"/>
+      <c r="AI20" s="262"/>
+      <c r="AJ20" s="262"/>
+      <c r="AK20" s="262"/>
+      <c r="BA20" s="263"/>
+    </row>
+    <row r="21" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A21" s="261"/>
+      <c r="B21" s="262"/>
+      <c r="C21" s="262"/>
+      <c r="D21" s="262"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="262"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="262"/>
+      <c r="K21" s="262"/>
+      <c r="L21" s="262"/>
+      <c r="M21" s="262"/>
+      <c r="N21" s="262"/>
+      <c r="O21" s="262"/>
+      <c r="P21" s="262"/>
+      <c r="Q21" s="262"/>
+      <c r="R21" s="262"/>
+      <c r="S21" s="262"/>
+      <c r="T21" s="262"/>
+      <c r="U21" s="262"/>
+      <c r="V21" s="262"/>
+      <c r="W21" s="262"/>
+      <c r="X21" s="262"/>
+      <c r="Y21" s="262"/>
+      <c r="Z21" s="262"/>
+      <c r="AA21" s="262"/>
+      <c r="AB21" s="262"/>
+      <c r="AC21" s="262"/>
+      <c r="AD21" s="262"/>
+      <c r="AE21" s="262"/>
+      <c r="AF21" s="262"/>
+      <c r="AG21" s="262"/>
+      <c r="AH21" s="262"/>
+      <c r="AI21" s="262"/>
+      <c r="AJ21" s="262"/>
+      <c r="AK21" s="262"/>
+      <c r="BA21" s="263"/>
+    </row>
+    <row r="22" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A22" s="261"/>
+      <c r="B22" s="262"/>
+      <c r="C22" s="262"/>
+      <c r="D22" s="262"/>
+      <c r="E22" s="262"/>
+      <c r="F22" s="262"/>
+      <c r="G22" s="262"/>
+      <c r="H22" s="262"/>
+      <c r="I22" s="262"/>
+      <c r="J22" s="262"/>
+      <c r="K22" s="262"/>
+      <c r="L22" s="262"/>
+      <c r="M22" s="262"/>
+      <c r="N22" s="262"/>
+      <c r="O22" s="262"/>
+      <c r="P22" s="262"/>
+      <c r="Q22" s="262"/>
+      <c r="R22" s="262"/>
+      <c r="S22" s="262"/>
+      <c r="T22" s="262"/>
+      <c r="U22" s="262"/>
+      <c r="V22" s="262"/>
+      <c r="W22" s="262"/>
+      <c r="X22" s="262"/>
+      <c r="Y22" s="262"/>
+      <c r="Z22" s="262"/>
+      <c r="AA22" s="262"/>
+      <c r="AB22" s="262"/>
+      <c r="AC22" s="262"/>
+      <c r="AD22" s="262"/>
+      <c r="AE22" s="262"/>
+      <c r="AF22" s="262"/>
+      <c r="AG22" s="262"/>
+      <c r="AH22" s="262"/>
+      <c r="AI22" s="262"/>
+      <c r="AJ22" s="262"/>
+      <c r="AK22" s="262"/>
+      <c r="BA22" s="263"/>
+    </row>
+    <row r="23" spans="1:53" ht="21.75" customHeight="1">
+      <c r="A23" s="261"/>
+      <c r="B23" s="262"/>
+      <c r="C23" s="262"/>
+      <c r="D23" s="262"/>
+      <c r="E23" s="262"/>
+      <c r="F23" s="262"/>
+      <c r="G23" s="262"/>
+      <c r="H23" s="262"/>
+      <c r="I23" s="262"/>
+      <c r="J23" s="262"/>
+      <c r="K23" s="262"/>
+      <c r="L23" s="262"/>
+      <c r="M23" s="262"/>
+      <c r="N23" s="262"/>
+      <c r="O23" s="262"/>
+      <c r="P23" s="262"/>
+      <c r="Q23" s="262"/>
+      <c r="R23" s="262"/>
+      <c r="S23" s="262"/>
+      <c r="T23" s="262"/>
+      <c r="U23" s="262"/>
+      <c r="V23" s="262"/>
+      <c r="W23" s="262"/>
+      <c r="X23" s="262"/>
+      <c r="Y23" s="262"/>
+      <c r="Z23" s="262"/>
+      <c r="AA23" s="262"/>
+      <c r="AB23" s="262"/>
+      <c r="AC23" s="262"/>
+      <c r="AD23" s="262"/>
+      <c r="AE23" s="262"/>
+      <c r="AF23" s="262"/>
+      <c r="AG23" s="262"/>
+      <c r="AH23" s="262"/>
+      <c r="AI23" s="262"/>
+      <c r="AJ23" s="262"/>
+      <c r="AK23" s="262"/>
+      <c r="BA23" s="263"/>
+    </row>
+    <row r="24" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A24" s="261"/>
+      <c r="B24" s="262"/>
+      <c r="C24" s="262"/>
+      <c r="D24" s="262"/>
+      <c r="E24" s="262"/>
+      <c r="F24" s="262"/>
+      <c r="G24" s="262"/>
+      <c r="H24" s="262"/>
+      <c r="I24" s="262"/>
+      <c r="J24" s="262"/>
+      <c r="K24" s="262"/>
+      <c r="L24" s="262"/>
+      <c r="M24" s="262"/>
+      <c r="N24" s="262"/>
+      <c r="O24" s="262"/>
+      <c r="P24" s="262"/>
+      <c r="Q24" s="262"/>
+      <c r="R24" s="262"/>
+      <c r="S24" s="262"/>
+      <c r="T24" s="262"/>
+      <c r="U24" s="262"/>
+      <c r="V24" s="262"/>
+      <c r="W24" s="262"/>
+      <c r="X24" s="262"/>
+      <c r="Y24" s="262"/>
+      <c r="Z24" s="262"/>
+      <c r="AA24" s="262"/>
+      <c r="AB24" s="262"/>
+      <c r="AC24" s="262"/>
+      <c r="AD24" s="262"/>
+      <c r="AE24" s="262"/>
+      <c r="AF24" s="262"/>
+      <c r="AG24" s="262"/>
+      <c r="AH24" s="262"/>
+      <c r="AI24" s="262"/>
+      <c r="AJ24" s="262"/>
+      <c r="AK24" s="262"/>
+      <c r="BA24" s="263"/>
+    </row>
+    <row r="25" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A25" s="261"/>
+      <c r="B25" s="262"/>
+      <c r="C25" s="262"/>
+      <c r="D25" s="262"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="262"/>
+      <c r="G25" s="262"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="262"/>
+      <c r="J25" s="262"/>
+      <c r="K25" s="262"/>
+      <c r="L25" s="262"/>
+      <c r="M25" s="262"/>
+      <c r="N25" s="262"/>
+      <c r="O25" s="262"/>
+      <c r="P25" s="262"/>
+      <c r="Q25" s="262"/>
+      <c r="R25" s="262"/>
+      <c r="S25" s="262"/>
+      <c r="T25" s="262"/>
+      <c r="U25" s="262"/>
+      <c r="V25" s="262"/>
+      <c r="W25" s="262"/>
+      <c r="X25" s="262"/>
+      <c r="Y25" s="262"/>
+      <c r="Z25" s="262"/>
+      <c r="AA25" s="262"/>
+      <c r="AB25" s="262"/>
+      <c r="AC25" s="262"/>
+      <c r="AD25" s="262"/>
+      <c r="AE25" s="262"/>
+      <c r="AF25" s="262"/>
+      <c r="AG25" s="262"/>
+      <c r="AH25" s="262"/>
+      <c r="AI25" s="262"/>
+      <c r="AJ25" s="262"/>
+      <c r="AK25" s="262"/>
+      <c r="BA25" s="263"/>
+    </row>
+    <row r="26" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A26" s="261"/>
+      <c r="B26" s="262"/>
+      <c r="C26" s="262"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
+      <c r="M26" s="262"/>
+      <c r="N26" s="262"/>
+      <c r="O26" s="262"/>
+      <c r="P26" s="262"/>
+      <c r="Q26" s="262"/>
+      <c r="R26" s="262"/>
+      <c r="S26" s="262"/>
+      <c r="T26" s="262"/>
+      <c r="U26" s="262"/>
+      <c r="V26" s="262"/>
+      <c r="W26" s="262"/>
+      <c r="X26" s="262"/>
+      <c r="Y26" s="262"/>
+      <c r="Z26" s="262"/>
+      <c r="AA26" s="262"/>
+      <c r="AB26" s="262"/>
+      <c r="AC26" s="262"/>
+      <c r="AD26" s="262"/>
+      <c r="AE26" s="262"/>
+      <c r="AF26" s="262"/>
+      <c r="AG26" s="262"/>
+      <c r="AH26" s="262"/>
+      <c r="AI26" s="262"/>
+      <c r="AJ26" s="262"/>
+      <c r="AK26" s="262"/>
+      <c r="BA26" s="263"/>
+    </row>
+    <row r="27" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A27" s="261"/>
+      <c r="B27" s="262"/>
+      <c r="C27" s="262"/>
+      <c r="D27" s="262"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="262"/>
+      <c r="G27" s="262"/>
+      <c r="H27" s="262"/>
+      <c r="I27" s="262"/>
+      <c r="J27" s="262"/>
+      <c r="K27" s="262"/>
+      <c r="L27" s="262"/>
+      <c r="M27" s="262"/>
+      <c r="N27" s="262"/>
+      <c r="O27" s="262"/>
+      <c r="P27" s="262"/>
+      <c r="Q27" s="262"/>
+      <c r="R27" s="262"/>
+      <c r="S27" s="262"/>
+      <c r="T27" s="262"/>
+      <c r="U27" s="262"/>
+      <c r="V27" s="262"/>
+      <c r="W27" s="262"/>
+      <c r="X27" s="262"/>
+      <c r="Y27" s="262"/>
+      <c r="Z27" s="262"/>
+      <c r="AA27" s="262"/>
+      <c r="AB27" s="262"/>
+      <c r="AC27" s="262"/>
+      <c r="AD27" s="262"/>
+      <c r="AE27" s="262"/>
+      <c r="AF27" s="262"/>
+      <c r="AG27" s="262"/>
+      <c r="AH27" s="262"/>
+      <c r="AI27" s="262"/>
+      <c r="AJ27" s="262"/>
+      <c r="AK27" s="262"/>
+      <c r="BA27" s="263"/>
+    </row>
+    <row r="28" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A28" s="261"/>
+      <c r="B28" s="262"/>
+      <c r="C28" s="262"/>
+      <c r="D28" s="262"/>
+      <c r="E28" s="262"/>
+      <c r="F28" s="262"/>
+      <c r="G28" s="262"/>
+      <c r="H28" s="262"/>
+      <c r="I28" s="262"/>
+      <c r="J28" s="262"/>
+      <c r="K28" s="262"/>
+      <c r="L28" s="262"/>
+      <c r="M28" s="262"/>
+      <c r="N28" s="262"/>
+      <c r="O28" s="262"/>
+      <c r="P28" s="262"/>
+      <c r="Q28" s="262"/>
+      <c r="R28" s="262"/>
+      <c r="S28" s="262"/>
+      <c r="T28" s="262"/>
+      <c r="U28" s="262"/>
+      <c r="V28" s="262"/>
+      <c r="W28" s="262"/>
+      <c r="X28" s="262"/>
+      <c r="Y28" s="262"/>
+      <c r="Z28" s="262"/>
+      <c r="AA28" s="262"/>
+      <c r="AB28" s="262"/>
+      <c r="AC28" s="262"/>
+      <c r="AD28" s="262"/>
+      <c r="AE28" s="262"/>
+      <c r="AF28" s="262"/>
+      <c r="AG28" s="262"/>
+      <c r="AH28" s="262"/>
+      <c r="AI28" s="262"/>
+      <c r="AJ28" s="262"/>
+      <c r="AK28" s="262"/>
+      <c r="BA28" s="263"/>
+    </row>
+    <row r="29" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A29" s="261"/>
+      <c r="B29" s="262"/>
+      <c r="C29" s="262"/>
+      <c r="D29" s="262"/>
+      <c r="E29" s="262"/>
+      <c r="F29" s="262"/>
+      <c r="G29" s="262"/>
+      <c r="H29" s="262"/>
+      <c r="I29" s="262"/>
+      <c r="J29" s="262"/>
+      <c r="K29" s="262"/>
+      <c r="L29" s="262"/>
+      <c r="M29" s="262"/>
+      <c r="N29" s="262"/>
+      <c r="O29" s="262"/>
+      <c r="P29" s="262"/>
+      <c r="Q29" s="262"/>
+      <c r="R29" s="262"/>
+      <c r="S29" s="262"/>
+      <c r="T29" s="262"/>
+      <c r="U29" s="262"/>
+      <c r="V29" s="262"/>
+      <c r="W29" s="262"/>
+      <c r="X29" s="262"/>
+      <c r="Y29" s="262"/>
+      <c r="Z29" s="262"/>
+      <c r="AA29" s="262"/>
+      <c r="AB29" s="262"/>
+      <c r="AC29" s="262"/>
+      <c r="AD29" s="262"/>
+      <c r="AE29" s="262"/>
+      <c r="AF29" s="262"/>
+      <c r="AG29" s="262"/>
+      <c r="AH29" s="262"/>
+      <c r="AI29" s="262"/>
+      <c r="AJ29" s="262"/>
+      <c r="AK29" s="262"/>
+      <c r="BA29" s="263"/>
+    </row>
+    <row r="30" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A30" s="261"/>
+      <c r="B30" s="262"/>
+      <c r="C30" s="262"/>
+      <c r="D30" s="262"/>
+      <c r="E30" s="262"/>
+      <c r="F30" s="262"/>
+      <c r="G30" s="262"/>
+      <c r="H30" s="262"/>
+      <c r="I30" s="262"/>
+      <c r="J30" s="262"/>
+      <c r="K30" s="262"/>
+      <c r="L30" s="262"/>
+      <c r="M30" s="262"/>
+      <c r="N30" s="262"/>
+      <c r="O30" s="262"/>
+      <c r="P30" s="262"/>
+      <c r="Q30" s="262"/>
+      <c r="R30" s="262"/>
+      <c r="S30" s="262"/>
+      <c r="T30" s="262"/>
+      <c r="U30" s="262"/>
+      <c r="V30" s="262"/>
+      <c r="W30" s="262"/>
+      <c r="X30" s="262"/>
+      <c r="Y30" s="262"/>
+      <c r="Z30" s="262"/>
+      <c r="AA30" s="262"/>
+      <c r="AB30" s="262"/>
+      <c r="AC30" s="262"/>
+      <c r="AD30" s="262"/>
+      <c r="AE30" s="262"/>
+      <c r="AF30" s="262"/>
+      <c r="AG30" s="262"/>
+      <c r="AH30" s="262"/>
+      <c r="AI30" s="262"/>
+      <c r="AJ30" s="262"/>
+      <c r="AK30" s="262"/>
+      <c r="BA30" s="263"/>
+    </row>
+    <row r="31" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A31" s="261"/>
+      <c r="B31" s="262"/>
+      <c r="C31" s="262"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="262"/>
+      <c r="G31" s="262"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="262"/>
+      <c r="J31" s="262"/>
+      <c r="K31" s="262"/>
+      <c r="L31" s="262"/>
+      <c r="M31" s="262"/>
+      <c r="N31" s="262"/>
+      <c r="O31" s="262"/>
+      <c r="P31" s="262"/>
+      <c r="Q31" s="262"/>
+      <c r="R31" s="262"/>
+      <c r="S31" s="262"/>
+      <c r="T31" s="262"/>
+      <c r="U31" s="262"/>
+      <c r="V31" s="262"/>
+      <c r="W31" s="262"/>
+      <c r="X31" s="262"/>
+      <c r="Y31" s="262"/>
+      <c r="Z31" s="262"/>
+      <c r="AA31" s="262"/>
+      <c r="AB31" s="262"/>
+      <c r="AC31" s="262"/>
+      <c r="AD31" s="262"/>
+      <c r="AE31" s="262"/>
+      <c r="AF31" s="262"/>
+      <c r="AG31" s="262"/>
+      <c r="AH31" s="262"/>
+      <c r="AI31" s="262"/>
+      <c r="AJ31" s="262"/>
+      <c r="AK31" s="262"/>
+      <c r="BA31" s="263"/>
+    </row>
+    <row r="32" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A32" s="261"/>
+      <c r="B32" s="262"/>
+      <c r="C32" s="262"/>
+      <c r="D32" s="262"/>
+      <c r="E32" s="262"/>
+      <c r="F32" s="262"/>
+      <c r="G32" s="262"/>
+      <c r="H32" s="262"/>
+      <c r="I32" s="262"/>
+      <c r="J32" s="262"/>
+      <c r="K32" s="262"/>
+      <c r="L32" s="262"/>
+      <c r="M32" s="262"/>
+      <c r="N32" s="262"/>
+      <c r="O32" s="262"/>
+      <c r="P32" s="262"/>
+      <c r="Q32" s="262"/>
+      <c r="R32" s="262"/>
+      <c r="S32" s="262"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="262"/>
+      <c r="X32" s="262"/>
+      <c r="Y32" s="262"/>
+      <c r="Z32" s="262"/>
+      <c r="AA32" s="262"/>
+      <c r="AB32" s="262"/>
+      <c r="AC32" s="262"/>
+      <c r="AD32" s="262"/>
+      <c r="AE32" s="262"/>
+      <c r="AF32" s="262"/>
+      <c r="AG32" s="262"/>
+      <c r="AH32" s="262"/>
+      <c r="AI32" s="262"/>
+      <c r="AJ32" s="262"/>
+      <c r="AK32" s="262"/>
+      <c r="BA32" s="263"/>
+    </row>
+    <row r="33" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A33" s="261"/>
+      <c r="B33" s="262"/>
+      <c r="C33" s="262"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
+      <c r="M33" s="262"/>
+      <c r="N33" s="262"/>
+      <c r="O33" s="262"/>
+      <c r="P33" s="262"/>
+      <c r="Q33" s="262"/>
+      <c r="R33" s="262"/>
+      <c r="S33" s="262"/>
+      <c r="T33" s="262"/>
+      <c r="U33" s="262"/>
+      <c r="V33" s="262"/>
+      <c r="W33" s="262"/>
+      <c r="X33" s="262"/>
+      <c r="Y33" s="262"/>
+      <c r="Z33" s="262"/>
+      <c r="AA33" s="262"/>
+      <c r="AB33" s="262"/>
+      <c r="AC33" s="262"/>
+      <c r="AD33" s="262"/>
+      <c r="AE33" s="262"/>
+      <c r="AF33" s="262"/>
+      <c r="AG33" s="262"/>
+      <c r="AH33" s="262"/>
+      <c r="AI33" s="262"/>
+      <c r="AJ33" s="262"/>
+      <c r="AK33" s="262"/>
+      <c r="BA33" s="263"/>
+    </row>
+    <row r="34" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A34" s="261"/>
+      <c r="B34" s="262"/>
+      <c r="C34" s="262"/>
+      <c r="D34" s="262"/>
+      <c r="E34" s="262"/>
+      <c r="F34" s="262"/>
+      <c r="G34" s="262"/>
+      <c r="H34" s="262"/>
+      <c r="I34" s="262"/>
+      <c r="J34" s="262"/>
+      <c r="K34" s="262"/>
+      <c r="L34" s="262"/>
+      <c r="M34" s="262"/>
+      <c r="N34" s="262"/>
+      <c r="O34" s="262"/>
+      <c r="P34" s="262"/>
+      <c r="Q34" s="262"/>
+      <c r="R34" s="262"/>
+      <c r="S34" s="262"/>
+      <c r="T34" s="262"/>
+      <c r="U34" s="262"/>
+      <c r="V34" s="262"/>
+      <c r="W34" s="262"/>
+      <c r="X34" s="262"/>
+      <c r="Y34" s="262"/>
+      <c r="Z34" s="262"/>
+      <c r="AA34" s="262"/>
+      <c r="AB34" s="262"/>
+      <c r="AC34" s="262"/>
+      <c r="AD34" s="262"/>
+      <c r="AE34" s="262"/>
+      <c r="AF34" s="262"/>
+      <c r="AG34" s="262"/>
+      <c r="AH34" s="262"/>
+      <c r="AI34" s="262"/>
+      <c r="AJ34" s="262"/>
+      <c r="AK34" s="262"/>
+      <c r="BA34" s="263"/>
+    </row>
+    <row r="35" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A35" s="261"/>
+      <c r="B35" s="262"/>
+      <c r="C35" s="262"/>
+      <c r="D35" s="262"/>
+      <c r="E35" s="262"/>
+      <c r="F35" s="262"/>
+      <c r="G35" s="262"/>
+      <c r="H35" s="262"/>
+      <c r="I35" s="262"/>
+      <c r="J35" s="262"/>
+      <c r="K35" s="262"/>
+      <c r="L35" s="262"/>
+      <c r="M35" s="262"/>
+      <c r="N35" s="262"/>
+      <c r="O35" s="262"/>
+      <c r="P35" s="262"/>
+      <c r="Q35" s="262"/>
+      <c r="R35" s="262"/>
+      <c r="S35" s="262"/>
+      <c r="T35" s="262"/>
+      <c r="U35" s="262"/>
+      <c r="V35" s="262"/>
+      <c r="W35" s="262"/>
+      <c r="X35" s="262"/>
+      <c r="Y35" s="262"/>
+      <c r="Z35" s="262"/>
+      <c r="AA35" s="262"/>
+      <c r="AB35" s="262"/>
+      <c r="AC35" s="262"/>
+      <c r="AD35" s="262"/>
+      <c r="AE35" s="262"/>
+      <c r="AF35" s="262"/>
+      <c r="AG35" s="262"/>
+      <c r="AH35" s="262"/>
+      <c r="AI35" s="262"/>
+      <c r="AJ35" s="262"/>
+      <c r="AK35" s="262"/>
+      <c r="BA35" s="263"/>
+    </row>
+    <row r="36" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A36" s="261"/>
+      <c r="B36" s="262"/>
+      <c r="C36" s="262"/>
+      <c r="D36" s="262"/>
+      <c r="E36" s="262"/>
+      <c r="F36" s="262"/>
+      <c r="G36" s="262"/>
+      <c r="H36" s="262"/>
+      <c r="I36" s="262"/>
+      <c r="J36" s="262"/>
+      <c r="K36" s="262"/>
+      <c r="L36" s="262"/>
+      <c r="M36" s="262"/>
+      <c r="N36" s="262"/>
+      <c r="O36" s="262"/>
+      <c r="P36" s="262"/>
+      <c r="Q36" s="262"/>
+      <c r="R36" s="262"/>
+      <c r="S36" s="262"/>
+      <c r="T36" s="262"/>
+      <c r="U36" s="262"/>
+      <c r="V36" s="262"/>
+      <c r="W36" s="262"/>
+      <c r="X36" s="262"/>
+      <c r="Y36" s="262"/>
+      <c r="Z36" s="262"/>
+      <c r="AA36" s="262"/>
+      <c r="AB36" s="262"/>
+      <c r="AC36" s="262"/>
+      <c r="AD36" s="262"/>
+      <c r="AE36" s="262"/>
+      <c r="AF36" s="262"/>
+      <c r="AG36" s="262"/>
+      <c r="AH36" s="262"/>
+      <c r="AI36" s="262"/>
+      <c r="AJ36" s="262"/>
+      <c r="AK36" s="262"/>
+      <c r="BA36" s="263"/>
+    </row>
+    <row r="37" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A37" s="261"/>
+      <c r="B37" s="262"/>
+      <c r="C37" s="262"/>
+      <c r="D37" s="262"/>
+      <c r="E37" s="262"/>
+      <c r="F37" s="262"/>
+      <c r="G37" s="262"/>
+      <c r="H37" s="262"/>
+      <c r="I37" s="262"/>
+      <c r="J37" s="262"/>
+      <c r="K37" s="262"/>
+      <c r="L37" s="262"/>
+      <c r="M37" s="262"/>
+      <c r="N37" s="262"/>
+      <c r="O37" s="262"/>
+      <c r="P37" s="262"/>
+      <c r="Q37" s="262"/>
+      <c r="R37" s="262"/>
+      <c r="S37" s="262"/>
+      <c r="T37" s="262"/>
+      <c r="U37" s="262"/>
+      <c r="V37" s="262"/>
+      <c r="W37" s="262"/>
+      <c r="X37" s="262"/>
+      <c r="Y37" s="262"/>
+      <c r="Z37" s="262"/>
+      <c r="AA37" s="262"/>
+      <c r="AB37" s="262"/>
+      <c r="AC37" s="262"/>
+      <c r="AD37" s="262"/>
+      <c r="AE37" s="262"/>
+      <c r="AF37" s="262"/>
+      <c r="AG37" s="262"/>
+      <c r="AH37" s="262"/>
+      <c r="AI37" s="262"/>
+      <c r="AJ37" s="262"/>
+      <c r="AK37" s="262"/>
+      <c r="BA37" s="263"/>
+    </row>
+    <row r="38" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A38" s="261"/>
+      <c r="B38" s="262"/>
+      <c r="C38" s="262"/>
+      <c r="D38" s="262"/>
+      <c r="E38" s="262"/>
+      <c r="F38" s="262"/>
+      <c r="G38" s="262"/>
+      <c r="H38" s="262"/>
+      <c r="I38" s="262"/>
+      <c r="J38" s="262"/>
+      <c r="K38" s="262"/>
+      <c r="L38" s="262"/>
+      <c r="M38" s="262"/>
+      <c r="N38" s="262"/>
+      <c r="O38" s="262"/>
+      <c r="P38" s="262"/>
+      <c r="Q38" s="262"/>
+      <c r="R38" s="262"/>
+      <c r="S38" s="262"/>
+      <c r="T38" s="262"/>
+      <c r="U38" s="262"/>
+      <c r="V38" s="262"/>
+      <c r="W38" s="262"/>
+      <c r="X38" s="262"/>
+      <c r="Y38" s="262"/>
+      <c r="Z38" s="262"/>
+      <c r="AA38" s="262"/>
+      <c r="AB38" s="262"/>
+      <c r="AC38" s="262"/>
+      <c r="AD38" s="262"/>
+      <c r="AE38" s="262"/>
+      <c r="AF38" s="262"/>
+      <c r="AG38" s="262"/>
+      <c r="AH38" s="262"/>
+      <c r="AI38" s="262"/>
+      <c r="AJ38" s="262"/>
+      <c r="AK38" s="262"/>
+      <c r="BA38" s="263"/>
+    </row>
+    <row r="39" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A39" s="261"/>
+      <c r="B39" s="262"/>
+      <c r="C39" s="262"/>
+      <c r="D39" s="262"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="262"/>
+      <c r="G39" s="262"/>
+      <c r="H39" s="262"/>
+      <c r="I39" s="262"/>
+      <c r="J39" s="262"/>
+      <c r="K39" s="262"/>
+      <c r="L39" s="262"/>
+      <c r="M39" s="262"/>
+      <c r="N39" s="262"/>
+      <c r="O39" s="262"/>
+      <c r="P39" s="262"/>
+      <c r="Q39" s="262"/>
+      <c r="R39" s="262"/>
+      <c r="S39" s="262"/>
+      <c r="T39" s="262"/>
+      <c r="U39" s="262"/>
+      <c r="V39" s="262"/>
+      <c r="W39" s="262"/>
+      <c r="X39" s="262"/>
+      <c r="Y39" s="262"/>
+      <c r="Z39" s="262"/>
+      <c r="AA39" s="262"/>
+      <c r="AB39" s="262"/>
+      <c r="AC39" s="262"/>
+      <c r="AD39" s="262"/>
+      <c r="AE39" s="262"/>
+      <c r="AF39" s="262"/>
+      <c r="AG39" s="262"/>
+      <c r="AH39" s="262"/>
+      <c r="AI39" s="262"/>
+      <c r="AJ39" s="262"/>
+      <c r="AK39" s="262"/>
+      <c r="BA39" s="263"/>
+    </row>
+    <row r="40" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A40" s="261"/>
+      <c r="B40" s="262"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
+      <c r="M40" s="262"/>
+      <c r="N40" s="262"/>
+      <c r="O40" s="262"/>
+      <c r="P40" s="262"/>
+      <c r="Q40" s="262"/>
+      <c r="R40" s="262"/>
+      <c r="S40" s="262"/>
+      <c r="T40" s="262"/>
+      <c r="U40" s="262"/>
+      <c r="V40" s="262"/>
+      <c r="W40" s="262"/>
+      <c r="X40" s="262"/>
+      <c r="Y40" s="262"/>
+      <c r="Z40" s="262"/>
+      <c r="AA40" s="262"/>
+      <c r="AB40" s="262"/>
+      <c r="AC40" s="262"/>
+      <c r="AD40" s="262"/>
+      <c r="AE40" s="262"/>
+      <c r="AF40" s="262"/>
+      <c r="AG40" s="262"/>
+      <c r="AH40" s="262"/>
+      <c r="AI40" s="262"/>
+      <c r="AJ40" s="262"/>
+      <c r="AK40" s="262"/>
+      <c r="BA40" s="263"/>
+    </row>
+    <row r="41" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A41" s="261"/>
+      <c r="B41" s="262"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="262"/>
+      <c r="E41" s="262"/>
+      <c r="F41" s="262"/>
+      <c r="G41" s="262"/>
+      <c r="H41" s="262"/>
+      <c r="I41" s="262"/>
+      <c r="J41" s="262"/>
+      <c r="K41" s="262"/>
+      <c r="L41" s="262"/>
+      <c r="M41" s="262"/>
+      <c r="N41" s="262"/>
+      <c r="O41" s="262"/>
+      <c r="P41" s="262"/>
+      <c r="Q41" s="262"/>
+      <c r="R41" s="262"/>
+      <c r="S41" s="262"/>
+      <c r="T41" s="262"/>
+      <c r="U41" s="262"/>
+      <c r="V41" s="262"/>
+      <c r="W41" s="262"/>
+      <c r="X41" s="262"/>
+      <c r="Y41" s="262"/>
+      <c r="Z41" s="262"/>
+      <c r="AA41" s="262"/>
+      <c r="AB41" s="262"/>
+      <c r="AC41" s="262"/>
+      <c r="AD41" s="262"/>
+      <c r="AE41" s="262"/>
+      <c r="AF41" s="262"/>
+      <c r="AG41" s="262"/>
+      <c r="AH41" s="262"/>
+      <c r="AI41" s="262"/>
+      <c r="AJ41" s="262"/>
+      <c r="AK41" s="262"/>
+      <c r="BA41" s="263"/>
+    </row>
+    <row r="42" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A42" s="261"/>
+      <c r="B42" s="262"/>
+      <c r="C42" s="262"/>
+      <c r="D42" s="262"/>
+      <c r="E42" s="262"/>
+      <c r="F42" s="262"/>
+      <c r="G42" s="262"/>
+      <c r="H42" s="262"/>
+      <c r="I42" s="262"/>
+      <c r="J42" s="262"/>
+      <c r="K42" s="262"/>
+      <c r="L42" s="262"/>
+      <c r="M42" s="262"/>
+      <c r="N42" s="262"/>
+      <c r="O42" s="262"/>
+      <c r="P42" s="262"/>
+      <c r="Q42" s="262"/>
+      <c r="R42" s="262"/>
+      <c r="S42" s="262"/>
+      <c r="T42" s="262"/>
+      <c r="U42" s="262"/>
+      <c r="V42" s="262"/>
+      <c r="W42" s="262"/>
+      <c r="X42" s="262"/>
+      <c r="Y42" s="262"/>
+      <c r="Z42" s="262"/>
+      <c r="AA42" s="262"/>
+      <c r="AB42" s="262"/>
+      <c r="AC42" s="262"/>
+      <c r="AD42" s="262"/>
+      <c r="AE42" s="262"/>
+      <c r="AF42" s="262"/>
+      <c r="AG42" s="262"/>
+      <c r="AH42" s="262"/>
+      <c r="AI42" s="262"/>
+      <c r="AJ42" s="262"/>
+      <c r="AK42" s="262"/>
+      <c r="BA42" s="263"/>
+    </row>
+    <row r="43" spans="1:53" ht="18" customHeight="1">
+      <c r="A43" s="254" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" s="255"/>
+      <c r="C43" s="255"/>
+      <c r="D43" s="255"/>
+      <c r="E43" s="255"/>
+      <c r="F43" s="255"/>
+      <c r="G43" s="255"/>
+      <c r="H43" s="255"/>
+      <c r="I43" s="255"/>
+      <c r="J43" s="255"/>
+      <c r="K43" s="255"/>
+      <c r="L43" s="255"/>
+      <c r="M43" s="255"/>
+      <c r="N43" s="255"/>
+      <c r="O43" s="255"/>
+      <c r="P43" s="255"/>
+      <c r="Q43" s="255"/>
+      <c r="R43" s="255"/>
+      <c r="S43" s="255"/>
+      <c r="T43" s="255"/>
+      <c r="U43" s="255"/>
+      <c r="V43" s="255"/>
+      <c r="W43" s="255"/>
+      <c r="X43" s="255"/>
+      <c r="Y43" s="255"/>
+      <c r="Z43" s="255"/>
+      <c r="AA43" s="255"/>
+      <c r="AB43" s="255"/>
+      <c r="AC43" s="255"/>
+      <c r="AD43" s="255"/>
+      <c r="AE43" s="255"/>
+      <c r="AF43" s="255"/>
+      <c r="AG43" s="255"/>
+      <c r="AH43" s="255"/>
+      <c r="AI43" s="255"/>
+      <c r="AJ43" s="255"/>
+      <c r="AK43" s="255"/>
+      <c r="AL43" s="255"/>
+      <c r="AM43" s="255"/>
+      <c r="AN43" s="255"/>
+      <c r="AO43" s="255"/>
+      <c r="AP43" s="255"/>
+      <c r="AQ43" s="255"/>
+      <c r="AR43" s="255"/>
+      <c r="AS43" s="255"/>
+      <c r="AT43" s="255"/>
+      <c r="AU43" s="255"/>
+      <c r="AV43" s="255"/>
+      <c r="AW43" s="255"/>
+      <c r="AX43" s="255"/>
+      <c r="AY43" s="255"/>
+      <c r="AZ43" s="255"/>
+      <c r="BA43" s="256"/>
+    </row>
+    <row r="44" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A44" s="264"/>
+      <c r="B44" s="265"/>
+      <c r="C44" s="265"/>
+      <c r="D44" s="265"/>
+      <c r="E44" s="265"/>
+      <c r="F44" s="265"/>
+      <c r="G44" s="265"/>
+      <c r="H44" s="265"/>
+      <c r="I44" s="265"/>
+      <c r="J44" s="265"/>
+      <c r="K44" s="265"/>
+      <c r="L44" s="265"/>
+      <c r="M44" s="265"/>
+      <c r="N44" s="265"/>
+      <c r="O44" s="265"/>
+      <c r="P44" s="265"/>
+      <c r="Q44" s="265"/>
+      <c r="R44" s="265"/>
+      <c r="S44" s="265"/>
+      <c r="T44" s="265"/>
+      <c r="U44" s="265"/>
+      <c r="V44" s="265"/>
+      <c r="W44" s="265"/>
+      <c r="X44" s="265"/>
+      <c r="Y44" s="265"/>
+      <c r="Z44" s="265"/>
+      <c r="AA44" s="265"/>
+      <c r="AB44" s="265"/>
+      <c r="AC44" s="265"/>
+      <c r="AD44" s="265"/>
+      <c r="AE44" s="265"/>
+      <c r="AF44" s="265"/>
+      <c r="AG44" s="265"/>
+      <c r="AH44" s="265"/>
+      <c r="AI44" s="262"/>
+      <c r="AJ44" s="262"/>
+      <c r="AK44" s="262"/>
+      <c r="BA44" s="263"/>
+    </row>
+    <row r="45" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A45" s="261"/>
+      <c r="B45" s="262"/>
+      <c r="C45" s="262"/>
+      <c r="D45" s="262"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="262"/>
+      <c r="G45" s="262"/>
+      <c r="H45" s="262"/>
+      <c r="I45" s="262"/>
+      <c r="J45" s="262"/>
+      <c r="K45" s="262"/>
+      <c r="L45" s="262"/>
+      <c r="M45" s="262"/>
+      <c r="N45" s="262"/>
+      <c r="O45" s="262"/>
+      <c r="P45" s="262"/>
+      <c r="Q45" s="262"/>
+      <c r="R45" s="262"/>
+      <c r="S45" s="262"/>
+      <c r="T45" s="262"/>
+      <c r="U45" s="262"/>
+      <c r="V45" s="262"/>
+      <c r="W45" s="262"/>
+      <c r="X45" s="262"/>
+      <c r="Y45" s="262"/>
+      <c r="Z45" s="262"/>
+      <c r="AA45" s="262"/>
+      <c r="AB45" s="262"/>
+      <c r="AC45" s="262"/>
+      <c r="AD45" s="262"/>
+      <c r="AE45" s="262"/>
+      <c r="AF45" s="262"/>
+      <c r="AG45" s="262"/>
+      <c r="AH45" s="262"/>
+      <c r="AI45" s="262"/>
+      <c r="AJ45" s="262"/>
+      <c r="AK45" s="262"/>
+      <c r="BA45" s="263"/>
+    </row>
+    <row r="46" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A46" s="261"/>
+      <c r="B46" s="262"/>
+      <c r="C46" s="262"/>
+      <c r="D46" s="262"/>
+      <c r="E46" s="262"/>
+      <c r="F46" s="262"/>
+      <c r="G46" s="262"/>
+      <c r="H46" s="262"/>
+      <c r="I46" s="262"/>
+      <c r="J46" s="262"/>
+      <c r="K46" s="262"/>
+      <c r="L46" s="262"/>
+      <c r="M46" s="262"/>
+      <c r="N46" s="262"/>
+      <c r="O46" s="262"/>
+      <c r="P46" s="262"/>
+      <c r="Q46" s="262"/>
+      <c r="R46" s="262"/>
+      <c r="S46" s="262"/>
+      <c r="T46" s="262"/>
+      <c r="U46" s="262"/>
+      <c r="V46" s="262"/>
+      <c r="W46" s="262"/>
+      <c r="X46" s="262"/>
+      <c r="Y46" s="262"/>
+      <c r="Z46" s="262"/>
+      <c r="AA46" s="262"/>
+      <c r="AB46" s="262"/>
+      <c r="AC46" s="262"/>
+      <c r="AD46" s="262"/>
+      <c r="AE46" s="262"/>
+      <c r="AF46" s="262"/>
+      <c r="AG46" s="262"/>
+      <c r="AH46" s="262"/>
+      <c r="AI46" s="262"/>
+      <c r="AJ46" s="262"/>
+      <c r="AK46" s="262"/>
+      <c r="BA46" s="263"/>
+    </row>
+    <row r="47" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A47" s="261"/>
+      <c r="B47" s="262"/>
+      <c r="C47" s="262"/>
+      <c r="D47" s="262"/>
+      <c r="E47" s="262"/>
+      <c r="F47" s="262"/>
+      <c r="G47" s="262"/>
+      <c r="H47" s="262"/>
+      <c r="I47" s="262"/>
+      <c r="J47" s="262"/>
+      <c r="K47" s="262"/>
+      <c r="L47" s="262"/>
+      <c r="M47" s="262"/>
+      <c r="N47" s="262"/>
+      <c r="O47" s="262"/>
+      <c r="P47" s="262"/>
+      <c r="Q47" s="262"/>
+      <c r="R47" s="262"/>
+      <c r="S47" s="262"/>
+      <c r="T47" s="262"/>
+      <c r="U47" s="262"/>
+      <c r="V47" s="262"/>
+      <c r="W47" s="262"/>
+      <c r="X47" s="262"/>
+      <c r="Y47" s="262"/>
+      <c r="Z47" s="262"/>
+      <c r="AA47" s="262"/>
+      <c r="AB47" s="262"/>
+      <c r="AC47" s="262"/>
+      <c r="AD47" s="262"/>
+      <c r="AE47" s="262"/>
+      <c r="AF47" s="262"/>
+      <c r="AG47" s="262"/>
+      <c r="AH47" s="262"/>
+      <c r="AI47" s="262"/>
+      <c r="AJ47" s="262"/>
+      <c r="AK47" s="262"/>
+      <c r="BA47" s="263"/>
+    </row>
+    <row r="48" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A48" s="261"/>
+      <c r="B48" s="262"/>
+      <c r="C48" s="262"/>
+      <c r="D48" s="262"/>
+      <c r="E48" s="262"/>
+      <c r="F48" s="262"/>
+      <c r="G48" s="262"/>
+      <c r="H48" s="262"/>
+      <c r="I48" s="262"/>
+      <c r="J48" s="262"/>
+      <c r="K48" s="262"/>
+      <c r="L48" s="262"/>
+      <c r="M48" s="262"/>
+      <c r="N48" s="262"/>
+      <c r="O48" s="262"/>
+      <c r="P48" s="262"/>
+      <c r="Q48" s="262"/>
+      <c r="R48" s="262"/>
+      <c r="S48" s="262"/>
+      <c r="T48" s="262"/>
+      <c r="U48" s="262"/>
+      <c r="V48" s="262"/>
+      <c r="W48" s="262"/>
+      <c r="X48" s="262"/>
+      <c r="Y48" s="262"/>
+      <c r="Z48" s="262"/>
+      <c r="AA48" s="262"/>
+      <c r="AB48" s="262"/>
+      <c r="AC48" s="262"/>
+      <c r="AD48" s="262"/>
+      <c r="AE48" s="262"/>
+      <c r="AF48" s="262"/>
+      <c r="AG48" s="262"/>
+      <c r="AH48" s="262"/>
+      <c r="AI48" s="262"/>
+      <c r="AJ48" s="262"/>
+      <c r="AK48" s="262"/>
+      <c r="BA48" s="263"/>
+    </row>
+    <row r="49" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A49" s="261"/>
+      <c r="B49" s="262"/>
+      <c r="C49" s="262"/>
+      <c r="D49" s="262"/>
+      <c r="E49" s="262"/>
+      <c r="F49" s="262"/>
+      <c r="G49" s="262"/>
+      <c r="H49" s="262"/>
+      <c r="I49" s="262"/>
+      <c r="J49" s="262"/>
+      <c r="K49" s="262"/>
+      <c r="L49" s="262"/>
+      <c r="M49" s="262"/>
+      <c r="N49" s="262"/>
+      <c r="O49" s="262"/>
+      <c r="P49" s="262"/>
+      <c r="Q49" s="262"/>
+      <c r="R49" s="262"/>
+      <c r="S49" s="262"/>
+      <c r="T49" s="262"/>
+      <c r="U49" s="262"/>
+      <c r="V49" s="262"/>
+      <c r="W49" s="262"/>
+      <c r="X49" s="262"/>
+      <c r="Y49" s="262"/>
+      <c r="Z49" s="262"/>
+      <c r="AA49" s="262"/>
+      <c r="AB49" s="262"/>
+      <c r="AC49" s="262"/>
+      <c r="AD49" s="262"/>
+      <c r="AE49" s="262"/>
+      <c r="AF49" s="262"/>
+      <c r="AG49" s="262"/>
+      <c r="AH49" s="262"/>
+      <c r="AI49" s="262"/>
+      <c r="AJ49" s="262"/>
+      <c r="AK49" s="262"/>
+      <c r="BA49" s="263"/>
+    </row>
+    <row r="50" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A50" s="261"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
+      <c r="D50" s="262"/>
+      <c r="E50" s="262"/>
+      <c r="F50" s="262"/>
+      <c r="G50" s="262"/>
+      <c r="H50" s="262"/>
+      <c r="I50" s="262"/>
+      <c r="J50" s="262"/>
+      <c r="K50" s="262"/>
+      <c r="L50" s="262"/>
+      <c r="M50" s="262"/>
+      <c r="N50" s="262"/>
+      <c r="O50" s="262"/>
+      <c r="P50" s="262"/>
+      <c r="Q50" s="262"/>
+      <c r="R50" s="262"/>
+      <c r="S50" s="262"/>
+      <c r="T50" s="262"/>
+      <c r="U50" s="262"/>
+      <c r="V50" s="262"/>
+      <c r="W50" s="262"/>
+      <c r="X50" s="262"/>
+      <c r="Y50" s="262"/>
+      <c r="Z50" s="262"/>
+      <c r="AA50" s="262"/>
+      <c r="AB50" s="262"/>
+      <c r="AC50" s="262"/>
+      <c r="AD50" s="262"/>
+      <c r="AE50" s="262"/>
+      <c r="AF50" s="262"/>
+      <c r="AG50" s="262"/>
+      <c r="AH50" s="262"/>
+      <c r="AI50" s="262"/>
+      <c r="AJ50" s="262"/>
+      <c r="AK50" s="262"/>
+      <c r="BA50" s="263"/>
+    </row>
+    <row r="51" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A51" s="266"/>
+      <c r="B51" s="267"/>
+      <c r="C51" s="267"/>
+      <c r="D51" s="267"/>
+      <c r="E51" s="267"/>
+      <c r="F51" s="267"/>
+      <c r="G51" s="267"/>
+      <c r="H51" s="267"/>
+      <c r="I51" s="267"/>
+      <c r="J51" s="267"/>
+      <c r="K51" s="267"/>
+      <c r="L51" s="267"/>
+      <c r="M51" s="267"/>
+      <c r="N51" s="267"/>
+      <c r="O51" s="267"/>
+      <c r="P51" s="267"/>
+      <c r="Q51" s="267"/>
+      <c r="R51" s="267"/>
+      <c r="S51" s="267"/>
+      <c r="T51" s="267"/>
+      <c r="U51" s="267"/>
+      <c r="V51" s="267"/>
+      <c r="W51" s="267"/>
+      <c r="X51" s="267"/>
+      <c r="Y51" s="267"/>
+      <c r="Z51" s="267"/>
+      <c r="AA51" s="267"/>
+      <c r="AB51" s="267"/>
+      <c r="AC51" s="267"/>
+      <c r="AD51" s="267"/>
+      <c r="AE51" s="267"/>
+      <c r="AF51" s="267"/>
+      <c r="AG51" s="267"/>
+      <c r="AH51" s="267"/>
+      <c r="AI51" s="267"/>
+      <c r="AJ51" s="267"/>
+      <c r="AK51" s="262"/>
+      <c r="BA51" s="263"/>
+    </row>
+    <row r="52" spans="1:53" ht="18" customHeight="1">
+      <c r="A52" s="254" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="255"/>
+      <c r="C52" s="255"/>
+      <c r="D52" s="255"/>
+      <c r="E52" s="255"/>
+      <c r="F52" s="255"/>
+      <c r="G52" s="255"/>
+      <c r="H52" s="255"/>
+      <c r="I52" s="255"/>
+      <c r="J52" s="255"/>
+      <c r="K52" s="255"/>
+      <c r="L52" s="255"/>
+      <c r="M52" s="255"/>
+      <c r="N52" s="255"/>
+      <c r="O52" s="255"/>
+      <c r="P52" s="255"/>
+      <c r="Q52" s="255"/>
+      <c r="R52" s="255"/>
+      <c r="S52" s="255"/>
+      <c r="T52" s="255"/>
+      <c r="U52" s="255"/>
+      <c r="V52" s="255"/>
+      <c r="W52" s="255"/>
+      <c r="X52" s="255"/>
+      <c r="Y52" s="255"/>
+      <c r="Z52" s="255"/>
+      <c r="AA52" s="255"/>
+      <c r="AB52" s="255"/>
+      <c r="AC52" s="255"/>
+      <c r="AD52" s="255"/>
+      <c r="AE52" s="255"/>
+      <c r="AF52" s="255"/>
+      <c r="AG52" s="255"/>
+      <c r="AH52" s="255"/>
+      <c r="AI52" s="255"/>
+      <c r="AJ52" s="255"/>
+      <c r="AK52" s="255"/>
+      <c r="AL52" s="255"/>
+      <c r="AM52" s="255"/>
+      <c r="AN52" s="255"/>
+      <c r="AO52" s="255"/>
+      <c r="AP52" s="255"/>
+      <c r="AQ52" s="255"/>
+      <c r="AR52" s="255"/>
+      <c r="AS52" s="255"/>
+      <c r="AT52" s="255"/>
+      <c r="AU52" s="255"/>
+      <c r="AV52" s="255"/>
+      <c r="AW52" s="255"/>
+      <c r="AX52" s="255"/>
+      <c r="AY52" s="255"/>
+      <c r="AZ52" s="255"/>
+      <c r="BA52" s="255"/>
+    </row>
+    <row r="53" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A53" s="264"/>
+      <c r="B53" s="265"/>
+      <c r="C53" s="265"/>
+      <c r="D53" s="265"/>
+      <c r="E53" s="265"/>
+      <c r="F53" s="265"/>
+      <c r="G53" s="265"/>
+      <c r="H53" s="265"/>
+      <c r="I53" s="265"/>
+      <c r="J53" s="265"/>
+      <c r="K53" s="265"/>
+      <c r="L53" s="265"/>
+      <c r="M53" s="265"/>
+      <c r="N53" s="265"/>
+      <c r="O53" s="265"/>
+      <c r="P53" s="265"/>
+      <c r="Q53" s="265"/>
+      <c r="R53" s="265"/>
+      <c r="S53" s="265"/>
+      <c r="T53" s="265"/>
+      <c r="U53" s="265"/>
+      <c r="V53" s="265"/>
+      <c r="W53" s="265"/>
+      <c r="X53" s="265"/>
+      <c r="Y53" s="265"/>
+      <c r="Z53" s="265"/>
+      <c r="AA53" s="265"/>
+      <c r="AB53" s="265"/>
+      <c r="AC53" s="265"/>
+      <c r="AD53" s="265"/>
+      <c r="AE53" s="265"/>
+      <c r="AF53" s="265"/>
+      <c r="AG53" s="265"/>
+      <c r="AH53" s="265"/>
+      <c r="AI53" s="265"/>
+      <c r="AJ53" s="265"/>
+      <c r="AK53" s="262"/>
+      <c r="BA53" s="263"/>
+    </row>
+    <row r="54" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A54" s="261"/>
+      <c r="B54" s="262"/>
+      <c r="C54" s="262"/>
+      <c r="D54" s="262"/>
+      <c r="E54" s="262"/>
+      <c r="F54" s="262"/>
+      <c r="G54" s="262"/>
+      <c r="H54" s="262"/>
+      <c r="I54" s="262"/>
+      <c r="J54" s="262"/>
+      <c r="K54" s="262"/>
+      <c r="L54" s="262"/>
+      <c r="M54" s="262"/>
+      <c r="N54" s="262"/>
+      <c r="O54" s="262"/>
+      <c r="P54" s="262"/>
+      <c r="Q54" s="262"/>
+      <c r="R54" s="262"/>
+      <c r="S54" s="262"/>
+      <c r="T54" s="262"/>
+      <c r="U54" s="262"/>
+      <c r="V54" s="262"/>
+      <c r="W54" s="262"/>
+      <c r="X54" s="262"/>
+      <c r="Y54" s="262"/>
+      <c r="Z54" s="262"/>
+      <c r="AA54" s="262"/>
+      <c r="AB54" s="262"/>
+      <c r="AC54" s="262"/>
+      <c r="AD54" s="262"/>
+      <c r="AE54" s="262"/>
+      <c r="AF54" s="262"/>
+      <c r="AG54" s="262"/>
+      <c r="AH54" s="262"/>
+      <c r="AI54" s="262"/>
+      <c r="AJ54" s="262"/>
+      <c r="AK54" s="262"/>
+      <c r="BA54" s="263"/>
+    </row>
+    <row r="55" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A55" s="266"/>
+      <c r="B55" s="267"/>
+      <c r="C55" s="267"/>
+      <c r="D55" s="267"/>
+      <c r="E55" s="267"/>
+      <c r="F55" s="267"/>
+      <c r="G55" s="267"/>
+      <c r="H55" s="267"/>
+      <c r="I55" s="267"/>
+      <c r="J55" s="267"/>
+      <c r="K55" s="267"/>
+      <c r="L55" s="267"/>
+      <c r="M55" s="267"/>
+      <c r="N55" s="267"/>
+      <c r="O55" s="267"/>
+      <c r="P55" s="267"/>
+      <c r="Q55" s="267"/>
+      <c r="R55" s="267"/>
+      <c r="S55" s="267"/>
+      <c r="T55" s="267"/>
+      <c r="U55" s="267"/>
+      <c r="V55" s="267"/>
+      <c r="W55" s="267"/>
+      <c r="X55" s="267"/>
+      <c r="Y55" s="267"/>
+      <c r="Z55" s="267"/>
+      <c r="AA55" s="267"/>
+      <c r="AB55" s="267"/>
+      <c r="AC55" s="267"/>
+      <c r="AD55" s="267"/>
+      <c r="AE55" s="267"/>
+      <c r="AF55" s="267"/>
+      <c r="AG55" s="267"/>
+      <c r="AH55" s="267"/>
+      <c r="AI55" s="267"/>
+      <c r="AJ55" s="267"/>
+      <c r="AK55" s="267"/>
+      <c r="AL55" s="242"/>
+      <c r="AM55" s="242"/>
+      <c r="AN55" s="242"/>
+      <c r="AO55" s="242"/>
+      <c r="AP55" s="242"/>
+      <c r="AQ55" s="242"/>
+      <c r="AR55" s="242"/>
+      <c r="AS55" s="242"/>
+      <c r="AT55" s="242"/>
+      <c r="AU55" s="242"/>
+      <c r="AV55" s="242"/>
+      <c r="AW55" s="242"/>
+      <c r="AX55" s="242"/>
+      <c r="AY55" s="242"/>
+      <c r="AZ55" s="242"/>
+      <c r="BA55" s="268"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A9:BA9"/>
+    <mergeCell ref="A43:BA43"/>
+    <mergeCell ref="A52:BA52"/>
+    <mergeCell ref="AO1:AS1"/>
+    <mergeCell ref="AT1:BA1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:S5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:S6"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <dataValidations count="2">
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{BD114640-60E2-43CB-A3CE-EB84A34449F7}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A10:AK42 N1:O1 I1:L1 A53:AK55 G5:G6 V1 AC1 AE1 A44:AK51" xr:uid="{94F93DB4-7C3A-4A6B-8E3D-189CF0B65D2B}"/>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>